--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G286"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +453,7695 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AEK Athens vs Levski Sofia</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Celje vs Slovan Bratislava</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Lyon vs Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Viking vs Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rapid Wien vs Hearts</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Wolfsburg (K) vs Inter Milano (K)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sparta Prague (K) vs Servette Chenois (K)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Czarni Sosnowiec (K) vs Oud-Heverlee Leuven (K)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PSV (K) vs Koge (K)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Frankfurt (K) vs Paris Saint Germain (K)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ajax (K) vs Real Madrid (K)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chelsea (K) vs Real Sociedad (K)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>St. Polten (K) vs Juventus (K)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>17</v>
+      </c>
+      <c r="C14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Apollon Limassol (K) vs Hafnarfjordur (K)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SeaSters Odessa (K) vs Rosenborg (K)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Mitrovica (K) vs Metalist Kharkiv (K)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Sarajevo (K) vs Slovan Liberec (K)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ZNK Radomlje (W) vs Valerenga (K)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>23</v>
+      </c>
+      <c r="C19" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Hajduk Split (K) vs Fortuna Hjorring (K)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Sturm Graz (K) vs Gintra (K)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Anderlecht (K) vs Feyenoord (K)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Breidablik Kopavogur (K) vs AFK Csikszereda Miercurea Ciuc (W)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ZFK Spartak Subotica (K) vs Brondby (K)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Torreense (K) vs Kolos Kovalivka (W)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Bootle vs Northwich Victoria</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bradford vs Burnley</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tottenham vs Charlton</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Newcastle vs West Bromwich</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D29" t="n">
+        <v>7</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Preston vs Everton</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Stocksbridge PS vs Lincoln United</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Rugby Borough vs Wellingborough Town</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Coventry United vs Mickleover Sports</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Avro vs Leek Town</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Stockport County U21 vs Charlton Athletic U21</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Bromley U21 vs West Brom U21</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Real Madrid vs Real Sociedad</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D37" t="n">
+        <v>9</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Schoningen vs St. Pauli II</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Jeddeloh vs Hannover 96 II</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>VfB Lubeck vs Hamburger SV II</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F40" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Drochtersen / Assel vs Werder Bremen II</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CSD Central Ballester vs Sportivo Barracas</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C42" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Club Atletico Acassuso vs CA San Telmo</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CA Chaco For Ever vs CA San Miguel</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>CA Patronato vs CA Atlanta</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Colon Reserves vs Lanus Reserves</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Ca Platense Reserves vs Atletico Rafaela Reserves</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Banfield Reserves vs Ca Talleres De Cordoba Reserves</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>San Lorenzo Reserves vs Godoy Cruz Reserves</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Quilmes Reserves vs Ca Independiente Reserves</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Estudiantes La Plata Reserves vs Boca Juniors Reserves</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Deportivo Camioneros vs Comunicaciones de Bueno Aires</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C52" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Deportivo Liniers vs Deportivo Armenio</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C53" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Canuelas FC Reserves vs CA Lugano Reserves</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Yupanqui U20 vs Sacachispas U20</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Defensores De Belgrano vs Los Andes Reserves</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Deportivo Moron Reserves vs Almirante Brown Reserves</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Nueva Chicago Reserves vs Ferrocarril Midland Reserves</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D58" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Chacarita Juniors Reserves vs CA San Miguel Reserves</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D59" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Vietnam vs Tayland</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C60" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D60" t="n">
+        <v>4</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Preston Lions vs South Melbourne</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Darwin Hearts vs Casuarina</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F62" t="n">
+        <v>5</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Palmerston Rovers vs Port Darwin</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C63" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F63" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>RRC Stockay-Warfusee vs Royale Union Hutoise</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Crossing Schaerbeek vs RFC Union La Calamine</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D65" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F65" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RSC Habay vs RWDM Brussels</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F66" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Union Saint Gilloise II vs Union Rochefortoise</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Renaissance Mons (RAEC) vs Meux</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D68" t="n">
+        <v>5</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AFC Tubize vs Charleroi II</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F69" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Royal Olympic Charleroi vs Standard de Liege 16 FC</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F70" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs The Strongest</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F71" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>FK Igman Konjic vs Stupcanica Olovo</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>America PE U20 vs Nautico U20</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>5</v>
+      </c>
+      <c r="C73" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F73" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Santa Cruz PE U20 vs Ipojuca U20</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F74" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Nova Iguacu FC vs Sampaio Correa RJ</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C75" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F75" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Boavista SC/RJ vs Madureira RJ</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Fastav Zlin U19 vs Pardubice U19</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="C77" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>FC Sparta Brno vs Banik Ostrava</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>15</v>
+      </c>
+      <c r="C78" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F78" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Kozlovice Fc vs MFK Karvina</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>17</v>
+      </c>
+      <c r="C79" t="n">
+        <v>8</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F79" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Meteor Praha vs Mlada Boleslav</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>19</v>
+      </c>
+      <c r="C80" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F80" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>FK Krimice vs Teplice</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>9</v>
+      </c>
+      <c r="C81" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F81" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>FK Prepere vs Slovan Liberec</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>19</v>
+      </c>
+      <c r="C82" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>FC Spartak Velka Bites vs Slovacko</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>15</v>
+      </c>
+      <c r="C83" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Frydlant Nad Ostravici vs Zbrojovka Brno</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>15</v>
+      </c>
+      <c r="C84" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>FK Banik Sokolov vs Graffin Vlasim</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>8</v>
+      </c>
+      <c r="C85" t="n">
+        <v>5</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>FC Pisek vs Pardubice</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C86" t="n">
+        <v>5</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Uhersky Brod vs Artis Brno</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>8</v>
+      </c>
+      <c r="C87" t="n">
+        <v>5</v>
+      </c>
+      <c r="D87" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Bzenec vs Trinec</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C88" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>FK Admira Praha vs Táborsko</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>6</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Tatran Vsechovice vs Prostejov</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>6</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D90" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Kraluv Dvur vs Loko Praha</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C91" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D91" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Fk Banik Sous vs Pribram</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SK Benatky nad Jizerou vs Neratovice Byskovice</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>MFK Vitkovice vs Polanka</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C94" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D94" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Marienlyst vs VSK Arhus</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>5</v>
+      </c>
+      <c r="C95" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D95" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Fredericia vs Odense</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C96" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FA 2000 vs Lyngby</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>10</v>
+      </c>
+      <c r="C97" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Al Ahli Jeddah vs Auckland FC</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="C98" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D98" t="n">
+        <v>15</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Italy U20 (W) vs Portugal U20 (W)</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C99" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D99" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F99" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Terrassa CF vs CF Vilanova Geltru</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C100" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D100" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FC Barcelona B vs Reus FC Reddis</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C101" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>CD Numancia vs Utebo</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Atletico Astorga CF vs Salamanca CF UDS</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Oyonesa vs San Ignacio</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C104" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Real Union de Tenerife Santa Cruz vs Tenerife B</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C105" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D105" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F105" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Arsenal (K) vs Charlton (K)</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="C106" t="n">
+        <v>13</v>
+      </c>
+      <c r="D106" t="n">
+        <v>34</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Fulham U21 vs Borussia Dortmund II U21</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C107" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F107" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>LDU Portoviejo vs Delfin SC</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C108" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Mika Yerevan vs FC Bentonit</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>4</v>
+      </c>
+      <c r="C109" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D109" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>JK Tammeka Tartu vs Flora Tallinn</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>4</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D110" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F110" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>JK Trans Narva vs Nomme Kalju</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C111" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Levadia Tallinn vs Paide Linnameeskond</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C112" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D112" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Lautp vs Kotajarven Pallo</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F113" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>JyTy vs VG-62</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C114" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F114" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Metso vs JJK Jyvaskyla 2</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C115" t="n">
+        <v>6</v>
+      </c>
+      <c r="D115" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F115" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>KPV Akatemia vs VIFK</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C116" t="n">
+        <v>6</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F116" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>KuPS Akatemia II vs Ylamyllyn Yllatys</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C117" t="n">
+        <v>4</v>
+      </c>
+      <c r="D117" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F117" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Lepa vs MPS</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C118" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D118" t="n">
+        <v>6</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Golden Arrows vs Stellenbosch</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C119" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Mamelodi Sundowns vs AmaZulu</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D120" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Richards Bay vs Kaizer Chiefs</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C121" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D121" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E121" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Polokwane City vs Milford FC</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C122" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D122" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F122" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Dila Gori vs FC Samgurali Tskaltubo</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C123" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>FC Gagra vs Aragvi Dusheti</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D124" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Torpedo Kutaisi vs FC Dinamo Batumi</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C125" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>FC WIT Georgia Tblisi vs Iberia 2010 Tbilisi</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="C126" t="n">
+        <v>6</v>
+      </c>
+      <c r="D126" t="n">
+        <v>12</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>NK Dinamo Zagreb U19 vs HNK Gorica U19</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C127" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D127" t="n">
+        <v>11</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F127" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Nk Rudes U19 vs Kustosija U19</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C128" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>NK Trnje U19 vs NK Istra 1961 U19</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>3</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>HNK Rijeka U19 vs NK Lucko U19</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>NK Radnik Sesvete U19 vs NK Solin U19</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>NK Varazdin U19 vs HNK Hajduk Split U19</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F132" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>NK Vrbovec vs HNK Daruvar</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>NK Tomislav Cerna vs NK Uljanik</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>6</v>
+      </c>
+      <c r="C134" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>NK Dinamo Predavac vs NK Hrvatski Dragovoljac</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Zagora Unesic vs NK Bratstvo Jurovec</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C136" t="n">
+        <v>11</v>
+      </c>
+      <c r="D136" t="n">
+        <v>23</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F136" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>GNK Tigar Sveta Nedelja vs Karlovac</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>8</v>
+      </c>
+      <c r="C137" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F137" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Orijent 1919 vs Radnik Krizevci</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C138" t="n">
+        <v>4</v>
+      </c>
+      <c r="D138" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Bidhannagar MSA vs Bhawanipore</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>31</v>
+      </c>
+      <c r="C139" t="n">
+        <v>11</v>
+      </c>
+      <c r="D139" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F139" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Patha Chakra vs BSS Sporting Club</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C140" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F140" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Calcutta Customs vs United Kolkata</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F141" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>George Telegraph vs Mohun Bagan SG Reserves</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>26</v>
+      </c>
+      <c r="C142" t="n">
+        <v>8</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Mizoram vs Dinthar FC</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C143" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D143" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F143" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Saikhamakawn FC vs Aizawl Fc</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>26</v>
+      </c>
+      <c r="C144" t="n">
+        <v>10</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F144" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Mylliem SC vs Mawlai SC</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>26</v>
+      </c>
+      <c r="C145" t="n">
+        <v>10</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F145" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Al Naft vs Duhok</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C146" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="D146" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E146" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Al Kahrabaa Club vs Al Karma</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D147" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E147" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Mosul FC vs Karbala Fc</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D148" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E148" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Al Minaa vs Al-Gharraf SC</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="C149" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D149" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E149" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Al Talaba Fc vs Newroz SC</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C150" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Finglas United FC vs Killester United</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C151" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D151" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E151" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F151" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>St Mochtas vs Kilbarrack United</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C152" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F152" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Gartcairn (W) vs Dundee United WFC (W)</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F153" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Livingston (W) vs Queens Park (W)</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C154" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F154" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>IFK Umea vs Umea FC Akademi</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C155" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F155" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>FC Stockholm Internazionale vs Hammarby</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>11</v>
+      </c>
+      <c r="C156" t="n">
+        <v>6</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Skovde AIK vs Halmstads BK</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C157" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Bollstanas SK vs United IK Nordic</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C158" t="n">
+        <v>5</v>
+      </c>
+      <c r="D158" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F158" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Dalstorps IF vs Norrby IF</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C159" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D159" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F159" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Fc Bulle vs Young Boys Ii</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="C160" t="n">
+        <v>4</v>
+      </c>
+      <c r="D160" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F160" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>FC Langenthal vs FC Schotz 1927</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C161" t="n">
+        <v>4</v>
+      </c>
+      <c r="D161" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E161" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F161" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>FC Courtetelle vs Munsingen</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C162" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Meyrin vs Servette II</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C163" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D163" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E163" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F163" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Vikingur Reykjavik U19 vs FH Hafnarfjordur U19</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C164" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D164" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E164" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F164" t="n">
+        <v>5</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Sanfrecce Hiroshima vs Okinawa Sv</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="C165" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D165" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F165" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Cerezo Osaka vs FC Gifu</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C166" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D166" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Machida Zelvia vs Grulla Morioka</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="C167" t="n">
+        <v>7</v>
+      </c>
+      <c r="D167" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F167" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Tokushima Vortis vs Tokushima</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="C168" t="n">
+        <v>8</v>
+      </c>
+      <c r="D168" t="n">
+        <v>15</v>
+      </c>
+      <c r="E168" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F168" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy 1969 vs ThespaKusatsu Gunma</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C169" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D169" t="n">
+        <v>7</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Nagoya Grampus Eight vs Gainare Tottori</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C170" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D170" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F170" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Imabari vs Blaublitz Akita</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C171" t="n">
+        <v>3</v>
+      </c>
+      <c r="D171" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E171" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F171" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Omiya Ardija vs Vanraure Hachnohe</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D172" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Sagan Tosu vs Kataller Toyama</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D173" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Kashima Antlers vs Atletico Suzuka</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C174" t="n">
+        <v>11</v>
+      </c>
+      <c r="D174" t="n">
+        <v>26</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F174" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Kawasaki Frontale vs Tochigi</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C175" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D175" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F175" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Avispa Fukuoka vs Verspah Oita</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C176" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D176" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F176" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Consadole Sapporo vs Ventforet Kofu</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D177" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Iwaki SC vs Oita Trinita</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D178" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Jubilo Iwata vs Tegevajaro Miyazaki</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Albirex Niigata vs Kagoshima United</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D180" t="n">
+        <v>4</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Vegalta Sendai vs Tochigi City</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D181" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Vissel Kobe vs Veroskronos Tsuno</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C182" t="n">
+        <v>10</v>
+      </c>
+      <c r="D182" t="n">
+        <v>23</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F182" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Gamba Osaka vs Mio Biwako Shiga</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C183" t="n">
+        <v>11</v>
+      </c>
+      <c r="D183" t="n">
+        <v>23</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F183" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Montedio Yamagata vs Fujieda MYFC</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D184" t="n">
+        <v>3</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>V-Varen Nagasaki vs Ehime FC</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C185" t="n">
+        <v>5</v>
+      </c>
+      <c r="D185" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F185" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Kyoto Purple Sanga vs Maruyasu Okazaki</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C186" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D186" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F186" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Fagiano Okayama vs Belugarosso Iwami</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C187" t="n">
+        <v>11</v>
+      </c>
+      <c r="D187" t="n">
+        <v>26</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F187" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>FC Tokyo vs Nagano Parceiro</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C188" t="n">
+        <v>8</v>
+      </c>
+      <c r="D188" t="n">
+        <v>17</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F188" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Daejeon Citizen vs Ulsan Hyundai Horang-i</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C189" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F189" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Anyang vs Incheon United</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C190" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D190" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E190" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Gangwon vs Gwangju</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C191" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D191" t="n">
+        <v>6</v>
+      </c>
+      <c r="E191" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Al-Shabab vs Al-Jahra</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Al-Salmiyah vs Al-Nasr Kuwait</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D193" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Ballymena United (K) vs Mid Ulster (K)</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D194" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F194" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Bangor Reserves vs Portadown Reserves</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F195" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Crusaders Reserves vs Ballymena United Reserves</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F196" t="n">
+        <v>3</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>FK Utenis Utena vs FM Klaipedos</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C197" t="n">
+        <v>5</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F197" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>FC Ujpest II vs Szeged-Csanad Grosics II</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C198" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D198" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Tiszafuredi vs Cigand SE</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C199" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Erzsebeti SMTK vs Sandorfalvi Ske</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="C200" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D200" t="n">
+        <v>6</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F200" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>MTE 1904 Mosonmagyarovar vs 1908 SZAC Budapest</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C201" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D201" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F201" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>PTE PEAC vs Budaorsi SC</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D202" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F202" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Tatabanya vs Sarisapi BSE</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C203" t="n">
+        <v>5</v>
+      </c>
+      <c r="D203" t="n">
+        <v>8</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F203" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Debreceni VSC II vs Eger SE</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D204" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F204" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Kaposvari Rakoczi vs Paksi SE II</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C205" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D205" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E205" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F205" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Budapest Honved II vs Szegedi VSE</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="C206" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D206" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F206" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Csepel FC vs BKV Elore</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D207" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F207" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Godollo SK vs Fuzesabony</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C208" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D208" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F208" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Dorogi FC vs Komarom VSE</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D209" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Budafoki MTE-Ujbuda vs Szekszardi Ufc</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C210" t="n">
+        <v>7</v>
+      </c>
+      <c r="D210" t="n">
+        <v>15</v>
+      </c>
+      <c r="E210" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F210" t="n">
+        <v>3</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Nyiregyhaza II vs Ozd-Sajovolgye</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="C211" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D211" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Monori SE vs Hodmezovasarhelyi</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D212" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F212" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Ferencvarosi TC II vs Majosi SE</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C213" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D213" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F213" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Veszprem FC vs Szombathelyi Haladas</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C214" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D214" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F214" t="n">
+        <v>2</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Iii Ker Tue Upe vs Bekescsaba 1912 Elore SE</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C215" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D215" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E215" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Papai Perutz vs Zalaegerszegi TE II</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C216" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D216" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E216" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Gyori ETO FC II vs Kiraly SZE</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C217" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D217" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>MTK Hungaria (K) vs Astra Hungary (W)</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C218" t="n">
+        <v>10</v>
+      </c>
+      <c r="D218" t="n">
+        <v>26</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F218" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Puskas FC (K) vs Ujpest (W)</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C219" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D219" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E219" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F219" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Szent Mihaly SE (W) vs Szekszardi (W)</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C220" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D220" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F220" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Budapest Honved (W) vs Gyori ETO (K)</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C221" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F221" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Johor Darul Takzim FC vs Kelantan Red Warrior FC</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="C222" t="n">
+        <v>15</v>
+      </c>
+      <c r="D222" t="n">
+        <v>31</v>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur City FC vs Kuching City FC</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C223" t="n">
+        <v>5</v>
+      </c>
+      <c r="D223" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E223" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F223" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Smouha vs Asyut Cement Petroleum</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C224" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D224" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>National Bank of Egypt SC vs El Zamalek</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C225" t="n">
+        <v>3</v>
+      </c>
+      <c r="D225" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E225" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F225" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Petrojet vs Talaea El Gaish</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C226" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D226" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E226" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F226" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Costa Do Sol vs Black Bulls Maputo</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C227" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D227" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E227" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F227" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Strommen vs Raufoss</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C228" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D228" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E228" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F228" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Stromsgodset vs Hodd</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C229" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D229" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="F229" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Moss vs Sogndal</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C230" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D230" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F230" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Odd vs Kongsvinger</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C231" t="n">
+        <v>4</v>
+      </c>
+      <c r="D231" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F231" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Asane vs Lyn</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C232" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E232" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F232" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Haugesund vs Egersund</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C233" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D233" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F233" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Stabaek vs Ranheim</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C234" t="n">
+        <v>5</v>
+      </c>
+      <c r="D234" t="n">
+        <v>5</v>
+      </c>
+      <c r="E234" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F234" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Rana FK vs Follo</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C235" t="n">
+        <v>4</v>
+      </c>
+      <c r="D235" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E235" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F235" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Lillestrom U19 vs Tromso U19</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C236" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D236" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E236" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F236" t="n">
+        <v>5</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Varhaug vs Sandnes</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="C237" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D237" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E237" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F237" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>FK Mash'al Mubarek vs Navbahor</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>8</v>
+      </c>
+      <c r="C238" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D238" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Lokomotiv Tashkent FK vs FC Bunyodkor</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C239" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D239" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F239" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>PFK Qizilqum Zarafshon vs Nasaf Qarshi</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>4</v>
+      </c>
+      <c r="C240" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D240" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E240" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Deportivo Santani vs Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C241" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D241" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense (W) vs 2 de Mayo (W)</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C242" t="n">
+        <v>5</v>
+      </c>
+      <c r="D242" t="n">
+        <v>6</v>
+      </c>
+      <c r="E242" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F242" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Atletico Grau vs Sport Boys</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D243" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E243" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F243" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Sporting Cristal Lima vs Sport Huancayo</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D244" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E244" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F244" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Spartakus Daleszyce vs LKS Orleta Kielce</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>4</v>
+      </c>
+      <c r="C245" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="E245" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F245" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>LKS Mszczonowianka Mszczonow vs Hutnik Warsaw</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>4</v>
+      </c>
+      <c r="C246" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D246" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E246" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F246" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>KS Ruch Chorzow II vs Podlesianka Katowice</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C247" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E247" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F247" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>MKS Przasnysz vs MKS Makowianka Makow Maz</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C248" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D248" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F248" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Jaguar Gdansk vs Starogard Gdanski</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="C249" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D249" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F249" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Unia Tarnow vs Dalin Myslenice</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C250" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D250" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F250" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Ruch Radzionkow vs GKS Katowice II</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>2</v>
+      </c>
+      <c r="C251" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D251" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E251" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F251" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Bron Radom vs Legionovia Legionowo</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D252" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E252" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F252" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Victoria Sulejowek vs Polonia Warsaw II</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C253" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D253" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E253" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F253" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Hutnik Krakow II vs GKS Victoria Jaworzno</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C254" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D254" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E254" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F254" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>KDV Tomsk vs Chertanovo Moscow</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C255" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D255" t="n">
+        <v>5</v>
+      </c>
+      <c r="E255" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F255" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>NoSta Novotroitsk vs FK Sokol Saratov</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C256" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D256" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E256" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F256" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Torpedo Miass vs Volna Nizhegorodskaya</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="C257" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D257" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F257" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Dinamo Stavropol vs FK Astrakhan</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D258" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E258" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F258" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Druzhba Maikop vs Neftyanik Izberbash</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="C259" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D259" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E259" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F259" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>FC Volgar Astrakhan vs FK Spartak Nalchik</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D260" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E260" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F260" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Vodovac U19 vs Brodarac U19</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C261" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D261" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E261" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F261" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Usce Novi Beograd U19 vs Spartak Subotica U19</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D262" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E262" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F262" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Vojvodina U19 vs Cukaricki U19</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D263" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E263" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F263" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Jedinstvo Ub U19 vs Mladost Lucani U19</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D264" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E264" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F264" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Geca 73 vs Fk Kosicka Nova Ves</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>15</v>
+      </c>
+      <c r="C265" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D265" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F265" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>FK Gerlachov vs Tatran Liptovsky Mikulas</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>15</v>
+      </c>
+      <c r="C266" t="n">
+        <v>9</v>
+      </c>
+      <c r="D266" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F266" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Zp Sport Podbrezova U19 vs FC Petrzalka U19</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C267" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D267" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F267" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>NK IB 1975 Ljubljana vs NK Litija</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="C268" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D268" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F268" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>NK Skofja Loka vs Sencur</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D269" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E269" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F269" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>ND Adria vs NK Bilje</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>8</v>
+      </c>
+      <c r="C270" t="n">
+        <v>5</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E270" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F270" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>NK Race vs Korotan Prevalje</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C271" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D271" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F271" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Al Faisaly Harmah vs Al Fateh</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C272" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D272" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F272" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Al-Draih vs Al Kholood</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C273" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D273" t="n">
+        <v>4</v>
+      </c>
+      <c r="E273" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F273" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Al Adalah vs Al Taee Hail</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C274" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D274" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E274" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F274" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Al Zulfi FC vs Al Wahda Mecca</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C275" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D275" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E275" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F275" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Juventud Piedras vs Club Oriental</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C276" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D276" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F276" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Danubio vs Atenas</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C277" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D277" t="n">
+        <v>4</v>
+      </c>
+      <c r="E277" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F277" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>CA Progreso Montevideo vs Club Atletico River Plate</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C278" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D278" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E278" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F278" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Plaza Colonia vs Cerro Largo FC</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C279" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D279" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E279" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F279" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Bolivar SC vs Monagas SC</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C280" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D280" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="E280" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F280" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Atletico El Vigia vs Club Atletico Barinas</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C281" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D281" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E281" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F281" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Mineros Guayana vs Dynamo Puerto Fc</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C282" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D282" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E282" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F282" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Rayo Zuliano vs Urena Fc</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C283" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D283" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E283" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F283" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Zamora FC vs Real Frontera</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C284" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D284" t="n">
+        <v>19</v>
+      </c>
+      <c r="E284" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F284" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Aragua FC vs Yaracuyanos FC</t>
+        </is>
+      </c>
+      <c r="B285" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C285" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D285" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E285" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F285" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Trujillanos FC vs Deportivo Lara</t>
+        </is>
+      </c>
+      <c r="B286" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C286" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D286" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E286" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F286" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:G273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bandirmaspor vs Antalyaspor</t>
+          <t>Vanspor FK vs Batman Petrolspor</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="C2" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="E2" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="F2" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -483,23 +483,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Umraniyespor vs Muglaspor</t>
+          <t>Karagumruk vs Kayserispor</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>2.45</v>
       </c>
       <c r="C3" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="D3" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="E3" t="n">
-        <v>2.31</v>
+        <v>1.92</v>
       </c>
       <c r="F3" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -510,23 +510,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sariyer GK vs Pendikspor</t>
+          <t>Sivasspor vs Mardin Buyuksehir Belediyespor</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.39</v>
+        <v>2.22</v>
       </c>
       <c r="C4" t="n">
         <v>3.2</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="E4" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="F4" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -537,23 +537,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Boluspor vs Keçiörengücü</t>
+          <t>Paris Saint Germain (K) vs Frankfurt (K)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="C5" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="E5" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="F5" t="n">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Austria Vienna (K) vs Brann (K)</t>
+          <t>Inter Milano (K) vs Wolfsburg (K)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="C6" t="n">
         <v>3.6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.84</v>
+        <v>2.07</v>
       </c>
       <c r="E6" t="n">
         <v>1.55</v>
       </c>
       <c r="F6" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -591,23 +591,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Metalist Kharkiv (K) vs Mitrovica (K)</t>
+          <t>Servette Chenois (K) vs Sparta Prague (K)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D7" t="n">
-        <v>4.75</v>
+        <v>3.7</v>
       </c>
       <c r="E7" t="n">
         <v>1.55</v>
       </c>
       <c r="F7" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -618,23 +618,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Preston vs Bristol</t>
+          <t>Real Sociedad (K) vs Chelsea (K)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.73</v>
+        <v>5.5</v>
       </c>
       <c r="C8" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4</v>
+        <v>1.41</v>
       </c>
       <c r="E8" t="n">
-        <v>1.87</v>
+        <v>1.43</v>
       </c>
       <c r="F8" t="n">
-        <v>1.83</v>
+        <v>2.55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -645,23 +645,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sheffield United vs Bolton</t>
+          <t>Koge (K) vs PSV (K)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="C9" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D9" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="E9" t="n">
         <v>1.76</v>
       </c>
       <c r="F9" t="n">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -672,23 +672,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>West Ham vs Wolverhampton</t>
+          <t>Oud-Heverlee Leuven (K) vs Czarni Sosnowiec (K)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="C10" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D10" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="E10" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="F10" t="n">
-        <v>2.11</v>
+        <v>2.55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -699,23 +699,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Portsmouth vs Derby County</t>
+          <t>Real Madrid (K) vs Ajax (K)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="C11" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>3.7</v>
+        <v>13.25</v>
       </c>
       <c r="E11" t="n">
-        <v>1.98</v>
+        <v>1.28</v>
       </c>
       <c r="F11" t="n">
-        <v>1.78</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -726,23 +726,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lincoln City vs Blackburn</t>
+          <t>Juventus (K) vs St. Polten (K)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.23</v>
+        <v>1.12</v>
       </c>
       <c r="C12" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9</v>
+        <v>1.41</v>
       </c>
       <c r="F12" t="n">
-        <v>1.84</v>
+        <v>2.63</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -753,23 +753,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swansea vs Watford</t>
+          <t>Gintra (K) vs Sturm Graz (K)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.86</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8</v>
+        <v>1.98</v>
       </c>
       <c r="E13" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="F13" t="n">
-        <v>1.87</v>
+        <v>2.23</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -780,23 +780,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Birmingham vs Southampton</t>
+          <t>Slovan Liberec (K) vs Sarajevo (K)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.45</v>
+        <v>1.79</v>
       </c>
       <c r="C14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D14" t="n">
         <v>3.5</v>
       </c>
-      <c r="D14" t="n">
-        <v>2.63</v>
-      </c>
       <c r="E14" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="F14" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -807,23 +807,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Stoke vs Norwich</t>
+          <t>Fortuna Hjorring (K) vs Hajduk Split (K)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.15</v>
+        <v>1.3</v>
       </c>
       <c r="C15" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="F15" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -834,23 +834,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Bradford vs Cambridge Utd</t>
+          <t>AFK Csikszereda Miercurea Ciuc (W) vs Breidablik Kopavogur (K)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.76</v>
+        <v>9.5</v>
       </c>
       <c r="C16" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2</v>
+        <v>1.16</v>
       </c>
       <c r="E16" t="n">
-        <v>1.95</v>
+        <v>1.18</v>
       </c>
       <c r="F16" t="n">
-        <v>1.74</v>
+        <v>4.33</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -861,23 +861,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Peterborough vs Stevenage</t>
+          <t>Rosenborg (K) vs SeaSters Odessa (K)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.4</v>
+        <v>1.08</v>
       </c>
       <c r="C17" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>2.68</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>1.93</v>
+        <v>1.35</v>
       </c>
       <c r="F17" t="n">
-        <v>1.76</v>
+        <v>2.9</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -888,23 +888,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Doncaster vs Notts County</t>
+          <t>Hafnarfjordur (K) vs Apollon Limassol (K)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.16</v>
+        <v>1.62</v>
       </c>
       <c r="C18" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="F18" t="n">
-        <v>1.81</v>
+        <v>2.22</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Leicester City vs Plymouth</t>
+          <t>Brondby (K) vs ZFK Spartak Subotica (K)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="C19" t="n">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>3.4</v>
+        <v>36</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F19" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -942,23 +942,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Bromley vs Leyton Orient</t>
+          <t>Valerenga (K) vs ZNK Radomlje (W)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.5</v>
+        <v>17</v>
       </c>
       <c r="C20" t="n">
-        <v>3.3</v>
+        <v>41</v>
       </c>
       <c r="D20" t="n">
-        <v>2.58</v>
+        <v>1.11</v>
       </c>
       <c r="E20" t="n">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="F20" t="n">
-        <v>1.81</v>
+        <v>5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -969,23 +969,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Huddersfield vs Oxford United</t>
+          <t>Feyenoord (K) vs Anderlecht (K)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="C21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="E21" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="F21" t="n">
-        <v>2.03</v>
+        <v>2.23</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -996,23 +996,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Wycombe vs Sheffield Wednesday</t>
+          <t>QPR vs Cardiff</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="C22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D22" t="n">
         <v>3.5</v>
       </c>
-      <c r="D22" t="n">
-        <v>2.45</v>
-      </c>
       <c r="E22" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="F22" t="n">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1023,23 +1023,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Bristol Rovers vs Colchester</t>
+          <t>West Bromwich vs Charlton</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="C23" t="n">
         <v>3.6</v>
       </c>
       <c r="D23" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="E23" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="F23" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1050,23 +1050,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Chesterfield vs Gillingham</t>
+          <t>Millwall vs Wrexham</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6</v>
+        <v>2.23</v>
       </c>
       <c r="C24" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>3.05</v>
       </c>
       <c r="E24" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="F24" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1077,23 +1077,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Fleetwood Town vs Oldham</t>
+          <t>Burnley vs Middlesbrough</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="C25" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D25" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="E25" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="F25" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1104,23 +1104,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Accrington vs Grimsby</t>
+          <t>Wigan vs MK Dons</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="C26" t="n">
         <v>3.4</v>
       </c>
-      <c r="C26" t="n">
-        <v>3.5</v>
-      </c>
       <c r="D26" t="n">
-        <v>2.02</v>
+        <v>2.73</v>
       </c>
       <c r="E26" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="F26" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1131,23 +1131,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Salford vs Newport</t>
+          <t>Burton vs AFC Wimbledon</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="C27" t="n">
-        <v>4.25</v>
+        <v>3.3</v>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="E27" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="F27" t="n">
-        <v>2.18</v>
+        <v>1.68</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1158,23 +1158,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Swindon vs Port Vale</t>
+          <t>Luton vs Stockport</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="C28" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F28" t="n">
         <v>2.14</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1.86</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1185,23 +1185,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Tranmere vs Rotherham</t>
+          <t>Barnsley vs Blackpool</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="C29" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D29" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="E29" t="n">
-        <v>2.02</v>
+        <v>1.66</v>
       </c>
       <c r="F29" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1212,23 +1212,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Northampton vs Crawley</t>
+          <t>Reading vs Mansfield</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="C30" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D30" t="n">
-        <v>4.2</v>
+        <v>3.15</v>
       </c>
       <c r="E30" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="F30" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1239,23 +1239,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Exeter vs Barnet</t>
+          <t>Preston U21 vs Wolverhampton U21</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="C31" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D31" t="n">
-        <v>1.91</v>
+        <v>2.18</v>
       </c>
       <c r="E31" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="F31" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1266,23 +1266,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Crewe vs Walsall</t>
+          <t>Sabadell vs FC Barcelona B</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.27</v>
+        <v>1.43</v>
       </c>
       <c r="C32" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="D32" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="E32" t="n">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="F32" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1293,23 +1293,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rochdale vs Shrewsbury</t>
+          <t>Sassuolo vs Frosinone</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.18</v>
+        <v>1.81</v>
       </c>
       <c r="C33" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D33" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="E33" t="n">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="F33" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1320,23 +1320,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cheltenham vs York</t>
+          <t>Udinese vs Venezia</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3.6</v>
+        <v>1.94</v>
       </c>
       <c r="C34" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E34" t="n">
         <v>1.91</v>
       </c>
-      <c r="E34" t="n">
-        <v>1.79</v>
-      </c>
       <c r="F34" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1347,23 +1347,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Halifax vs Hartlepool</t>
+          <t>Guidonia Montecelio vs Latina</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="C35" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="D35" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="E35" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="F35" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1374,23 +1374,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Leek Town vs Warrington Town</t>
+          <t>Gubbio vs Vis Pesaro</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>2.5</v>
       </c>
       <c r="C36" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D36" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="E36" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="F36" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1401,23 +1401,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Hull City U21 vs Swansea City U21</t>
+          <t>Union Brescia vs Giana Erminio</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.55</v>
+        <v>1.51</v>
       </c>
       <c r="C37" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D37" t="n">
-        <v>2.18</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>1.28</v>
+        <v>1.93</v>
       </c>
       <c r="F37" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1428,23 +1428,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Charlton Athletic U21 vs Wigan U21</t>
+          <t>Arzignano Valchiampo vs Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="C38" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="D38" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="E38" t="n">
-        <v>1.16</v>
+        <v>2.12</v>
       </c>
       <c r="F38" t="n">
-        <v>4.15</v>
+        <v>1.64</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1455,23 +1455,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Huddersfield U21 vs Queens Park Rangers U21</t>
+          <t>Carpi vs Pro Vercelli</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.68</v>
+        <v>2.27</v>
       </c>
       <c r="C39" t="n">
-        <v>4.25</v>
+        <v>3.05</v>
       </c>
       <c r="D39" t="n">
-        <v>3.5</v>
+        <v>2.77</v>
       </c>
       <c r="E39" t="n">
-        <v>1.2</v>
+        <v>2.14</v>
       </c>
       <c r="F39" t="n">
-        <v>3.7</v>
+        <v>1.62</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1482,23 +1482,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Bristol City U21 vs Sheffield Utd U21</t>
+          <t>Sorrento vs Cosenza</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="C40" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="D40" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="E40" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="F40" t="n">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1509,23 +1509,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fleetwood Town U21 vs Millwall U21</t>
+          <t>Altamura vs Sambenedettese</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2.11</v>
       </c>
       <c r="C41" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="D41" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="E41" t="n">
-        <v>1.28</v>
+        <v>2.34</v>
       </c>
       <c r="F41" t="n">
-        <v>3.1</v>
+        <v>1.51</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1536,23 +1536,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Colchester U21 vs Barnsley U21</t>
+          <t>Spezia vs Vado</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3.3</v>
+        <v>1.58</v>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D42" t="n">
-        <v>1.78</v>
+        <v>4.75</v>
       </c>
       <c r="E42" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="F42" t="n">
-        <v>2.9</v>
+        <v>1.83</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1563,23 +1563,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cardiff U21 vs Sheffield Wednesday U21</t>
+          <t>Catania vs Savoia</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D43" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="E43" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="F43" t="n">
-        <v>2.9</v>
+        <v>1.81</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1590,23 +1590,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Stourbridge vs Leamington</t>
+          <t>VfL Osnabruck vs FC Bayern Münih</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.04</v>
+        <v>31</v>
       </c>
       <c r="C44" t="n">
-        <v>3.4</v>
+        <v>15</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="E44" t="n">
-        <v>1.72</v>
+        <v>1.05</v>
       </c>
       <c r="F44" t="n">
-        <v>1.96</v>
+        <v>7.5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1617,23 +1617,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Parma vs Cremonese</t>
+          <t>SC Wiedenbruck vs Borussia Monchengladbach II</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="C45" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="D45" t="n">
-        <v>3.4</v>
+        <v>1.87</v>
       </c>
       <c r="E45" t="n">
-        <v>2.26</v>
+        <v>1.53</v>
       </c>
       <c r="F45" t="n">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1644,23 +1644,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Torino vs Monza</t>
+          <t>Carl Zeiss Jena vs VSG Altglienicke</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="C46" t="n">
         <v>3.5</v>
       </c>
       <c r="D46" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="E46" t="n">
-        <v>2.05</v>
+        <v>1.64</v>
       </c>
       <c r="F46" t="n">
-        <v>1.71</v>
+        <v>2.11</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1671,23 +1671,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Citta Di Campobasso vs Scafatese</t>
+          <t>HSC Hannover vs Phoenix Luebeck</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.86</v>
+        <v>3.3</v>
       </c>
       <c r="C47" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D47" t="n">
-        <v>3.5</v>
+        <v>1.84</v>
       </c>
       <c r="E47" t="n">
-        <v>1.96</v>
+        <v>1.43</v>
       </c>
       <c r="F47" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1698,23 +1698,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bari vs Picerno</t>
+          <t>Benfica U23 vs Academico Viseu U23</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="C48" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D48" t="n">
-        <v>4.75</v>
+        <v>2.31</v>
       </c>
       <c r="E48" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="F48" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1725,23 +1725,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ravenna vs Forli</t>
+          <t>Groene Ster vs VV Heerjansdam</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="C49" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="E49" t="n">
-        <v>1.95</v>
+        <v>1.32</v>
       </c>
       <c r="F49" t="n">
-        <v>1.76</v>
+        <v>3.05</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1752,23 +1752,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Potenza vs Monopoli</t>
+          <t>VV Sparta Nijkerk vs SV Venray</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.27</v>
+        <v>1.22</v>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D50" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
       <c r="E50" t="n">
-        <v>2.23</v>
+        <v>1.18</v>
       </c>
       <c r="F50" t="n">
-        <v>1.55</v>
+        <v>4.33</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1779,23 +1779,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Hamburg Eimsbutteler BC vs Borussia Dortmund</t>
+          <t>Staphorst vs VV UNA</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>41</v>
+        <v>2.12</v>
       </c>
       <c r="C51" t="n">
-        <v>23</v>
+        <v>3.7</v>
       </c>
       <c r="D51" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="E51" t="n">
         <v>1.47</v>
       </c>
       <c r="F51" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1806,23 +1806,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BV Borussia 09 Dortmund II vs FC Schalke 04 II</t>
+          <t>USV Hercules vs EVV Echt</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="C52" t="n">
         <v>3.8</v>
       </c>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="E52" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1833,23 +1833,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FC Bocholt 1900 vs Bonner SC</t>
+          <t>VV Dongen vs JOS/Watergraafsmeer</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="C53" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="D53" t="n">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="E53" t="n">
-        <v>1.58</v>
+        <v>1.3</v>
       </c>
       <c r="F53" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -1860,23 +1860,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gil Vicente FC U23 vs Rio Ave U23</t>
+          <t>Tot Ons Genoegen Berkel vs VV Katwijk</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="C54" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="D54" t="n">
-        <v>2.26</v>
+        <v>1.45</v>
       </c>
       <c r="E54" t="n">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="F54" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -1887,23 +1887,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Uniao de Leiria U23 vs Maritimo U23</t>
+          <t>VV Hoogeveen vs SV Zwaluwen Wierden</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="C55" t="n">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="D55" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="E55" t="n">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="F55" t="n">
-        <v>1.81</v>
+        <v>3</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FC Felgueiras 1932 U23 vs Estoril U23</t>
+          <t>Ferro Carril Oeste Reserves vs Estudiantes La Plata Reserves</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="C56" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D56" t="n">
-        <v>2.36</v>
+        <v>1.85</v>
       </c>
       <c r="E56" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="F56" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -1941,20 +1941,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Estrela Da Amadora U23 vs Sporting Lisboa U23</t>
+          <t>Estudiantes Rio Cuarto Reserves vs San Martin de San Juan Reserves</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="C57" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="D57" t="n">
-        <v>2.18</v>
+        <v>4.15</v>
       </c>
       <c r="E57" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="F57" t="n">
         <v>1.81</v>
@@ -1968,23 +1968,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Penafiel U23 vs Leixoes U23</t>
+          <t>Newells Old Boys Reserves vs Deportivo Riestra Reserves</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="C58" t="n">
         <v>3.2</v>
       </c>
       <c r="D58" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="E58" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="F58" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -1995,23 +1995,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sportlust '46 vs Blauw Geel 38</t>
+          <t>Ca Independiente Reserves vs Ca Platense Reserves</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.03</v>
+        <v>1.51</v>
       </c>
       <c r="C59" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="E59" t="n">
-        <v>1.55</v>
+        <v>1.94</v>
       </c>
       <c r="F59" t="n">
-        <v>2.27</v>
+        <v>1.74</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2022,23 +2022,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ADO '20 Heemskerk vs Excelsior Maassluis</t>
+          <t>Godoy Cruz Reserves vs Tigre Reserves</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="C60" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="D60" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="E60" t="n">
-        <v>1.64</v>
+        <v>2.14</v>
       </c>
       <c r="F60" t="n">
-        <v>2.09</v>
+        <v>1.6</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2049,23 +2049,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SC Genemuiden vs FC Lisse</t>
+          <t>Atletico Tucuman Reserves vs San Lorenzo Reserves</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="C61" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="D61" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="E61" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="F61" t="n">
-        <v>2.26</v>
+        <v>1.68</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2076,23 +2076,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Achilles Veen vs SV Poortugaal</t>
+          <t>El Porvenir Reserves vs Estrella del Sur Reserves</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.81</v>
+        <v>2.23</v>
       </c>
       <c r="C62" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="E62" t="n">
-        <v>1.43</v>
+        <v>2.23</v>
       </c>
       <c r="F62" t="n">
-        <v>2.59</v>
+        <v>1.57</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2103,23 +2103,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Harkemase Boys vs Excelsior '31 FC</t>
+          <t>Argentino de Rosario Reserves vs Deportivo Espanol Reserves</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2.25</v>
+        <v>3.05</v>
       </c>
       <c r="C63" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D63" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="F63" t="n">
-        <v>2.27</v>
+        <v>2.03</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2130,23 +2130,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AFC '34 Alkmaar vs VV Scherpenzeel</t>
+          <t>Villa Dalmine Reserves vs Real Pilar Reserves</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3.6</v>
+        <v>2.73</v>
       </c>
       <c r="C64" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D64" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="E64" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="F64" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2157,23 +2157,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Primeiro de Agosto vs G.D. Interclube</t>
+          <t>CA Ituzaingo Reserves vs UAI Urquiza Reserves</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1.93</v>
+        <v>3.8</v>
       </c>
       <c r="C65" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="D65" t="n">
-        <v>4</v>
+        <v>1.74</v>
       </c>
       <c r="E65" t="n">
-        <v>2.77</v>
+        <v>1.78</v>
       </c>
       <c r="F65" t="n">
-        <v>1.35</v>
+        <v>1.92</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2184,23 +2184,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lanus Reserves vs CA Belgrano Cordoba Reserves</t>
+          <t>Arsenal De Sarandi Reserves vs Villa San Carlos Reserves</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="C66" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D66" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="E66" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="F66" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2211,23 +2211,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Gimnasia La Plata Reserves vs CA River Plate Reserves</t>
+          <t>Deportivo Armenio Reserves vs CS Dock Sud Reserves</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3.3</v>
+        <v>2.68</v>
       </c>
       <c r="C67" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="D67" t="n">
-        <v>1.95</v>
+        <v>2.31</v>
       </c>
       <c r="E67" t="n">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="F67" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2238,23 +2238,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Union Santa Fe Reserves vs Velez Sarsfield Reserves</t>
+          <t>CA Brown de Adrogue Reserves vs Deportivo Merlo Reserves</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="C68" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="D68" t="n">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="E68" t="n">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="F68" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2265,23 +2265,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Argentinos Juniors Reserves vs CA Sarmiento Reserves</t>
+          <t>Flandria Reserves vs Club Comunicaciones Reserves</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="C69" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>3.7</v>
+        <v>2.34</v>
       </c>
       <c r="E69" t="n">
-        <v>2.31</v>
+        <v>2.18</v>
       </c>
       <c r="F69" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2292,23 +2292,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Atletico Rafaela Reserves vs Colon Reserves</t>
+          <t>Club Atletico Mitre Reserves vs Chacarita Juniors Reserves</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2.23</v>
+        <v>3.3</v>
       </c>
       <c r="C70" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="D70" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="E70" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="F70" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2319,23 +2319,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CA Aldosivi Reserves vs Racing Club De Avellaneda Reserves</t>
+          <t>CA San Telmo Reserves vs Acassuso Reserves</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2.45</v>
+        <v>1.76</v>
       </c>
       <c r="C71" t="n">
         <v>3.15</v>
       </c>
       <c r="D71" t="n">
-        <v>2.5</v>
+        <v>3.8</v>
       </c>
       <c r="E71" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="F71" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2346,23 +2346,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Club Sportivo Barracas Reserves vs CA Atlas Reserves</t>
+          <t>Ferrocarril Midland Reserves vs Talleres Remedios Reserves</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.28</v>
+        <v>2.4</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="D72" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="E72" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="F72" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2373,23 +2373,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Victoriano Arenas Reserves vs Sacachispas Reserves</t>
+          <t>Port Darwin vs Casuarina</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4.5</v>
+        <v>1.79</v>
       </c>
       <c r="C73" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="D73" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="E73" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="F73" t="n">
-        <v>2.18</v>
+        <v>4.25</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2400,23 +2400,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Puerto Nuevo Reserves vs Deportivo Muniz Reserves</t>
+          <t>Sutherland Sharks vs Manly United</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.27</v>
+        <v>2.27</v>
       </c>
       <c r="C74" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="D74" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="E74" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="F74" t="n">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2427,23 +2427,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Defensores de Cambaceres Reserves vs CA Claypole Reserves</t>
+          <t>Marconi Stallions vs Ghfa Spirit</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2.58</v>
+        <v>1.87</v>
       </c>
       <c r="C75" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D75" t="n">
-        <v>2.33</v>
+        <v>3.6</v>
       </c>
       <c r="E75" t="n">
         <v>1.87</v>
       </c>
       <c r="F75" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2454,23 +2454,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Leones de Rosario Reserves vs Central Ballester Reserves</t>
+          <t>Austria Wien vs WSG Tirol</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.28</v>
+        <v>1.9</v>
       </c>
       <c r="C76" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="D76" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="E76" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="F76" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2481,23 +2481,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Excursionistas Reserves vs Deportivo Liniers Reserves</t>
+          <t>RB Salzburg vs Rapid Wien</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="C77" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D77" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="E77" t="n">
-        <v>2.25</v>
+        <v>1.43</v>
       </c>
       <c r="F77" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2508,23 +2508,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Banfield (K) vs Ferro Carril Oeste (K)</t>
+          <t>Malkiya Club vs Al-Najma Manama</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2.35</v>
+        <v>3.15</v>
       </c>
       <c r="C78" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="D78" t="n">
-        <v>2.77</v>
+        <v>2.1</v>
       </c>
       <c r="E78" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="F78" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2535,23 +2535,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Wolfsberger vs LASK Linz</t>
+          <t>East Riffa vs Sitra</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="C79" t="n">
-        <v>4.33</v>
+        <v>3.15</v>
       </c>
       <c r="D79" t="n">
-        <v>1.5</v>
+        <v>2.04</v>
       </c>
       <c r="E79" t="n">
-        <v>1.43</v>
+        <v>2.16</v>
       </c>
       <c r="F79" t="n">
-        <v>2.58</v>
+        <v>1.6</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2562,23 +2562,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SV Horn vs SC ESV Parndorf 1919</t>
+          <t>Sint-Truiden vs Royale Union SG</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="C80" t="n">
         <v>3.5</v>
       </c>
       <c r="D80" t="n">
-        <v>2.27</v>
+        <v>1.96</v>
       </c>
       <c r="E80" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="F80" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2589,23 +2589,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Deutschlandsberger SC vs Gleisdorf</t>
+          <t>FC Flenu vs RCS Onhaye</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D81" t="n">
-        <v>4.5</v>
+        <v>2.73</v>
       </c>
       <c r="E81" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="F81" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2616,23 +2616,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SV Lafnitz vs SC Kalsdorf</t>
+          <t>ML Vitebsk vs Belshina Bobruisk</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2.8</v>
+        <v>1.14</v>
       </c>
       <c r="C82" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E82" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="F82" t="n">
-        <v>2.22</v>
+        <v>2.77</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2643,23 +2643,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sloga Doboj vs NK Celik Zenica</t>
+          <t>Dinamo Minsk vs Naftan Novopolotsk</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1.87</v>
+        <v>1.16</v>
       </c>
       <c r="C83" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="D83" t="n">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="E83" t="n">
-        <v>2.22</v>
+        <v>1.43</v>
       </c>
       <c r="F83" t="n">
-        <v>1.58</v>
+        <v>2.55</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2670,23 +2670,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Zrinjski Mostar vs FK BSK Banja Luka</t>
+          <t>GV Club Deportivo San Jose de Oruro vs Club Bolivar</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D84" t="n">
-        <v>11</v>
+        <v>1.58</v>
       </c>
       <c r="E84" t="n">
-        <v>1.64</v>
+        <v>1.38</v>
       </c>
       <c r="F84" t="n">
-        <v>2.1</v>
+        <v>2.73</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -2697,23 +2697,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>APAFUT Caxias Do Sul RS vs Gremio Esportivo Brasil RS</t>
+          <t>Velez Mostar vs Radnik Bijeljina</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>3.05</v>
+        <v>1.8</v>
       </c>
       <c r="C85" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="D85" t="n">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="E85" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="F85" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -2724,23 +2724,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Hebar Pazardzhik vs Fratria</t>
+          <t>NK Siroki Brijeg vs Sarajevo</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2.73</v>
+        <v>3.3</v>
       </c>
       <c r="C86" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="D86" t="n">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="E86" t="n">
-        <v>1.96</v>
+        <v>2.31</v>
       </c>
       <c r="F86" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -2751,23 +2751,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sigma Olomouc U19 vs Sparta Prague U19</t>
+          <t>Borac Banjaluka vs FK Zeljeznicar Sarajevo</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2.16</v>
+        <v>1.35</v>
       </c>
       <c r="C87" t="n">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="D87" t="n">
-        <v>2.45</v>
+        <v>7</v>
       </c>
       <c r="E87" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="F87" t="n">
-        <v>3.5</v>
+        <v>1.92</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -2778,23 +2778,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Beijing Guoan vs Lanzhou Longyuan Athletic</t>
+          <t>FK Slavija Sarajevo vs Sutjeska Foca</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="C88" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="D88" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="E88" t="n">
-        <v>1.33</v>
+        <v>1.81</v>
       </c>
       <c r="F88" t="n">
-        <v>3.05</v>
+        <v>1.86</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -2805,23 +2805,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Shandong Luneng Taishan vs Shanghai Port</t>
+          <t>FK Romanija Pale vs FK Omarska</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2.27</v>
+        <v>1.57</v>
       </c>
       <c r="C89" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D89" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="E89" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="F89" t="n">
-        <v>2.9</v>
+        <v>1.99</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -2832,23 +2832,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Dalian Young Boy vs Shanghai Shenhua</t>
+          <t>Velez Nevesinje vs FK Drina Zvornik</t>
         </is>
       </c>
       <c r="B90" t="n">
         <v>2.63</v>
       </c>
       <c r="C90" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D90" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="E90" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="F90" t="n">
-        <v>2.7</v>
+        <v>2.08</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -2859,23 +2859,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IF Lyseng vs AC Horsens</t>
+          <t>Fk Majevica Lopare vs Kozara</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>23</v>
+        <v>3.15</v>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="D91" t="n">
-        <v>1.06</v>
+        <v>2.03</v>
       </c>
       <c r="E91" t="n">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
       <c r="F91" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -2886,23 +2886,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Nordsjaelland (K) vs Kolding IF (K)</t>
+          <t>Retro FC Brasil U20 vs Atletico Torres PE U20</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="C92" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D92" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E92" t="n">
-        <v>1.22</v>
+        <v>1.83</v>
       </c>
       <c r="F92" t="n">
-        <v>3.6</v>
+        <v>1.85</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -2913,23 +2913,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KPV Akatemia vs Sporting Kristina</t>
+          <t>Olaria RJ U20 vs Perolas Negras U20</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="D93" t="n">
-        <v>2.03</v>
+        <v>3.3</v>
       </c>
       <c r="E93" t="n">
-        <v>1.25</v>
+        <v>2.16</v>
       </c>
       <c r="F93" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -2940,23 +2940,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Haka Juniors vs Ylojarvi United</t>
+          <t>America RJ U20 vs Resende RJ U20</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2.31</v>
+        <v>2.08</v>
       </c>
       <c r="C94" t="n">
-        <v>4.15</v>
+        <v>3.15</v>
       </c>
       <c r="D94" t="n">
-        <v>2.27</v>
+        <v>3.15</v>
       </c>
       <c r="E94" t="n">
-        <v>1.14</v>
+        <v>2.14</v>
       </c>
       <c r="F94" t="n">
-        <v>4.5</v>
+        <v>1.62</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -2967,23 +2967,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SalPa II vs EuPa</t>
+          <t>Sampaio Correa RJ vs Nova Iguacu FC</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3.3</v>
+        <v>2.26</v>
       </c>
       <c r="C95" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="D95" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="E95" t="n">
-        <v>1.43</v>
+        <v>2.18</v>
       </c>
       <c r="F95" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -2994,23 +2994,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Durban City FC vs Stellenbosch</t>
+          <t>Madureira RJ vs Boavista SC/RJ</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="C96" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D96" t="n">
         <v>3</v>
       </c>
-      <c r="D96" t="n">
-        <v>2.6</v>
-      </c>
       <c r="E96" t="n">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="F96" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3021,23 +3021,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Kruger United vs Orlando Pirates</t>
+          <t>Slavia Sofia vs Levski Sofia</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="C97" t="n">
         <v>4.5</v>
       </c>
       <c r="D97" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="E97" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="F97" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3048,23 +3048,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Gol Gohar vs Aluminium Arak</t>
+          <t>Psfc Chernomoretz Burgas vs Ludogorets II</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="C98" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="D98" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="E98" t="n">
-        <v>2.8</v>
+        <v>1.98</v>
       </c>
       <c r="F98" t="n">
-        <v>1.35</v>
+        <v>1.72</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3075,23 +3075,23 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan vs Chadormalou</t>
+          <t>Marek Dupnica vs OFC Nesebar</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2.9</v>
+        <v>1.66</v>
       </c>
       <c r="C99" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="D99" t="n">
-        <v>2.31</v>
+        <v>4.5</v>
       </c>
       <c r="E99" t="n">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="F99" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3102,23 +3102,23 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin vs Tractor Sazi FC</t>
+          <t>Rilski Sportist vs Sportist Svoge</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>6</v>
+        <v>1.62</v>
       </c>
       <c r="C100" t="n">
         <v>3.4</v>
       </c>
       <c r="D100" t="n">
-        <v>1.51</v>
+        <v>4.75</v>
       </c>
       <c r="E100" t="n">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="F100" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3129,23 +3129,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Kilbarrack United vs St Francis FC</t>
+          <t>Yantra Gabrovo vs Pirin Blagoevgrad</t>
         </is>
       </c>
       <c r="B101" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C101" t="n">
+        <v>6</v>
+      </c>
+      <c r="D101" t="n">
+        <v>12</v>
+      </c>
+      <c r="E101" t="n">
         <v>1.38</v>
       </c>
-      <c r="C101" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D101" t="n">
-        <v>6</v>
-      </c>
-      <c r="E101" t="n">
-        <v>1.45</v>
-      </c>
       <c r="F101" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3156,23 +3156,23 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Wayside Celtic FC vs Montpelier FC</t>
+          <t>Zbrojovka Brno B vs FC Vsetin</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="C102" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="D102" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="E102" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="F102" t="n">
-        <v>1.45</v>
+        <v>1.66</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3183,23 +3183,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Tolka Rovers AFC vs Killester United</t>
+          <t>Fk Hodonin vs SK Sigma Olomouc 2</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="C103" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="D103" t="n">
-        <v>2.31</v>
+        <v>1.79</v>
       </c>
       <c r="E103" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="F103" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3210,23 +3210,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Stranraer vs Celtic II</t>
+          <t>MFK Vitkovice vs Unicov</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="C104" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D104" t="n">
-        <v>3.1</v>
+        <v>1.99</v>
       </c>
       <c r="E104" t="n">
-        <v>1.45</v>
+        <v>1.74</v>
       </c>
       <c r="F104" t="n">
-        <v>1.43</v>
+        <v>1.96</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3237,23 +3237,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Hapoel Hod Hasharon Irony vs Beitar Petah Tikva</t>
+          <t>MFK Karvina B vs Frydek Mistek</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1.47</v>
+        <v>3.28</v>
       </c>
       <c r="C105" t="n">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>1.87</v>
       </c>
       <c r="E105" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="F105" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3264,23 +3264,23 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Beitar Haifa Yakov vs Hapoel Daliyat Karmel</t>
+          <t>FK Apos Blansko vs Polanka</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="C106" t="n">
         <v>3.6</v>
       </c>
       <c r="D106" t="n">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="E106" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="F106" t="n">
-        <v>2.45</v>
+        <v>2.22</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3291,23 +3291,23 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Maccabi Ironi Amishav vs Ironi Beit Dagan</t>
+          <t>Fc Slovacko B vs SFK Vrchovina</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="C107" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D107" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="E107" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="F107" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3318,23 +3318,23 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Helsingborgs IF vs Orebro SK</t>
+          <t>Zlin B vs Uhersky Brod</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="C108" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D108" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="E108" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="F108" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3345,23 +3345,23 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Zurich vs Young Boys</t>
+          <t>SK Artis Brno II vs Mfk Havirov</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>4.5</v>
+        <v>1.22</v>
       </c>
       <c r="C109" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="D109" t="n">
-        <v>1.55</v>
+        <v>8</v>
       </c>
       <c r="E109" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="F109" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3372,23 +3372,23 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Stade Nyonnais vs Winterthur</t>
+          <t>SK Hranice vs Hlubina</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="C110" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D110" t="n">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="E110" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="F110" t="n">
-        <v>1.47</v>
+        <v>2.31</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3399,23 +3399,23 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>FC Rapperswil Jona vs SC Kriens</t>
+          <t>Benesov vs Sparta Prague B</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2.39</v>
+        <v>3.7</v>
       </c>
       <c r="C111" t="n">
         <v>3.7</v>
       </c>
       <c r="D111" t="n">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="E111" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="F111" t="n">
-        <v>2.8</v>
+        <v>2.22</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3426,23 +3426,23 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Neuchatel Xamax FC vs Yverdon-Sports</t>
+          <t>Povltavska FA vs TJ Jiskra Domazlice</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="C112" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="D112" t="n">
-        <v>2.36</v>
+        <v>1.4</v>
       </c>
       <c r="E112" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="F112" t="n">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3453,23 +3453,23 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FC Stade Lausanne Ouchy vs Etoile Carouge FC</t>
+          <t>FK Komarov vs SK Senco Doubravka</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="C113" t="n">
         <v>3.8</v>
       </c>
       <c r="D113" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="E113" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="F113" t="n">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3480,23 +3480,23 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>FC Collex Bossy vs Signal FC Bernex-Confignon</t>
+          <t>Zbrojovka Brno vs Hradec Kralove</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="C114" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D114" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="E114" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="F114" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -3507,23 +3507,23 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KR Reykjavik vs Vikingur Reykjavik</t>
+          <t>Bohemians 1905 vs Jablonec</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
       <c r="C115" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>2.59</v>
       </c>
       <c r="E115" t="n">
-        <v>1.13</v>
+        <v>1.9</v>
       </c>
       <c r="F115" t="n">
-        <v>5</v>
+        <v>1.81</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -3534,23 +3534,23 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Al Sadd vs Al-Gharafa</t>
+          <t>Yunnan Yukun vs Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="C116" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="D116" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="E116" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="F116" t="n">
-        <v>2.55</v>
+        <v>2.27</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3561,23 +3561,23 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Al-Shamal vs Al-Rayyan</t>
+          <t>Aarhus vs Midtjylland</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="C117" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D117" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="E117" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="F117" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -3588,23 +3588,23 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kyzylzhar (K) vs Astana (K)</t>
+          <t>Crystal Palace U21 vs Paris Saint-Germain U21</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.05</v>
+        <v>2.8</v>
       </c>
       <c r="C118" t="n">
-        <v>11</v>
+        <v>3.6</v>
       </c>
       <c r="D118" t="n">
-        <v>19</v>
+        <v>2.05</v>
       </c>
       <c r="E118" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="F118" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -3615,23 +3615,23 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Orsomarso (K) vs Deportivo Cali (K)</t>
+          <t>Aston Villa U21 vs Broendby IF U21</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>6</v>
+        <v>1.76</v>
       </c>
       <c r="C119" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D119" t="n">
-        <v>1.45</v>
+        <v>3.4</v>
       </c>
       <c r="E119" t="n">
-        <v>2.04</v>
+        <v>1.32</v>
       </c>
       <c r="F119" t="n">
-        <v>1.68</v>
+        <v>2.9</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -3642,23 +3642,23 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Envigado vs Union Magdalena Santa Marta</t>
+          <t>Macara vs Manta FC</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>2.35</v>
+        <v>1.45</v>
       </c>
       <c r="C120" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="D120" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="E120" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="F120" t="n">
-        <v>1.47</v>
+        <v>1.74</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -3669,23 +3669,23 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Kazma vs Al Sahel Abu Halifa</t>
+          <t>Flora Tallinn vs JK Tammeka Tartu</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="C121" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="D121" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="E121" t="n">
-        <v>2.06</v>
+        <v>1.38</v>
       </c>
       <c r="F121" t="n">
-        <v>1.66</v>
+        <v>2.73</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -3696,23 +3696,23 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Al Tadamon vs Al-Salmiyah</t>
+          <t>Harju JK Laagri (K) vs Flora Tallinn (K)</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>4.15</v>
+        <v>12</v>
       </c>
       <c r="C122" t="n">
-        <v>3.4</v>
+        <v>7.5</v>
       </c>
       <c r="D122" t="n">
-        <v>1.68</v>
+        <v>1.11</v>
       </c>
       <c r="E122" t="n">
-        <v>1.95</v>
+        <v>1.18</v>
       </c>
       <c r="F122" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -3723,23 +3723,23 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Ballymacash Rangers vs Ballymena United FC</t>
+          <t>JK Nomme United vs Parnu JK Vaprus</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>8</v>
+        <v>2.16</v>
       </c>
       <c r="C123" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="D123" t="n">
-        <v>1.22</v>
+        <v>2.63</v>
       </c>
       <c r="E123" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="F123" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -3750,24 +3750,20 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Glentoran vs Linfield</t>
+          <t>TPV II vs Fish United</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1.96</v>
+        <v>1.03</v>
       </c>
       <c r="C124" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="D124" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E124" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="F124" t="n">
-        <v>1.83</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
           <t>-</t>
@@ -3777,23 +3773,23 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ballyclare Comrades vs FC Ards</t>
+          <t>EPS vs FC Honka</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="D125" t="n">
         <v>1.51</v>
       </c>
       <c r="E125" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="F125" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -3804,23 +3800,23 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Crusaders FC vs Carrick Rangers</t>
+          <t>HJS vs Ilves Ii</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="C126" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D126" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="E126" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="F126" t="n">
-        <v>2.09</v>
+        <v>2.9</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -3831,23 +3827,23 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Minija Kretinga vs DFK Dainava Alytus</t>
+          <t>Pallo-Iirot Rauma vs AIFK Turku</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1.76</v>
+        <v>2.68</v>
       </c>
       <c r="C127" t="n">
         <v>3.5</v>
       </c>
       <c r="D127" t="n">
-        <v>3.7</v>
+        <v>2.16</v>
       </c>
       <c r="E127" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="F127" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -3858,23 +3854,23 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Brunei Dpmm FC vs Terengganu</t>
+          <t>Narpes Kraft vs FF Jaro II</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3.6</v>
+        <v>1.53</v>
       </c>
       <c r="C128" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D128" t="n">
-        <v>1.76</v>
+        <v>4</v>
       </c>
       <c r="E128" t="n">
-        <v>1.68</v>
+        <v>1.14</v>
       </c>
       <c r="F128" t="n">
-        <v>2.04</v>
+        <v>4.75</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -3885,23 +3881,23 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ghazl Al Mehalla vs ENPPI Club</t>
+          <t>Vps-J vs GBK Kokkola</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2.73</v>
+        <v>2.23</v>
       </c>
       <c r="C129" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="D129" t="n">
-        <v>2.8</v>
+        <v>2.39</v>
       </c>
       <c r="E129" t="n">
-        <v>3.7</v>
+        <v>1.16</v>
       </c>
       <c r="F129" t="n">
-        <v>1.22</v>
+        <v>4.2</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -3912,23 +3908,23 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Talaea El Gaish vs FC Masr (ZED)</t>
+          <t>Jakobstads Bollklubb vs Huima/Urho</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2.73</v>
+        <v>2.09</v>
       </c>
       <c r="C130" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D130" t="n">
         <v>2.68</v>
       </c>
-      <c r="D130" t="n">
-        <v>2.7</v>
-      </c>
       <c r="E130" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="F130" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -3939,23 +3935,23 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Wady Degla vs El Qanah FC</t>
+          <t>Mamelodi Sundowns vs Milford FC</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2.18</v>
+        <v>1.2</v>
       </c>
       <c r="C131" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="D131" t="n">
-        <v>3.3</v>
+        <v>11</v>
       </c>
       <c r="E131" t="n">
-        <v>2.77</v>
+        <v>1.58</v>
       </c>
       <c r="F131" t="n">
-        <v>1.38</v>
+        <v>2.2</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -3966,23 +3962,23 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Baia Pemba vs Ferroviario de Lichinga</t>
+          <t>Cape Town City vs Leicesterford City</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2.4</v>
+        <v>1.58</v>
       </c>
       <c r="C132" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="D132" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="E132" t="n">
-        <v>3</v>
+        <v>2.27</v>
       </c>
       <c r="F132" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -3993,23 +3989,23 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Nordstrand vs Grei</t>
+          <t>FC Samtredia vs Iberia 1999</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1.38</v>
+        <v>4.75</v>
       </c>
       <c r="C133" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="D133" t="n">
-        <v>5</v>
+        <v>1.53</v>
       </c>
       <c r="E133" t="n">
-        <v>1.16</v>
+        <v>1.66</v>
       </c>
       <c r="F133" t="n">
-        <v>4</v>
+        <v>2.07</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4020,23 +4016,23 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Fk Gjovik-Lyn vs Brumunddal</t>
+          <t>HNK Rijeka U19 vs Kustosija U19</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1.03</v>
+        <v>1.86</v>
       </c>
       <c r="C134" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="D134" t="n">
-        <v>23</v>
+        <v>3.15</v>
       </c>
       <c r="E134" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="F134" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4047,23 +4043,23 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Lillestrom (K) vs Bodo/Glimt (K)</t>
+          <t>Nk Rudes U19 vs HNK Hajduk Split U19</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="C135" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="D135" t="n">
-        <v>12</v>
+        <v>2.04</v>
       </c>
       <c r="E135" t="n">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="F135" t="n">
-        <v>3.5</v>
+        <v>1.97</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4074,23 +4070,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Rubio Nu vs Sportivo San Lorenzo</t>
+          <t>NK Varazdin U19 vs NK Radnik Sesvete U19</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="C136" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D136" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="E136" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="F136" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4101,23 +4097,23 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Atletico Grau vs FBC Melgar Arequipa</t>
+          <t>NK Slaven Belupo U19 vs NK Solin U19</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2.73</v>
+        <v>1.55</v>
       </c>
       <c r="C137" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="D137" t="n">
-        <v>2.45</v>
+        <v>4.5</v>
       </c>
       <c r="E137" t="n">
-        <v>2.27</v>
+        <v>1.55</v>
       </c>
       <c r="F137" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4128,23 +4124,23 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Korona Kielce II vs Radomiak Radom</t>
+          <t>NK Trnje U19 vs NK Lokomotiva Zagreb U19</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="C138" t="n">
-        <v>6</v>
+        <v>4.33</v>
       </c>
       <c r="D138" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="E138" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="F138" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4155,23 +4151,23 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NKP Podhale vs Pogon Grodzisk Mazowiecki</t>
+          <t>Vukovar 1991 vs GNK Dinamo Zagreb U21</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2.63</v>
+        <v>1.66</v>
       </c>
       <c r="C139" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D139" t="n">
-        <v>2.26</v>
+        <v>4.5</v>
       </c>
       <c r="E139" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="F139" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4182,23 +4178,23 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Kluczevia Stargard vs Pogon Siedlce</t>
+          <t>NK Mladost Zdralovi vs NK Radnik Sesvete</t>
         </is>
       </c>
       <c r="B140" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="C140" t="n">
         <v>3.2</v>
       </c>
-      <c r="C140" t="n">
-        <v>3.3</v>
-      </c>
       <c r="D140" t="n">
-        <v>1.97</v>
+        <v>2.9</v>
       </c>
       <c r="E140" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="F140" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4209,23 +4205,23 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Chemik Bydgoszcz vs Piast Gliwice</t>
+          <t>NK Dugopolje vs Karlovac</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>13.25</v>
+        <v>1.86</v>
       </c>
       <c r="C141" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="D141" t="n">
-        <v>1.12</v>
+        <v>3.7</v>
       </c>
       <c r="E141" t="n">
-        <v>1.33</v>
+        <v>2.04</v>
       </c>
       <c r="F141" t="n">
-        <v>2.9</v>
+        <v>1.68</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4236,23 +4232,23 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Siarka Tarnobrzeg vs Zaglebie Lubin</t>
+          <t>NK Jadran LP vs NK Dubrava Zagreb</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>7.5</v>
+        <v>1.72</v>
       </c>
       <c r="C142" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="D142" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="E142" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="F142" t="n">
-        <v>2.26</v>
+        <v>1.76</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -4263,23 +4259,23 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Wisla Plock II vs Puszcza Niepołomice</t>
+          <t>NK Croatia Zmijavci vs BSK Bijelo Brdo</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>5</v>
+        <v>1.94</v>
       </c>
       <c r="C143" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="D143" t="n">
-        <v>1.47</v>
+        <v>3.6</v>
       </c>
       <c r="E143" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="F143" t="n">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -4290,23 +4286,23 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Odra Opole vs Wisla Krakow</t>
+          <t>Opatija vs NK Hrvace</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>4.2</v>
+        <v>1.83</v>
       </c>
       <c r="C144" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D144" t="n">
-        <v>1.66</v>
+        <v>3.8</v>
       </c>
       <c r="E144" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="F144" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4317,23 +4313,23 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MKS Kluczbork vs Lechia Gdansk</t>
+          <t>HNK Cibalia Vinkovci vs Orijent 1919</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>5</v>
+        <v>2.05</v>
       </c>
       <c r="C145" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="D145" t="n">
-        <v>1.51</v>
+        <v>3.15</v>
       </c>
       <c r="E145" t="n">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="F145" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4344,23 +4340,23 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Stal Rzeszow vs Podbeskidzie Bielsko-Biala</t>
+          <t>George Telegraph vs Calcutta Customs</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2.37</v>
+        <v>7.5</v>
       </c>
       <c r="C146" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D146" t="n">
-        <v>2.45</v>
+        <v>1.27</v>
       </c>
       <c r="E146" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="F146" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -4371,23 +4367,23 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Polonia Sroda Wielkopolska vs Sandecja Nowy Sacz</t>
+          <t>United Kolkata vs East Bengal II</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="C147" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="D147" t="n">
-        <v>2.26</v>
+        <v>1.47</v>
       </c>
       <c r="E147" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="F147" t="n">
-        <v>2.16</v>
+        <v>2.73</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4398,23 +4394,23 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Wigry Suwalki vs Termalica BB Nieciecza</t>
+          <t>Kanan FC vs Aizawl Fc</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3.8</v>
+        <v>19</v>
       </c>
       <c r="C148" t="n">
-        <v>3.6</v>
+        <v>8.5</v>
       </c>
       <c r="D148" t="n">
-        <v>1.75</v>
+        <v>1.06</v>
       </c>
       <c r="E148" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F148" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -4425,23 +4421,23 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Motor Lublin vs Legia Warszawa</t>
+          <t>Nongkseh SCC vs Mawlai SC</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>4.15</v>
+        <v>2.37</v>
       </c>
       <c r="C149" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D149" t="n">
-        <v>1.66</v>
+        <v>2.45</v>
       </c>
       <c r="E149" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="F149" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -4452,23 +4448,23 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sepsi vs CFR Cluj</t>
+          <t>Malavan vs Nassaji Mazandaran</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2.4</v>
+        <v>2.09</v>
       </c>
       <c r="C150" t="n">
-        <v>3.15</v>
+        <v>2.63</v>
       </c>
       <c r="D150" t="n">
-        <v>2.63</v>
+        <v>3.8</v>
       </c>
       <c r="E150" t="n">
-        <v>2.04</v>
+        <v>3.5</v>
       </c>
       <c r="F150" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -4479,23 +4475,23 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>U Cluj vs Petrolul Ploiesti</t>
+          <t>Zob Ahan vs Paykan</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1.47</v>
+        <v>2.8</v>
       </c>
       <c r="C151" t="n">
-        <v>4</v>
+        <v>2.68</v>
       </c>
       <c r="D151" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="E151" t="n">
-        <v>1.66</v>
+        <v>3.2</v>
       </c>
       <c r="F151" t="n">
-        <v>2.09</v>
+        <v>1.28</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -4506,23 +4502,23 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Chindia Targoviste vs Voluntari</t>
+          <t>Kheybar Khorramabad vs Foolad Khuzestan FC</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="C152" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="D152" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="E152" t="n">
-        <v>1.87</v>
+        <v>2.63</v>
       </c>
       <c r="F152" t="n">
-        <v>1.81</v>
+        <v>1.41</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -4533,23 +4529,23 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Corona Brasov vs Bihor Oradea</t>
+          <t>Esteghlal Tehran vs Perspolis Teheran</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="C153" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="D153" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="E153" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="F153" t="n">
-        <v>1.81</v>
+        <v>1.45</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -4560,23 +4556,23 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>FK Fakel vs Krasnodar</t>
+          <t>Sanat Naft vs Sepahan</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="C154" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D154" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="E154" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="F154" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -4587,23 +4583,23 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Akron Tolyatti vs Lokomotiv Moskova</t>
+          <t>Celtic vs Aberdeen</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3</v>
+        <v>1.22</v>
       </c>
       <c r="C155" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="D155" t="n">
-        <v>2.16</v>
+        <v>9</v>
       </c>
       <c r="E155" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F155" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -4614,23 +4610,23 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Rostov vs CSKA Moskova</t>
+          <t>Kilmarnock vs St Mirren</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="C156" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D156" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="E156" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="F156" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -4641,23 +4637,23 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Teleoptik Zemun vs Vozdovac</t>
+          <t>Motherwell vs Dundee Utd</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>2.6</v>
+        <v>1.99</v>
       </c>
       <c r="C157" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D157" t="n">
-        <v>2.31</v>
+        <v>3.2</v>
       </c>
       <c r="E157" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="F157" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -4668,23 +4664,23 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SK Tomasov vs Inter Bratislava</t>
+          <t>Dundee vs St. Johnstone</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>9.5</v>
+        <v>2.68</v>
       </c>
       <c r="C158" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="D158" t="n">
-        <v>1.18</v>
+        <v>2.39</v>
       </c>
       <c r="E158" t="n">
-        <v>1.32</v>
+        <v>1.8</v>
       </c>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -4695,23 +4691,23 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sampion Celje vs Dravinja</t>
+          <t>Falkirk vs Rangers</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="C159" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="D159" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="E159" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="F159" t="n">
-        <v>2.8</v>
+        <v>2.27</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -4722,23 +4718,23 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>NK Smartno vs NK Rudar Velenje</t>
+          <t>Hapoel Beer-Sheva vs Hapoel Haifa</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>6.5</v>
+        <v>1.43</v>
       </c>
       <c r="C160" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="D160" t="n">
-        <v>1.33</v>
+        <v>5.5</v>
       </c>
       <c r="E160" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="F160" t="n">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -4749,23 +4745,23 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Al Hilal Riyadh vs Al Ahli Jeddah</t>
+          <t>Bk Olympic vs IFK Goteborg</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1.47</v>
+        <v>11</v>
       </c>
       <c r="C161" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="D161" t="n">
-        <v>5.5</v>
+        <v>1.16</v>
       </c>
       <c r="E161" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="F161" t="n">
-        <v>2.45</v>
+        <v>2.9</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -4776,23 +4772,23 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AL Khaleej Saihat U21 vs Al Wehda U21</t>
+          <t>Grasshopper vs St. Gallen</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="C162" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D162" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="E162" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="F162" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -4803,23 +4799,23 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Al-Jeel vs Jeddah Club</t>
+          <t>Thun vs Lausanne</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2.63</v>
+        <v>2.04</v>
       </c>
       <c r="C163" t="n">
-        <v>2.73</v>
+        <v>3.6</v>
       </c>
       <c r="D163" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="E163" t="n">
-        <v>2.1</v>
+        <v>1.58</v>
       </c>
       <c r="F163" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -4830,23 +4826,23 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Al-Orubah vs Al Zulfi FC</t>
+          <t>Luzern vs Vaduz</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2.2</v>
+        <v>1.64</v>
       </c>
       <c r="C164" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="D164" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="E164" t="n">
-        <v>2.04</v>
+        <v>1.3</v>
       </c>
       <c r="F164" t="n">
-        <v>1.68</v>
+        <v>3.05</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -4857,23 +4853,23 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Al Najma (SAUD) vs Al Jabalain</t>
+          <t>Arborg vs Alftanes</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="C165" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>2.06</v>
       </c>
       <c r="E165" t="n">
-        <v>2.04</v>
+        <v>1.22</v>
       </c>
       <c r="F165" t="n">
-        <v>1.66</v>
+        <v>3.7</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -4884,23 +4880,23 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Singida BS vs Namungo</t>
+          <t>Yokohama F Marinos vs Kyoto Purple Sanga</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>1.4</v>
+        <v>2.08</v>
       </c>
       <c r="C166" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D166" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="E166" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="F166" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -4911,21 +4907,23 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>NEC FC Bugolobi vs Lugazi Municipal FC</t>
+          <t>Cerezo Osaka vs Kashiwa Reysol</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1.62</v>
+        <v>3.3</v>
       </c>
       <c r="C167" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="D167" t="n">
-        <v>5</v>
-      </c>
-      <c r="E167" t="inlineStr"/>
+        <v>2.01</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1.72</v>
+      </c>
       <c r="F167" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -4936,23 +4934,23 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Entebbe UPPC FC vs Updf Fc</t>
+          <t>Machida Zelvia vs Kawasaki Frontale</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="C168" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D168" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="E168" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="F168" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -4963,23 +4961,23 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Colon FC vs Centro Atletico Fenix Montevideo</t>
+          <t>Sanfrecce Hiroshima vs Nagoya Grampus Eight</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>2.6</v>
+        <v>1.55</v>
       </c>
       <c r="C169" t="n">
-        <v>2.9</v>
+        <v>4.25</v>
       </c>
       <c r="D169" t="n">
-        <v>2.59</v>
+        <v>4.75</v>
       </c>
       <c r="E169" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F169" t="n">
         <v>2.45</v>
-      </c>
-      <c r="F169" t="n">
-        <v>1.45</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -4990,23 +4988,23 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Boston River Reserves vs CA River Plate Montevideo Reserves</t>
+          <t>Shimizu S-pulse vs FC Tokyo</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1.83</v>
+        <v>4.75</v>
       </c>
       <c r="C170" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="D170" t="n">
-        <v>3.4</v>
+        <v>1.68</v>
       </c>
       <c r="E170" t="n">
-        <v>1.66</v>
+        <v>1.94</v>
       </c>
       <c r="F170" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -5017,23 +5015,23 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Albion Reserves vs Cerro Largo FC Reserves</t>
+          <t>Avispa Fukuoka vs Urawa Red Diamonds</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>2.27</v>
+        <v>2.55</v>
       </c>
       <c r="C171" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D171" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="E171" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="F171" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -5044,25 +5042,2746 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Volos NFC vs Kalamata</t>
+          <t>Mito HollyHock vs Kashima Antlers</t>
         </is>
       </c>
       <c r="B172" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C172" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D172" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Tokyo Verdy 1969 vs Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C173" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D173" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Jef United Ichihara Chiba vs Fagiano Okayama</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C174" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>V-Varen Nagasaki vs Gamba Osaka</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C175" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D175" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F175" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Vanraure Hachnohe vs Tochigi City</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>SC Sagamihara vs Jubilo Iwata</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D177" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Gainare Tottori vs Omiya Ardija</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C178" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D178" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Giravanz Kitakyushu vs Iwaki SC</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Roasso Kumamoto vs Oita Trinita</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>FC Gifu vs Tokushima Vortis</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D181" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Tegevajaro Miyazaki vs Kataller Toyama</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C182" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Kagoshima United vs Consadole Sapporo</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C183" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E183" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F183" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Ehime FC vs Blaublitz Akita</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D184" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E184" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Renofa Yamaguchi vs Fujieda MYFC</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C185" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F185" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>FC Osaka vs Ventforet Kofu</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="C186" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E186" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F186" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>ThespaKusatsu Gunma vs Albirex Niigata</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C187" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F187" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>F.C. Ryukyu vs Yokohama FC</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C188" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F188" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Zweigen Kanazawa vs Imabari</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C189" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D189" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F189" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Nara Club vs Sagan Tosu</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C190" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F190" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Inac Kobe Leonessa (W) vs AC Nagano Parceiro (W)</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C191" t="n">
+        <v>6</v>
+      </c>
+      <c r="D191" t="n">
+        <v>13</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Nairobi United vs Kenya Commercial Bank Nairobi</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C192" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D192" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E192" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia vs Pafos</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D193" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Jeonbuk Hwacheon (K) vs Suwon (K)</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D194" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E194" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Seoul City (K) vs Incheon Hyundai Steel Red Angels (K)</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Sejong Sportstoto (K) vs Gyeongju H&amp;N Power (K)</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D196" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Gangjin Swans (K) vs Mungyeong Sangmu (K)</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C197" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F197" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Ballymoney United (K) vs Strabane Athletic (K)</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C198" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D198" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F198" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Ballyclare Comrades (K) vs Bangor (K)</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C199" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="E199" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F199" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>St. James Swifts (K) vs Greenisland (K)</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C200" t="n">
+        <v>4</v>
+      </c>
+      <c r="D200" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F200" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>BFC Daugava Daugavpils vs Auda</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D201" t="n">
+        <v>2</v>
+      </c>
+      <c r="E201" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>FM Klaipedos vs Vilnius Football Academy</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C202" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D202" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F202" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Sabah FC vs Selangor FC</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D203" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E203" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F203" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Melaka FC vs Penang FC</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D204" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Kedah vs Star City FC</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>4</v>
+      </c>
+      <c r="C205" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E205" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Kelantan WTS vs Negeri Sembilan</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C206" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F206" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Hibernians Paola FC vs Valletta</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Floriana vs Gzira United FC</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C208" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D208" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Tijuana U19 (W) vs Santos Laguna U19 (W)</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D209" t="n">
+        <v>3</v>
+      </c>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>El Gouna FC vs Al Moqawloon Al Arab</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C210" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="D210" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E210" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F210" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Ceramica Cleopatra FC vs Modern Sport FC</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C211" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D211" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E211" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="F211" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Abu Qir Semad FC vs Al Ittihad Al Sakandary</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>3</v>
+      </c>
+      <c r="C212" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D212" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E212" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="F212" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Al Qanater vs Ra Sporting Club</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="C213" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D213" t="n">
+        <v>3</v>
+      </c>
+      <c r="E213" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Cascada FC vs Banha</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="C214" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D214" t="n">
+        <v>3</v>
+      </c>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>El Ilamayeen vs Diamond SC</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="C215" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D215" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="F215" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Al Majd Al Sakandry FC vs MS Abu El Matamir</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C216" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D216" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Baia Pemba vs Ferroviario de Lichinga</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="C217" t="n">
+        <v>3</v>
+      </c>
+      <c r="D217" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E217" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F217" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Costa Do Sol vs Liga Desportiva De Sofala</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C218" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D218" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E218" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F218" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Clube Ferroviario De Maputo vs Uniao Desportiva Songo</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C219" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="D219" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E219" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F219" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Black Bulls Maputo vs Chingale de Tete</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C220" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D220" t="n">
+        <v>9</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Brodd vs Viking</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>17</v>
+      </c>
+      <c r="C221" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F221" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Sportivo Ameliano vs Sportivo Trinidense</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D222" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E222" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F222" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Nacional Asuncion vs Libertad Asuncion</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C223" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D223" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E223" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F223" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Sportivo Ameliano Reserves vs Sportivo Trinidense Reserves</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C224" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D224" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E224" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F224" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Wiked Luzino vs Wisla Plock</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>5</v>
+      </c>
+      <c r="C225" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D225" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E225" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F225" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Gornik Polkowice vs Polonia Warszawa</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C226" t="n">
+        <v>4</v>
+      </c>
+      <c r="D226" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="E226" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F226" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Beskid Andrychow vs Slask Wroclaw II</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C227" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D227" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F227" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>KS Gornik Zabrze II vs Olimpia Grudziadz</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>10</v>
+      </c>
+      <c r="C228" t="n">
+        <v>5</v>
+      </c>
+      <c r="D228" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E228" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F228" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Gornik Leczna vs Stal Mielec</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C229" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F229" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Znicz Pruszkow vs MKS Cracovia Krakow</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C230" t="n">
+        <v>4</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F230" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Lechia Zielona Gora vs KS Ruch Chorzow</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C231" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D231" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F231" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Sokol Ostroda vs Sokol Kleczew</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C232" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D232" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E232" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F232" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Miedz Legnica vs Chrobry Glogow</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C233" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D233" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E233" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F233" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Resovia Rzeszow vs Arka Gdynia</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C234" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D234" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E234" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F234" t="n">
         <v>1.94</v>
       </c>
-      <c r="C172" t="n">
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Widzew Lodz vs Korona Kielce</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C235" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D235" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E235" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F235" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>CS Sporting Liesti vs FC Dinamo Bükreş</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>15</v>
+      </c>
+      <c r="C236" t="n">
+        <v>8</v>
+      </c>
+      <c r="D236" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E236" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F236" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Gloria Bistrita vs Csikszereda</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C237" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D237" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E237" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="F237" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>FC Arges vs FCSB</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C238" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D238" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E238" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F238" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Minerul Lupeni vs UTA Arad</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>4</v>
+      </c>
+      <c r="C239" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D239" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E239" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F239" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Botosani vs Corvinul Hunedoara</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C240" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D240" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E240" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F240" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Orenburg vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C241" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D241" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E241" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F241" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Spartak Moskova vs Rodina Moscow</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C242" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D242" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E242" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F242" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Zenit vs Dynamo Makhachkala</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C243" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D243" t="n">
+        <v>8</v>
+      </c>
+      <c r="E243" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F243" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Baltika Kaliningrad vs Kryliya Sovetov</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C244" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D244" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E244" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F244" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Tanjong Pagar II vs Young Lions II</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C245" t="n">
+        <v>4</v>
+      </c>
+      <c r="D245" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E245" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F245" t="n">
         <v>3.3</v>
       </c>
-      <c r="D172" t="n">
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Balestier Khalsa FC II vs Hougang II</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
         <v>3.4</v>
       </c>
-      <c r="E172" t="n">
+      <c r="C246" t="n">
+        <v>4</v>
+      </c>
+      <c r="D246" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E246" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F246" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Svaty Jur vs Dunajska Luzna</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C247" t="n">
+        <v>6</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E247" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F247" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Fc Lokomativa Kosice vs Slavia Tu Kosice</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C248" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D248" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E248" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F248" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Tatran Oravske Vesele vs Povazska Bystrica</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="C249" t="n">
+        <v>5</v>
+      </c>
+      <c r="D249" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E249" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F249" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>FK Brezno vs MFK Zvolen</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>11</v>
+      </c>
+      <c r="C250" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F250" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Tatran Krasno Nad Kysucou vs AS Trencin</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>29</v>
+      </c>
+      <c r="C251" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="D251" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E251" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="F251" t="n">
+        <v>5</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Kysucke Nove Mesto vs FK Cadca</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C252" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D252" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E252" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F252" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Aluminij vs Celje</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C253" t="n">
+        <v>4</v>
+      </c>
+      <c r="D253" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E253" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F253" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ND Beltinci vs NS Mura</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C254" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D254" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E254" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F254" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Hajer vs Al-Anwar</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C255" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D255" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E255" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F255" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Al Wahda Mecca vs Damac FC</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
         <v>1.94</v>
       </c>
-      <c r="F172" t="n">
+      <c r="C256" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D256" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E256" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F256" t="n">
         <v>1.76</v>
       </c>
-      <c r="G172" t="inlineStr">
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Al-Ula vs Al Raed Buraidah</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="C257" t="n">
+        <v>4</v>
+      </c>
+      <c r="D257" t="n">
+        <v>5</v>
+      </c>
+      <c r="E257" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F257" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Blacks Power vs Police FC</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C258" t="n">
+        <v>3</v>
+      </c>
+      <c r="D258" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E258" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F258" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Ntugasaze FC vs Maroons Fc</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C259" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D259" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E259" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F259" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Cerrito CS vs Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C260" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D260" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E260" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="F260" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Central Espanol FC vs Juventud Piedras</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C261" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D261" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="E261" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F261" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Liverpool Montevideo vs Boston River</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C262" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E262" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F262" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Ittihad AL Ramtha vs Al Aqaba</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="C263" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D263" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E263" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F263" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Zamora FC vs Deportivo Tachira</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C264" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D264" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E264" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F264" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Atletico El Vigia vs Club Atletico Barinas</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C265" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D265" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E265" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F265" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Real Frontera vs Zamora Barinas II</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C266" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D266" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="E266" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F266" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Yaracuyanos FC vs Urena Fc</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="C267" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D267" t="n">
+        <v>3</v>
+      </c>
+      <c r="E267" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F267" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Nestos Chrisoupolis vs AEK Athens</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>19</v>
+      </c>
+      <c r="C268" t="n">
+        <v>7</v>
+      </c>
+      <c r="D268" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E268" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F268" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>FC Marko vs AE Kifisia</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C269" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D269" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E269" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F269" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Panserraikos vs Atromitos</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C270" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D270" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="E270" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F270" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>AE Larissa vs Olympiakos</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>11</v>
+      </c>
+      <c r="C271" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D271" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F271" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>PAOK vs OFI Crete</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="C272" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D272" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E272" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F272" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Scotland FC Mabvuku vs FC Platinum</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C273" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D273" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E273" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F273" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G273" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +453,4029 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Iğdır FK vs Manisa Futbol Kulubu</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bursaspor vs İstanbulspor</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bodrum FK vs Esenler Erokspor</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Real Sociedad vs Celta Vigo</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Palermo vs Mantova</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cagliari vs Verona</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Cittadella vs Renate</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Novara vs Livorno</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Trento vs Desenzano Calvina</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Toulouse vs Lille</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Rouen vs Valenciennes</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Barracas Central Reserves vs Banfield Reserves</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ca Huracan Reserves vs Central Cordoba Reserves</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Gimnasia Mendoza Reserves vs Rosario Central Reserves</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Defensa Y Justicia Reserves vs Independiente Rivadavia Reserves</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Deportivo Muniz Reserves vs Club Sportivo Barracas Reserves</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>General Lamadrid Reserves vs Berazategui Reserves</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Yupanqui Reserves vs Canuelas FC Reserves</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Deportivo Paraguayo Reserves vs Centro Espanol Reserve</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>JJ Urquiza Reserves vs Leandro N. Alem Reserves</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CA Fenix Pilar Reserves vs Juventud Unida San Miguel Reserves</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Deportivo Laferrere Reserves vs Deportivo Camioneros Reserves</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Argentino Merlo Reserves vs San Martin Burzaco Reserves</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Argentino Quilmes Reserves vs Defensores Unidos Reserves</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Estudiantes Caseros Reserves vs Almagro Reserves</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CA Agropecuario Reserves vs Temperley Reserves</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Almirante Brown Reserves vs CA Atlanta Reserves</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Los Andes Reserves vs Tristan Suarez Reserves</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>All Boys Reserves vs Deportivo Moron Reserves</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Bangladesh U20 vs Syria U20</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>10</v>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Laos U20 vs Indonesia U20</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>11</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Bhutan U20 vs Taiwan U20</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Palestine U20 vs Vietnam U20</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Cambodia U20 vs Japan U20</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>31</v>
+      </c>
+      <c r="C35" t="n">
+        <v>13</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Turkmenistan U20 vs Thailand U20</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sri Lanka U20 vs Maldives U20</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C37" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Afghanistan U20 vs Tajikistan U20</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>India U20 vs Uzbekistan U20</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>11</v>
+      </c>
+      <c r="C39" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kyrgyzstan U20 vs Lebanon U20</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D40" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hong Kong U20 vs Qatar U20</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>11</v>
+      </c>
+      <c r="C41" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Oman U20 vs Saudi Arabia U20</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Bahrain U20 vs Jordan U20</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Baku Sporting vs Karvan Yevlakh</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Moik Baku vs FK Sahdag Qusar</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Khankendi FK vs Sabayil FK</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Anderlecht vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D47" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Gent vs Leuven</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C48" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D48" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Isloch Minsk vs BATE Borisov</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C49" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D49" t="n">
+        <v>5</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>CSKA Sofia II vs Pfc Spartak Pleven</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Vihren Sandanski vs Etar Veliko Tarnovo</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Lokomotiv G.O. vs Dobrudzha Dobrich</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Beroe vs Montana</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ES Setif vs ES Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D54" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Jeunesse Sportive d'El Biar vs Olympique Akbou</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>FC Kopenhag vs Nordsjaelland</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Thisted vs Sonderjyske</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="C57" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F57" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>HB Koege U19 vs Esbjerg U19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>FAR Rabat vs Olympique de Safi</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D59" t="n">
+        <v>6</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ittihad Riadhi de Tanger vs COD Meknes</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Levante (K) vs Villarreal (K)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="C61" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Vinotinto Ecuador vs San Antonio FC Cotacachi</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C62" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Universidad Catolica Quito vs Aucas</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Alashkert vs FC Van</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C64" t="n">
+        <v>6</v>
+      </c>
+      <c r="D64" t="n">
+        <v>11</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Viimsi Jk vs FC Tallinn</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C65" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D65" t="n">
+        <v>8</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RoPo vs Santa Claus</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D66" t="n">
+        <v>11</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F66" t="n">
+        <v>5</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Eif/Akademi vs Lepa</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C67" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Tups vs Lahti 69</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C68" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PPJ/Lauttasaari vs MPS/Atletico Malmi</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C69" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F69" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>HooGee vs Lohjan Pallo</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F70" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Atlantis FC vs Pepo Lappeenranta</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C71" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F71" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>HIFK vs HPS</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C72" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D72" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F72" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Kolkheti Khobi vs FC Didube 2014</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>FC Margveti 2006 vs FC Merani Tbilisi</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C74" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Iberia 2010 Tbilisi vs FC Orbi Tbilisi</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C75" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Guria Lanchkhuti vs FC Gonio</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999 II vs Dinamo Tbilisi II</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="C77" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D77" t="n">
+        <v>4</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Lokomotiv Tbilisi vs FC Tbilisi 2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C78" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Iveria Khashuri vs FC WIT Georgia Tblisi</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" t="n">
+        <v>4</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F79" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sawmer SC vs Nangkiew Irat</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Mosul FC vs AL Zawraa SC</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F81" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Diyala FC vs Al Karma</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>4</v>
+      </c>
+      <c r="C82" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Duhok vs Al Quwa/Jawiya</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C83" t="n">
+        <v>3</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Al Kahrabaa Club vs Al-Gharraf SC</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Fajr Sepasi FC vs Mes Shahr-e Babak</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C85" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="D85" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Hibernian vs Hearts</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F86" t="n">
+        <v>2</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Hapoel Tel-Aviv vs Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Maccabi Kiryat Malakhi vs Hapoel Mahane Yehuda</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C88" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Agudat Sport Nordia Jerusalem vs Sport Club Dimona</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C89" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Shimshon Tel Aviv vs Ironi Beit Shemesh</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="C90" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Maccabi Yavne vs Hapoel Azor</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C91" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D91" t="n">
+        <v>5</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F91" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>MS Shikun Hamizrah vs Hapoel Segev Shalom</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C92" t="n">
+        <v>4</v>
+      </c>
+      <c r="D92" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F92" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Mjallby AIF vs Djurgardens IF</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D93" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Lugano vs Servette</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C94" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D94" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F94" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Basel vs Sion</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C95" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Ellidi vs Hamar Hveragerdi</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F96" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Hafnir vs Vaengir Jupiters</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C97" t="n">
+        <v>5</v>
+      </c>
+      <c r="D97" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F97" t="n">
+        <v>8</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>IH Hafnarfjordur vs Kfr Hvolsvollur</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="F98" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Ulfarnir vs Alafoss</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C99" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D99" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F99" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Mornar Bar vs FK Bokelj Kotor</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="C100" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D100" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Al-Ahli Doha vs Qatar SC Doha</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="C101" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Al Sailiya vs Al Arabi</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C102" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F102" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>FK Arys vs FK Ekibastuz</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D103" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Akademiya Ontyustik vs Aktobe II</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C104" t="n">
+        <v>4</v>
+      </c>
+      <c r="D104" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E104" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FC Shakhter Karagandy vs Khan Tengri FC</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C105" t="n">
+        <v>8</v>
+      </c>
+      <c r="D105" t="n">
+        <v>29</v>
+      </c>
+      <c r="E105" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>FC Astana II vs FC Taraz</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia vs Pafos</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="C107" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E107" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Cariari Pococi vs Pitbulls Santa Barbara</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C108" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>FK RFS vs Riga</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C109" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Banga Gargzdai vs Panevezys</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C110" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Siauliai FA vs Zalgiris Kauno</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C111" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D111" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F111" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Győr ETO vs Ferencváros</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C112" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F112" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Al Ahly Cairo vs Smouha</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C113" t="n">
+        <v>4</v>
+      </c>
+      <c r="D113" t="n">
+        <v>8</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F113" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>La Viena FC vs Team FC Cairo</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C114" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D114" t="n">
+        <v>4</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Haras El Hodood vs El Entag El Harby</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E115" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Dayrout vs We Sporting Club</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C116" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>El Sekka El Hadid SC vs Kafr El Zayat</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C117" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E117" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>El Mansoura vs Kahraba Ismailia</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C118" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CD Maxaquene vs Ferroviario Beira</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C119" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F119" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Viking U19 vs Brann U19</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F120" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Lillehammer U19 vs Ullensaker/Kisa U19</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="C121" t="n">
+        <v>5</v>
+      </c>
+      <c r="D121" t="n">
+        <v>5</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="F121" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>KFUM U19 vs Baerum Sk U19</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="C122" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D122" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F122" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Olmaliq OKMK vs Xorazm Urganch</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C123" t="n">
+        <v>4</v>
+      </c>
+      <c r="D123" t="n">
+        <v>5</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F123" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Deportivo Capiata vs 3 De Noviembre</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2</v>
+      </c>
+      <c r="F124" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Nacional Asunción Reserve vs Club Libertad Asuncion Reserves</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C125" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F125" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Olimpia Asuncion Reserves vs Club Guarani Asuncion Reserves</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F126" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa vs Gornik Zabrze</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C127" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F127" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Lech Poznan vs Jagiellonia Białystok</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4</v>
+      </c>
+      <c r="D128" t="n">
+        <v>4</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F128" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Sokol Bozepole Wielkie vs Stoczniowiec Gdansk</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C129" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D129" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E129" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F129" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Avia Swidnik vs Wieczysta Krakow</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D130" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F130" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>GKS 71 Tychy vs LKS Lodz</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F131" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Slask Wroclaw vs Pogon Szczecin</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F132" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Politehnica Timisoara vs Rapid Bükreş</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>FC Bacau vs Universitatea Craiova</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>7</v>
+      </c>
+      <c r="C134" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D134" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Dinamo Moskova vs Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D135" t="n">
+        <v>4</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Geylang International II vs Lion City Sailors FC II</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="C136" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D136" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F136" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>NK Triglav Kranj U19 vs Radomlje U19</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Al Feiha vs Al Kholood</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C138" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D138" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E138" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Neom SC vs Al-Khaleej</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C139" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D139" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Al Diriyah vs Al-Qadsiah Al Khubar</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>5</v>
+      </c>
+      <c r="C140" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D140" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Uhamiaji FC vs Chipukizi FC</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D141" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E141" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Kataka Fc vs Bul FC</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C142" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D142" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E142" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Express FC vs Kampala City Capital Authority Fc</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C143" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E143" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F143" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CA Rentistas vs Plaza Colonia</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C144" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D144" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E144" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Albion FC vs CA Progreso Montevideo</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D145" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Club Atletico River Plate vs Club Nacional de Montevideo</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F146" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Al-Baqa'a vs Doqarah FC</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F147" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Rayo Zuliano vs Carabobo</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C148" t="n">
+        <v>4</v>
+      </c>
+      <c r="D148" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Academia Anzoategui vs Monagas SC</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C149" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D149" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E149" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Panathinaikos vs Niki Volou</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="C150" t="n">
+        <v>7</v>
+      </c>
+      <c r="D150" t="n">
+        <v>17</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F150" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,6 +453,4399 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>İstanbulspor vs Iğdır FK</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Esenler Erokspor vs Kayserispor</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mardin 1969 Spor vs Bodrum FK</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Manisa Futbol Kulubu vs Bursaspor</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Göztepe vs Gaziantep FK</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Rizespor vs Alanyaspor</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Caykur Rizespor U19 vs Alanyaspor U19</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Göztepe Sk U19 vs Gaziantep Bb U19</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bromley vs AFC Wimbledon</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Carshalton Athletic vs Chertsey Town</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Swindon Supermarine vs Winslow United</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Redditch United vs Malvern Town</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Luton Town U21 vs Peterborough United U21</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Plymouth Argyle FC U21 vs Cardiff U21</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Reading U21 vs Bristol City U21</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Swansea City U21 vs Huddersfield U21</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Getafe vs Celta Vigo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Elche vs Real Sociedad</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Sabadell vs Cordoba</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Granada (K) vs Real Sociedad (K)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Cagliari vs Lecce</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Udinese vs Lazio</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Palermo vs Sampdoria</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Alcione Milano vs Treviso</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Pro Vercelli vs Folgore Caratese</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Renate vs Novara</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="C27" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Trento vs Lecco</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="C28" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Catania vs Cosenza</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Picerno vs Inter Milano U23</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="C30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Nantes vs AS Nancy Lorraine</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Union Berlin (K) vs Frankfurt (K)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Estoril vs Arouca</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sc Lusitania vs AVS</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Braga U23 vs Penafiel U23</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Jong Utrecht vs FC Eindhoven</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Jong PSV vs Den Bosch</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Portland Timbers II vs Vancouver Whitecaps II</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Deportivo Muniz vs Sportivo Barracas</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nueva Chicago vs Quilmes Atletico Club</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Escobar FC vs Defensores Puerto Vilelas</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Union Santa Fe (K) vs Social Atletico Television (K)</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>4</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chacarita Juniors U20 vs Almagro U20</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Al-Wahda Abu Dhabi U23 vs AL Dhafra U23</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D44" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ajman Club U23 vs Al-Nasr Dubai U23</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Isloch Minsk vs Arsenal Dzyarzhynsk</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="C46" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Dinamo Brest vs BATE Borisov</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Corinthians (K) vs Cruzeiro (K)</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F48" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Paulista SP vs Gremio Prudente</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7 De Abril RJ vs Serra Macaense</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Londrina EC PR vs IF Sao Joseense PR</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Metropolitano SC vs Marcilio Dias</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Dunav Ruse vs Slavia Sofia</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="C53" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sportist Svoge vs Lokomotiv G.O.</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Fratria vs Psfc Chernomoretz Burgas</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Pirin Blagoevgrad vs Ludogorets II</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C56" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Pfc Spartak Pleven vs Hebar Pazardzhik</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Wuhan Three Towns U20 vs Guangdong GZ-Power U20</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C58" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F58" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Midtjylland vs Nordsjaelland</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C59" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F59" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Kuzey Kore U20 (K) vs Portekiz U20 (K)</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>6</v>
+      </c>
+      <c r="D60" t="n">
+        <v>12</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F60" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>İspanya U20 (K) vs Nijerya U20 (K)</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C61" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F61" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Kosta Rika U20 (K) vs Kolombiya U20 (K)</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>9</v>
+      </c>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F62" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>VJS Vantaa II vs Toukolan Teras</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F63" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Klubi 04 vs Kapa/Pule</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F64" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Ilves Ii vs Pallo-Iirot Rauma</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D65" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>FC Telavi vs FC Samtredia</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C66" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AL Zawraa SC vs Al Kahrabaa Club</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="C67" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D67" t="n">
+        <v>5</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Karbala Fc vs Al Quwa/Jawiya</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C68" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="F68" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Mes Shahr-e Babak vs Malavan</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F69" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Perspolis Teheran vs Zob Ahan</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C70" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F70" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Nassaji Mazandaran vs Kheybar Khorramabad</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C71" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Foolad Khuzestan FC vs Fajr Sepasi FC</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C72" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Maccabi Netanya vs Hapoel Haifa</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C73" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F73" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Hapoel Tel-Aviv vs Hapoel Ramat Gan</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="C74" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D74" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F74" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Bnei Sakhnin FC vs Beitar Jerusalem</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="C75" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Hapoel Beer-Sheva vs Maccabi Tel-Aviv</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="C76" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F76" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Bnei-Yehuda Tel-Aviv vs Hapoel Ironi Rishon Lezion</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C77" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F77" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Maccabi Kiryat Gat Sports Club vs Maccabi Herzliya</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C78" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>KAFR Qasim vs Ironi Modiin</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C79" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D79" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Malmo FF vs AIK</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C80" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D80" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F80" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Kalmar FF vs Djurgardens IF</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C81" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F81" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Mjallby AIF vs IFK Goteborg</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C82" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Orebro SK vs Ostersunds FK</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C83" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Stjarnan (K) vs Vikingur Reykjavik (K)</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F84" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Throttur Reykjavik (K) vs Breidablik Kopavogur (K)</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D85" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>HFX Wanderers FC vs Cavalry FC</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C86" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D86" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Umm Salal vs Al-Khor</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D87" t="n">
+        <v>4</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F87" t="n">
+        <v>2</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Al-Gharafa II vs Muaither SC</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C88" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D88" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F88" t="n">
+        <v>2</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Kairat Almaty (K) vs Tomiris Turan (K)</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C89" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D89" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F89" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Pafos vs Olympiakos Nicosia FC</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D90" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E90" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F90" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Aris Limmasol vs Omonia Nicosia</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C91" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D91" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Carmelita vs Pitbulls Santa Barbara</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="C92" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Limavady United Reserves vs Ballymena United Reserves</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F93" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Linfield Reserves vs Portadown Reserves</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C94" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D94" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E94" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F94" t="n">
+        <v>4</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Asiagoal Bishkek vs FK Kyrgyzaltyn</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C95" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D95" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E95" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F95" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Al Ahed vs Al Akhaa Al Ahli</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C96" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D96" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="E96" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F96" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FK RFS vs Liepaja</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C97" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D97" t="n">
+        <v>7</v>
+      </c>
+      <c r="E97" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Riga vs BFC Daugava Daugavpils</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="C98" t="n">
+        <v>5</v>
+      </c>
+      <c r="D98" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E98" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F98" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Riga FC II vs Skanstes SK</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C99" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E99" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F99" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Hegelmann vs Panevezys</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C100" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E100" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Vilnius FK Zalgiris II vs FK Neptunas Klaipeda</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C101" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Videoton Fehervar vs Diosgyor VTK</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Floriana vs Valletta</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C103" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D103" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E103" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="F103" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>El Qanah FC vs Talaea El Gaish</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C104" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Al Ittihad Al Sakandary vs Asyut Cement Petroleum</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C105" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D105" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Petrojet vs Al Masry Club</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C106" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>National Bank of Egypt SC vs Ghazl Al Mehalla</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C107" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D107" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>KFUM 2 vs Lokomotiv Oslo</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C108" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E108" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="F108" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Molde (A) vs Aalesund FK II</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="C109" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="E109" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F109" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Kvik Trondheim vs Ranheim 2</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C110" t="n">
+        <v>4</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E110" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F110" t="n">
+        <v>4</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Droebak/Frogn vs Lyn Oslo 2</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C111" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E111" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="F111" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Orn Horten vs Sarpsborg 08 2</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C112" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E112" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F112" t="n">
+        <v>4</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Gneist vs Aasane Fotball II</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="C113" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="E113" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F113" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Fardu Ferghana vs PFK Aral</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C114" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E114" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guarani Asuncion vs Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C115" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D115" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E115" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense Reserves vs Olimpia Asuncion Reserves</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="C116" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D116" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E116" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Club Libertad Asuncion Reserves vs Rubio Nu Reserve</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="C117" t="n">
+        <v>12</v>
+      </c>
+      <c r="D117" t="n">
+        <v>21</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F117" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueno Reserves vs Sportivo Ameliano Reserves</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C118" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta (K) vs Club Guarani (K)</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="C119" t="n">
+        <v>7</v>
+      </c>
+      <c r="D119" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E119" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F119" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Club Sport Colonial vs General Caballero Campo Grande</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D120" t="n">
+        <v>11</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F120" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Molinos El Pirata vs Carlos A. Mannucci</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C121" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D121" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E121" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="F121" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Wieczysta Krakow vs Zaglebie Lubin</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>2</v>
+      </c>
+      <c r="C122" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D122" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E122" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Pogon Szczecin vs Wisla Plock</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C123" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F123" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>KS Ruch Chorzow vs Unia Skierniewice</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C124" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D124" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F124" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Voluntari vs FC Arges</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C125" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova vs U Cluj</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C126" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D126" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F126" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Gazovik Orenburg 2 vs FK Izhevsk</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C127" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E127" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="F127" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Rubin Kazan vs Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C128" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Police Fc (Rwanda) vs Gicumbi FC</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D129" t="n">
+        <v>5</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="F129" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>OFK Belgrade vs IMT Belgrade</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F130" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Vozdovac vs Backa Topola</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F131" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ZFK Spartak Subotica (K) vs ZFK Masinac Nis (K)</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="C132" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D132" t="n">
+        <v>12</v>
+      </c>
+      <c r="E132" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="F132" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Balestier Khalsa FC II vs Tanjong Pagar II</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C133" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F133" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Geylang International II vs FC Jurong II</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E134" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>MSK Zilina B vs SK Slovan Bratislava B</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C135" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D135" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E135" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F135" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Raslavice vs Vranov nad Topl'ou</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C136" t="n">
+        <v>4</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E136" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F136" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Radomlje U19 vs NK Aluminij U19</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F137" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>FC Koper U19 vs Olimpija Ljubljana U19</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C138" t="n">
+        <v>4</v>
+      </c>
+      <c r="D138" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F138" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>NK Celje U19 vs Beltinci U19</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C139" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D139" t="n">
+        <v>6</v>
+      </c>
+      <c r="E139" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F139" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Jadran Dekani U19 vs Ns Mura U19</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="C140" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D140" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E140" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F140" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Al-Khaleej vs Al Riyadh</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Al Hilal Riyadh vs Neom SC</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C142" t="n">
+        <v>6</v>
+      </c>
+      <c r="D142" t="n">
+        <v>11</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F142" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Al-Faisaly Harmah U21 vs Al Najma SC U21</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="C143" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D143" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E143" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="F143" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Damac U21 vs AL Riyadh SC U21</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C144" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D144" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E144" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>AL Kholood U21 vs Al Orobah U21</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D145" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F145" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>AL Taawoun U21 vs Al Hilal U21</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C146" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="E146" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F146" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Al Adalah vs Al-Saqer FC</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D147" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E147" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F147" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Al Jabalain vs Al Wahda Mecca</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D148" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E148" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F148" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Al Akhdoud vs Al Najma (SAUD)</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="C149" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E149" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="F149" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Azam vs Namungo</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="C150" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D150" t="n">
+        <v>10</v>
+      </c>
+      <c r="E150" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F150" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Albion FC vs CA Progreso Montevideo</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="C151" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D151" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E151" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Ca Penarol Reserves vs Boston River Reserves</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C152" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E152" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F152" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Montevideo City Torque Reserve vs Liverpool Montevideo Reserves</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D153" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E153" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F153" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Club Oriental Reserves vs Racing Club de Montevideo Reserves</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C154" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E154" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F154" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Colon Montevideo Reserves vs Montevideo Wanderers Reserves</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C155" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D155" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E155" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="F155" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Cerro Largo FC Reserves vs Defensor Sporting Reserves</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C156" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F156" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CA River Plate Montevideo Reserves vs Nacional de Montevideo Reserves</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>4</v>
+      </c>
+      <c r="C157" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E157" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F157" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Deportivo Maldonado Reserves vs Juventud De Las Piedras Reserves</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C158" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D158" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E158" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="F158" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Nashama Al-Mustaqbal (W) vs Al Orthodoxi (W)</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C159" t="n">
+        <v>4</v>
+      </c>
+      <c r="D159" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Al Hashemeya vs Hayy Al-Amir Hassan</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C160" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D160" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F160" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis vs Iraklis</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C161" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D161" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E161" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>FC Marko vs Panserraikos</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C162" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D162" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E162" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="F162" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Kallithea vs Niki Volou</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C163" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D163" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E163" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="F163" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Ellas Syrou vs Apollon Kalamarias</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="C164" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D164" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G164"/>
+  <dimension ref="A1:G209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>İstanbulspor vs Iğdır FK</t>
+          <t>Club Brugge vs Aston Villa</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="C2" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D2" t="n">
-        <v>2.11</v>
+        <v>2.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="F2" t="n">
-        <v>1.87</v>
+        <v>2.14</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -483,23 +483,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Esenler Erokspor vs Kayserispor</t>
+          <t>AEK Athens vs LASK Linz</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.37</v>
+        <v>1.76</v>
       </c>
       <c r="C3" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2.55</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="F3" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -510,23 +510,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Mardin 1969 Spor vs Bodrum FK</t>
+          <t>Porto vs Manchester City</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.78</v>
+        <v>4.5</v>
       </c>
       <c r="C4" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1.71</v>
       </c>
       <c r="E4" t="n">
-        <v>1.98</v>
+        <v>1.64</v>
       </c>
       <c r="F4" t="n">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -537,23 +537,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Manisa Futbol Kulubu vs Bursaspor</t>
+          <t>Lille vs Real Betis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="C5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7</v>
+        <v>3.05</v>
       </c>
       <c r="E5" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="F5" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Göztepe vs Gaziantep FK</t>
+          <t>Borussia Dortmund vs Villarreal</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="C6" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="D6" t="n">
         <v>3.8</v>
       </c>
       <c r="E6" t="n">
-        <v>1.93</v>
+        <v>1.45</v>
       </c>
       <c r="F6" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -591,23 +591,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Rizespor vs Alanyaspor</t>
+          <t>Real Madrid vs Inter</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D7" t="n">
-        <v>4.15</v>
+        <v>4.75</v>
       </c>
       <c r="E7" t="n">
-        <v>2.06</v>
+        <v>1.41</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>2.73</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -618,23 +618,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Caykur Rizespor U19 vs Alanyaspor U19</t>
+          <t>Fc Porto vs Manchester City U19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.12</v>
+        <v>2.68</v>
       </c>
       <c r="C8" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="D8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F8" t="n">
         <v>2.8</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1.96</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -645,23 +645,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Göztepe Sk U19 vs Gaziantep Bb U19</t>
+          <t>Club Brugge U19 vs Aston Villa U19</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="C9" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="E9" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="F9" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -672,23 +672,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bromley vs AFC Wimbledon</t>
+          <t>Lille OSC U19 vs Real Betis Balompie Under 19</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="C10" t="n">
-        <v>3.28</v>
+        <v>3.8</v>
       </c>
       <c r="D10" t="n">
-        <v>2.73</v>
+        <v>1.81</v>
       </c>
       <c r="E10" t="n">
-        <v>1.97</v>
+        <v>1.41</v>
       </c>
       <c r="F10" t="n">
-        <v>1.72</v>
+        <v>2.63</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -699,23 +699,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Carshalton Athletic vs Chertsey Town</t>
+          <t>Real Madrid U19 vs Inter Milan U19</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="C11" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="D11" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="E11" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -726,23 +726,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Swindon Supermarine vs Winslow United</t>
+          <t>Borussia Dortmund U19 vs Villarreal CF U19</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.66</v>
+        <v>2.12</v>
       </c>
       <c r="C12" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="D12" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -753,23 +753,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Redditch United vs Malvern Town</t>
+          <t>Watford vs Preston</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="E13" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="F13" t="n">
-        <v>2.31</v>
+        <v>1.84</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -780,23 +780,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Luton Town U21 vs Peterborough United U21</t>
+          <t>Wrexham vs Burnley</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.77</v>
+        <v>2.02</v>
       </c>
       <c r="C14" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D14" t="n">
-        <v>2.03</v>
+        <v>3.4</v>
       </c>
       <c r="E14" t="n">
-        <v>1.32</v>
+        <v>1.85</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>1.87</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -807,23 +807,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Plymouth Argyle FC U21 vs Cardiff U21</t>
+          <t>Blackburn vs Sheffield United</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="C15" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="E15" t="n">
-        <v>1.33</v>
+        <v>1.86</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>1.87</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -834,23 +834,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Reading U21 vs Bristol City U21</t>
+          <t>Cardiff vs Stoke</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="C16" t="n">
         <v>3.7</v>
       </c>
       <c r="D16" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2.23</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -861,23 +861,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Swansea City U21 vs Huddersfield U21</t>
+          <t>Southampton vs Swansea</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="C17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D17" t="n">
         <v>3.8</v>
       </c>
-      <c r="D17" t="n">
-        <v>3.05</v>
-      </c>
       <c r="E17" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="F17" t="n">
-        <v>3.05</v>
+        <v>1.99</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -888,23 +888,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Getafe vs Celta Vigo</t>
+          <t>Bolton vs West Ham</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="C18" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="D18" t="n">
-        <v>3.15</v>
+        <v>1.62</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="F18" t="n">
-        <v>1.41</v>
+        <v>2.33</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Elche vs Real Sociedad</t>
+          <t>Worcester City vs Knowle FC</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.15</v>
+        <v>1.58</v>
       </c>
       <c r="C19" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D19" t="n">
-        <v>2.16</v>
+        <v>4.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="F19" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -942,23 +942,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sabadell vs Cordoba</t>
+          <t>Brentwood Town vs Concord Rangers FC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.04</v>
+        <v>1.53</v>
       </c>
       <c r="C20" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="D20" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="E20" t="n">
-        <v>2.02</v>
+        <v>1.45</v>
       </c>
       <c r="F20" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -969,23 +969,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Granada (K) vs Real Sociedad (K)</t>
+          <t>Fakenham Town FC vs Ware FC</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.33</v>
+        <v>2.55</v>
       </c>
       <c r="C21" t="n">
         <v>3.7</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6</v>
+        <v>2.23</v>
       </c>
       <c r="E21" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="F21" t="n">
-        <v>2.02</v>
+        <v>2.68</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -996,23 +996,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cagliari vs Lecce</t>
+          <t>Havant &amp; Waterloville vs Chippenham Town</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.09</v>
+        <v>2.73</v>
       </c>
       <c r="C22" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D22" t="n">
-        <v>3.6</v>
+        <v>2.18</v>
       </c>
       <c r="E22" t="n">
-        <v>2.45</v>
+        <v>1.68</v>
       </c>
       <c r="F22" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1023,23 +1023,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Udinese vs Lazio</t>
+          <t>Kettering Town vs Wellingborough Town</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.68</v>
+        <v>1.79</v>
       </c>
       <c r="C23" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="D23" t="n">
-        <v>2.63</v>
+        <v>3.7</v>
       </c>
       <c r="E23" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="F23" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1050,23 +1050,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Palermo vs Sampdoria</t>
+          <t>Needham Market vs Stanway Rovers</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="C24" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D24" t="n">
         <v>4.5</v>
       </c>
       <c r="E24" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="F24" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1077,23 +1077,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alcione Milano vs Treviso</t>
+          <t>Boldmere St Michaels vs Bourne Town FC</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.27</v>
+        <v>2.09</v>
       </c>
       <c r="C25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D25" t="n">
         <v>2.9</v>
       </c>
-      <c r="D25" t="n">
-        <v>3.05</v>
-      </c>
       <c r="E25" t="n">
-        <v>2.55</v>
+        <v>1.68</v>
       </c>
       <c r="F25" t="n">
-        <v>1.43</v>
+        <v>2.06</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1104,23 +1104,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pro Vercelli vs Folgore Caratese</t>
+          <t>Hitchin Town vs Biggleswade Town</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="C26" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="D26" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="E26" t="n">
-        <v>2.45</v>
+        <v>1.6</v>
       </c>
       <c r="F26" t="n">
-        <v>1.47</v>
+        <v>2.16</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1131,23 +1131,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Renate vs Novara</t>
+          <t>Doncaster vs Huddersfield</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="C27" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="D27" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="F27" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1158,23 +1158,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Trento vs Lecco</t>
+          <t>Exeter vs Tottenham U21</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="C28" t="n">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="D28" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2</v>
+        <v>1.38</v>
       </c>
       <c r="F28" t="n">
-        <v>1.58</v>
+        <v>2.8</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1185,23 +1185,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Catania vs Cosenza</t>
+          <t>Crystal Palace vs Middlesbrough</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="C29" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D29" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="E29" t="n">
-        <v>2.04</v>
+        <v>1.58</v>
       </c>
       <c r="F29" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1212,23 +1212,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Picerno vs Inter Milano U23</t>
+          <t>Leyton Orient vs Bradford</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.18</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D30" t="n">
-        <v>3.1</v>
+        <v>2.23</v>
       </c>
       <c r="E30" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="F30" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1239,23 +1239,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Nantes vs AS Nancy Lorraine</t>
+          <t>Bournemouth vs Lincoln City</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="C31" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>3.6</v>
+        <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>1.86</v>
+        <v>1.43</v>
       </c>
       <c r="F31" t="n">
-        <v>1.81</v>
+        <v>2.6</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1266,23 +1266,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Union Berlin (K) vs Frankfurt (K)</t>
+          <t>Sunderland vs Hull City</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3.5</v>
+        <v>1.68</v>
       </c>
       <c r="C32" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D32" t="n">
-        <v>1.75</v>
+        <v>4.5</v>
       </c>
       <c r="E32" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="F32" t="n">
-        <v>2.39</v>
+        <v>1.83</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1293,23 +1293,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Estoril vs Arouca</t>
+          <t>Millwall vs Newcastle</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.35</v>
+        <v>5.5</v>
       </c>
       <c r="C33" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="D33" t="n">
-        <v>2.73</v>
+        <v>1.5</v>
       </c>
       <c r="E33" t="n">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="F33" t="n">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1320,23 +1320,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sc Lusitania vs AVS</t>
+          <t>AFC Hornchurch vs Ipswich U21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="C34" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="D34" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="E34" t="n">
-        <v>2.01</v>
+        <v>1.4</v>
       </c>
       <c r="F34" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1347,23 +1347,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Braga U23 vs Penafiel U23</t>
+          <t>Boreham Wood vs Newcastle U21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.74</v>
+        <v>1.2</v>
       </c>
       <c r="C35" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="D35" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="E35" t="n">
-        <v>1.72</v>
+        <v>1.25</v>
       </c>
       <c r="F35" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1374,23 +1374,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jong Utrecht vs FC Eindhoven</t>
+          <t>Wealdstone vs Stoke U21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.14</v>
+        <v>1.45</v>
       </c>
       <c r="C36" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="D36" t="n">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="E36" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="F36" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1401,23 +1401,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jong PSV vs Den Bosch</t>
+          <t>Sutton Utd vs Birmingham U21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.96</v>
+        <v>1.5</v>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>4.75</v>
       </c>
       <c r="E37" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="F37" t="n">
-        <v>3.15</v>
+        <v>2.77</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1428,23 +1428,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portland Timbers II vs Vancouver Whitecaps II</t>
+          <t>Halifax vs Wolverhampton U21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="C38" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="D38" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="E38" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="F38" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1455,21 +1455,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Deportivo Muniz vs Sportivo Barracas</t>
+          <t>Scunthorpe vs Nottingham Forest U21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.1</v>
+        <v>1.76</v>
       </c>
       <c r="C39" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="D39" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
+        <v>3.4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1.45</v>
+      </c>
       <c r="F39" t="n">
-        <v>1.47</v>
+        <v>2.45</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1480,23 +1482,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nueva Chicago vs Quilmes Atletico Club</t>
+          <t>Boston United vs West Brom U21</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="F40" t="n">
         <v>2.63</v>
-      </c>
-      <c r="C40" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="D40" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E40" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F40" t="n">
-        <v>1.43</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1507,23 +1509,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Escobar FC vs Defensores Puerto Vilelas</t>
+          <t>Solihull Moors vs Leeds U21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="C41" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D41" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="E41" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="F41" t="n">
-        <v>1.64</v>
+        <v>2.8</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1534,23 +1536,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Union Santa Fe (K) vs Social Atletico Television (K)</t>
+          <t>Gateshead vs Derby U21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>1.92</v>
       </c>
       <c r="C42" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D42" t="n">
-        <v>1.75</v>
+        <v>2.9</v>
       </c>
       <c r="E42" t="n">
-        <v>2.09</v>
+        <v>1.28</v>
       </c>
       <c r="F42" t="n">
-        <v>1.64</v>
+        <v>3.1</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1561,23 +1563,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Chacarita Juniors U20 vs Almagro U20</t>
+          <t>Braintree vs Fulham U21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.45</v>
+        <v>2.39</v>
       </c>
       <c r="C43" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="D43" t="n">
-        <v>5.5</v>
+        <v>2.34</v>
       </c>
       <c r="E43" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="F43" t="n">
-        <v>2.03</v>
+        <v>2.77</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1588,23 +1590,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Al-Wahda Abu Dhabi U23 vs AL Dhafra U23</t>
+          <t>Worthing vs Norwich City U21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="C44" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="E44" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="F44" t="n">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1615,23 +1617,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ajman Club U23 vs Al-Nasr Dubai U23</t>
+          <t>Aldershot vs West Ham U21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="C45" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D45" t="n">
-        <v>3.6</v>
+        <v>2.63</v>
       </c>
       <c r="E45" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="F45" t="n">
-        <v>2.18</v>
+        <v>2.68</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1642,23 +1644,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Isloch Minsk vs Arsenal Dzyarzhynsk</t>
+          <t>Woking vs Southampton U21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.43</v>
+        <v>1.83</v>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="E46" t="n">
-        <v>1.76</v>
+        <v>1.37</v>
       </c>
       <c r="F46" t="n">
-        <v>1.93</v>
+        <v>2.7</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1669,23 +1671,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Dinamo Brest vs BATE Borisov</t>
+          <t>Macclesfield Town vs Scarborough Athletic</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="C47" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="E47" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="F47" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1696,23 +1698,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Corinthians (K) vs Cruzeiro (K)</t>
+          <t>Radcliffe Borough vs Hebburn Town</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.41</v>
+        <v>2.45</v>
       </c>
       <c r="C48" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="D48" t="n">
-        <v>5.5</v>
+        <v>2.39</v>
       </c>
       <c r="E48" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="F48" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1723,23 +1725,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Paulista SP vs Gremio Prudente</t>
+          <t>Spennymoor Town vs Spalding Utd</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="C49" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="D49" t="n">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
       <c r="E49" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="F49" t="n">
-        <v>1.45</v>
+        <v>1.94</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1750,23 +1752,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>7 De Abril RJ vs Serra Macaense</t>
+          <t>Worksop Town vs Bedford Town</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3.7</v>
+        <v>2.05</v>
       </c>
       <c r="C50" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D50" t="n">
-        <v>1.83</v>
+        <v>3.05</v>
       </c>
       <c r="E50" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="F50" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1777,23 +1779,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Londrina EC PR vs IF Sao Joseense PR</t>
+          <t>Chorley vs Darlington</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="C51" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="D51" t="n">
-        <v>3.4</v>
+        <v>2.77</v>
       </c>
       <c r="E51" t="n">
-        <v>2.27</v>
+        <v>1.62</v>
       </c>
       <c r="F51" t="n">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1804,23 +1806,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Metropolitano SC vs Marcilio Dias</t>
+          <t>Southport vs Morecambe</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="C52" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="D52" t="n">
         <v>2.16</v>
       </c>
       <c r="E52" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="F52" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1831,23 +1833,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dunav Ruse vs Slavia Sofia</t>
+          <t>Buxton vs Brackley</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2.58</v>
+        <v>1.68</v>
       </c>
       <c r="C53" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="D53" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="E53" t="n">
-        <v>2.35</v>
+        <v>1.64</v>
       </c>
       <c r="F53" t="n">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -1858,23 +1860,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sportist Svoge vs Lokomotiv G.O.</t>
+          <t>South Shields vs Marine</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2.16</v>
+        <v>1.43</v>
       </c>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="D54" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>2.34</v>
+        <v>1.47</v>
       </c>
       <c r="F54" t="n">
-        <v>1.51</v>
+        <v>2.45</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -1885,23 +1887,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Fratria vs Psfc Chernomoretz Burgas</t>
+          <t>Kings Lynn vs Hednesford Town</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="C55" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="E55" t="n">
-        <v>1.97</v>
+        <v>1.76</v>
       </c>
       <c r="F55" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -1912,23 +1914,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Pirin Blagoevgrad vs Ludogorets II</t>
+          <t>Harborough Town vs Hereford</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4.75</v>
+        <v>1.93</v>
       </c>
       <c r="C56" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="D56" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="F56" t="n">
-        <v>1.87</v>
+        <v>2.33</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -1939,23 +1941,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pfc Spartak Pleven vs Hebar Pazardzhik</t>
+          <t>Chester vs Merthyr Town</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3.05</v>
+        <v>1.6</v>
       </c>
       <c r="C57" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D57" t="n">
-        <v>2.08</v>
+        <v>4.33</v>
       </c>
       <c r="E57" t="n">
-        <v>1.87</v>
+        <v>1.64</v>
       </c>
       <c r="F57" t="n">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -1966,23 +1968,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns U20 vs Guangdong GZ-Power U20</t>
+          <t>Telford vs Oxford City</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="C58" t="n">
         <v>3.4</v>
       </c>
       <c r="D58" t="n">
-        <v>2.27</v>
+        <v>2.73</v>
       </c>
       <c r="E58" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="F58" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -1993,23 +1995,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Midtjylland vs Nordsjaelland</t>
+          <t>Maidenhead United vs Torquay United</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="C59" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D59" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="E59" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="F59" t="n">
-        <v>2.22</v>
+        <v>2.03</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2020,23 +2022,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Kuzey Kore U20 (K) vs Portekiz U20 (K)</t>
+          <t>Weston-super-Mare vs AFC Totton</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.16</v>
+        <v>1.68</v>
       </c>
       <c r="C60" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="D60" t="n">
-        <v>12</v>
+        <v>4.15</v>
       </c>
       <c r="E60" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="F60" t="n">
-        <v>2.08</v>
+        <v>1.87</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2047,17 +2049,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>İspanya U20 (K) vs Nijerya U20 (K)</t>
+          <t>Dagenham &amp; Redbridge vs Dover Athletic</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="C61" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="D61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E61" t="n">
         <v>1.43</v>
@@ -2074,23 +2076,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Kosta Rika U20 (K) vs Kolombiya U20 (K)</t>
+          <t>Ebbsfleet United vs Hemel Hempstead Town</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>9</v>
+        <v>1.81</v>
       </c>
       <c r="C62" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="D62" t="n">
-        <v>1.25</v>
+        <v>3.7</v>
       </c>
       <c r="E62" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="F62" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2101,23 +2103,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>VJS Vantaa II vs Toukolan Teras</t>
+          <t>Tonbridge Angels vs Maidstone Utd</t>
         </is>
       </c>
       <c r="B63" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="C63" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F63" t="n">
         <v>1.96</v>
-      </c>
-      <c r="C63" t="n">
-        <v>4</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E63" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F63" t="n">
-        <v>3.3</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2128,23 +2130,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Klubi 04 vs Kapa/Pule</t>
+          <t>Chesham United vs Billericay Town</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="C64" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D64" t="n">
         <v>3.2</v>
       </c>
       <c r="E64" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="F64" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2155,23 +2157,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ilves Ii vs Pallo-Iirot Rauma</t>
+          <t>Dorking Wanderers vs Chelmsford City</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1.55</v>
+        <v>2.02</v>
       </c>
       <c r="C65" t="n">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="D65" t="n">
-        <v>4.15</v>
+        <v>2.9</v>
       </c>
       <c r="E65" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="F65" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2182,23 +2184,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FC Telavi vs FC Samtredia</t>
+          <t>Hampton &amp; Richmond Borough vs Farnborough</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.76</v>
+        <v>2.5</v>
       </c>
       <c r="C66" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D66" t="n">
-        <v>3.8</v>
+        <v>2.27</v>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="F66" t="n">
-        <v>1.7</v>
+        <v>2.35</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2209,23 +2211,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AL Zawraa SC vs Al Kahrabaa Club</t>
+          <t>Salisbury vs Slough Town</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="C67" t="n">
-        <v>3.8</v>
+        <v>4.75</v>
       </c>
       <c r="D67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E67" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="F67" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2236,23 +2238,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Karbala Fc vs Al Quwa/Jawiya</t>
+          <t>Folkestone Invicta vs Horsham</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4.75</v>
+        <v>1.94</v>
       </c>
       <c r="C68" t="n">
         <v>3.5</v>
       </c>
       <c r="D68" t="n">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="E68" t="n">
-        <v>1.99</v>
+        <v>1.66</v>
       </c>
       <c r="F68" t="n">
-        <v>1.72</v>
+        <v>2.07</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2263,23 +2265,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak vs Malavan</t>
+          <t>West Auckland Town vs Ossett United</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="C69" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="D69" t="n">
-        <v>2.4</v>
+        <v>2.73</v>
       </c>
       <c r="E69" t="n">
-        <v>2.73</v>
+        <v>1.62</v>
       </c>
       <c r="F69" t="n">
-        <v>1.38</v>
+        <v>2.11</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2290,23 +2292,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Perspolis Teheran vs Zob Ahan</t>
+          <t>Bradford Park Avenue vs Silsden</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="C70" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="D70" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="E70" t="n">
-        <v>2.07</v>
+        <v>1.55</v>
       </c>
       <c r="F70" t="n">
-        <v>1.66</v>
+        <v>2.27</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2317,23 +2319,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Nassaji Mazandaran vs Kheybar Khorramabad</t>
+          <t>Garforth Town vs Beverley Town FC</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="C71" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="D71" t="n">
-        <v>2.73</v>
+        <v>3.7</v>
       </c>
       <c r="E71" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="F71" t="n">
-        <v>1.47</v>
+        <v>2.25</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2344,23 +2346,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Foolad Khuzestan FC vs Fajr Sepasi FC</t>
+          <t>Mossley vs Clitheroe</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="C72" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="D72" t="n">
-        <v>3.8</v>
+        <v>2.11</v>
       </c>
       <c r="E72" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="F72" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2371,23 +2373,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Maccabi Netanya vs Hapoel Haifa</t>
+          <t>Stafford Rangers vs Nantwich Town</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="C73" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D73" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="E73" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="F73" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2398,23 +2400,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Hapoel Tel-Aviv vs Hapoel Ramat Gan</t>
+          <t>Chasetown FC vs Kidsgrove Athletic</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.41</v>
+        <v>1.96</v>
       </c>
       <c r="C74" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="D74" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="F74" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2425,23 +2427,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin FC vs Beitar Jerusalem</t>
+          <t>Witton Albion vs Wythenshawe Town</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4.75</v>
+        <v>2.37</v>
       </c>
       <c r="C75" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D75" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="E75" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="F75" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2452,23 +2454,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hapoel Beer-Sheva vs Maccabi Tel-Aviv</t>
+          <t>Hull City U21 vs Brentford U21</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>2.37</v>
+        <v>3.7</v>
       </c>
       <c r="C76" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D76" t="n">
-        <v>2.55</v>
+        <v>1.66</v>
       </c>
       <c r="E76" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="F76" t="n">
-        <v>2.15</v>
+        <v>2.9</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2479,23 +2481,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Bnei-Yehuda Tel-Aviv vs Hapoel Ironi Rishon Lezion</t>
+          <t>Fleetwood Town U21 vs Burnley U21</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.87</v>
+        <v>2.77</v>
       </c>
       <c r="C77" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D77" t="n">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="E77" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="F77" t="n">
-        <v>2.08</v>
+        <v>2.6</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2506,23 +2508,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Maccabi Kiryat Gat Sports Club vs Maccabi Herzliya</t>
+          <t>Racing Santander (W) vs Osasuna (K)</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="C78" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>2.45</v>
+        <v>1.43</v>
       </c>
       <c r="E78" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="F78" t="n">
-        <v>1.81</v>
+        <v>1.97</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2533,23 +2535,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KAFR Qasim vs Ironi Modiin</t>
+          <t>Huesca (W) vs Zaragoza CFF (W)</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="C79" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="D79" t="n">
-        <v>2.59</v>
+        <v>2.4</v>
       </c>
       <c r="E79" t="n">
-        <v>2.27</v>
+        <v>2.06</v>
       </c>
       <c r="F79" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2560,23 +2562,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Malmo FF vs AIK</t>
+          <t>Alhama (K) vs Fundacion Albacete (K)</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="C80" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="E80" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="F80" t="n">
-        <v>2.37</v>
+        <v>2.12</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2587,23 +2589,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Kalmar FF vs Djurgardens IF</t>
+          <t>UD San Fernando vs Orihuela</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4.33</v>
+        <v>2.59</v>
       </c>
       <c r="C81" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="D81" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="E81" t="n">
-        <v>1.66</v>
+        <v>2.06</v>
       </c>
       <c r="F81" t="n">
-        <v>2.07</v>
+        <v>1.64</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2614,23 +2616,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mjallby AIF vs IFK Goteborg</t>
+          <t>Eintracht Trier vs SC Freiburg II</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="C82" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D82" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="E82" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2641,23 +2643,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Orebro SK vs Ostersunds FK</t>
+          <t>FC Astoria Walldorf vs SV Stuttgarter Kickers</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="C83" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D83" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="E83" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="F83" t="n">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2668,23 +2670,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Stjarnan (K) vs Vikingur Reykjavik (K)</t>
+          <t>Kickers Offenbach vs TSV Steinbach</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="C84" t="n">
         <v>3.8</v>
       </c>
       <c r="D84" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="F84" t="n">
         <v>2.9</v>
-      </c>
-      <c r="E84" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="F84" t="n">
-        <v>2.73</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -2695,23 +2697,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Throttur Reykjavik (K) vs Breidablik Kopavogur (K)</t>
+          <t>Estoril U23 vs Famalicao U23</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4.5</v>
+        <v>2.25</v>
       </c>
       <c r="C85" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="D85" t="n">
-        <v>1.51</v>
+        <v>2.54</v>
       </c>
       <c r="E85" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="F85" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -2722,23 +2724,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC vs Cavalry FC</t>
+          <t>Rio Ave U23 vs Torreense U23</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3.8</v>
+        <v>2.01</v>
       </c>
       <c r="C86" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D86" t="n">
-        <v>1.75</v>
+        <v>3.15</v>
       </c>
       <c r="E86" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="F86" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -2749,23 +2751,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Umm Salal vs Al-Khor</t>
+          <t>Portimonense U23 vs FC Felgueiras 1932 U23</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="C87" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="D87" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="E87" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="F87" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -2776,23 +2778,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Al-Gharafa II vs Muaither SC</t>
+          <t>Maritimo U23 vs Gil Vicente FC U23</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="C88" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D88" t="n">
-        <v>1.76</v>
+        <v>1.96</v>
       </c>
       <c r="E88" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="F88" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -2803,23 +2805,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Kairat Almaty (K) vs Tomiris Turan (K)</t>
+          <t>Estrela Da Amadora U23 vs Uniao de Leiria U23</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3.6</v>
+        <v>2.39</v>
       </c>
       <c r="C89" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="D89" t="n">
-        <v>1.76</v>
+        <v>2.6</v>
       </c>
       <c r="E89" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="F89" t="n">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -2830,23 +2832,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Pafos vs Olympiakos Nicosia FC</t>
+          <t>Academico Viseu U23 vs Moreirense FC U23</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1.38</v>
+        <v>1.87</v>
       </c>
       <c r="C90" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D90" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="E90" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="F90" t="n">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -2857,23 +2859,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Aris Limmasol vs Omonia Nicosia</t>
+          <t>NEC Nijmegen vs Excelsior</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3.05</v>
+        <v>1.6</v>
       </c>
       <c r="C91" t="n">
-        <v>3.5</v>
+        <v>4.25</v>
       </c>
       <c r="D91" t="n">
-        <v>1.99</v>
+        <v>4.5</v>
       </c>
       <c r="E91" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="F91" t="n">
-        <v>2.14</v>
+        <v>1.47</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -2884,23 +2886,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Carmelita vs Pitbulls Santa Barbara</t>
+          <t>Atlanta United II vs Connecticut United</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="C92" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="D92" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="E92" t="n">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="F92" t="n">
-        <v>1.93</v>
+        <v>2.73</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -2911,23 +2913,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Limavady United Reserves vs Ballymena United Reserves</t>
+          <t>Toronto Fc Ii vs Columbus Crew II</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1.74</v>
+        <v>2.11</v>
       </c>
       <c r="C93" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D93" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="E93" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="F93" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -2938,23 +2940,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Linfield Reserves vs Portadown Reserves</t>
+          <t>CA Claypole vs CSD Central Ballester</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1.14</v>
+        <v>2.08</v>
       </c>
       <c r="C94" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="D94" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="E94" t="n">
-        <v>1.2</v>
+        <v>2.63</v>
       </c>
       <c r="F94" t="n">
-        <v>4</v>
+        <v>1.41</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -2965,23 +2967,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Asiagoal Bishkek vs FK Kyrgyzaltyn</t>
+          <t>Colon Reserves vs CA Belgrano Cordoba Reserves</t>
         </is>
       </c>
       <c r="B95" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C95" t="n">
+        <v>3</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F95" t="n">
         <v>1.55</v>
-      </c>
-      <c r="C95" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D95" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E95" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="F95" t="n">
-        <v>2.1</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -2992,23 +2994,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Al Ahed vs Al Akhaa Al Ahli</t>
+          <t>Atletico Rafaela Reserves vs Ca Independiente Reserves</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="C96" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="D96" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="E96" t="n">
-        <v>1.41</v>
+        <v>1.87</v>
       </c>
       <c r="F96" t="n">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3019,23 +3021,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>FK RFS vs Liepaja</t>
+          <t>Velez Sarsfield Reserves vs Gimnasia La Plata Reserves</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="C97" t="n">
-        <v>4.75</v>
+        <v>3.8</v>
       </c>
       <c r="D97" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="E97" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="F97" t="n">
-        <v>2.6</v>
+        <v>1.83</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3046,23 +3048,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Riga vs BFC Daugava Daugavpils</t>
+          <t>Racing Club De Avellaneda Reserves vs Argentinos Juniors Reserves</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="D98" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="E98" t="n">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
       <c r="F98" t="n">
-        <v>2.8</v>
+        <v>1.79</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3073,23 +3075,23 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Riga FC II vs Skanstes SK</t>
+          <t>Quilmes Reserves vs Ferro Carril Oeste Reserves</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="C99" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D99" t="n">
-        <v>2.77</v>
+        <v>4.25</v>
       </c>
       <c r="E99" t="n">
-        <v>1.41</v>
+        <v>1.97</v>
       </c>
       <c r="F99" t="n">
-        <v>2.59</v>
+        <v>1.74</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3100,23 +3102,23 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Hegelmann vs Panevezys</t>
+          <t>Central Ballester Reserves vs General Lamadrid Reserves</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="C100" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D100" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="E100" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="F100" t="n">
-        <v>1.79</v>
+        <v>1.99</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3127,23 +3129,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Vilnius FK Zalgiris II vs FK Neptunas Klaipeda</t>
+          <t>CA Lugano Reserves vs Yupanqui Reserves</t>
         </is>
       </c>
       <c r="B101" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="C101" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D101" t="n">
         <v>2.9</v>
       </c>
-      <c r="C101" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D101" t="n">
-        <v>2.06</v>
-      </c>
       <c r="E101" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="F101" t="n">
-        <v>2.11</v>
+        <v>1.72</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3154,23 +3156,23 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Videoton Fehervar vs Diosgyor VTK</t>
+          <t>Lujan Reserves vs Club Sportivo Barracas Reserves</t>
         </is>
       </c>
       <c r="B102" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C102" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D102" t="n">
         <v>2.36</v>
       </c>
-      <c r="C102" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D102" t="n">
-        <v>2.63</v>
-      </c>
       <c r="E102" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="F102" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3181,23 +3183,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Floriana vs Valletta</t>
+          <t>CA Atlas Reserves vs Puerto Nuevo Reserves</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="C103" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D103" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="E103" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="F103" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3208,23 +3210,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>El Qanah FC vs Talaea El Gaish</t>
+          <t>Leandro N. Alem Reserves vs Deportivo Paraguayo Reserves</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="C104" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="D104" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="E104" t="n">
-        <v>2.9</v>
+        <v>1.71</v>
       </c>
       <c r="F104" t="n">
-        <v>1.35</v>
+        <v>2</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3235,23 +3237,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Al Ittihad Al Sakandary vs Asyut Cement Petroleum</t>
+          <t>San Martin Burzaco Reserves vs Arsenal De Sarandi Reserves</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1.76</v>
+        <v>5</v>
       </c>
       <c r="C105" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="D105" t="n">
-        <v>4.75</v>
+        <v>1.47</v>
       </c>
       <c r="E105" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="F105" t="n">
-        <v>1.41</v>
+        <v>2.18</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3262,23 +3264,23 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Petrojet vs Al Masry Club</t>
+          <t>Kingsway Olympic vs Perth Azzurri</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="C106" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F106" t="n">
         <v>3.05</v>
-      </c>
-      <c r="D106" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E106" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="F106" t="n">
-        <v>1.51</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3289,23 +3291,23 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>National Bank of Egypt SC vs Ghazl Al Mehalla</t>
+          <t>Perth SC (W) vs Fremantle City Fc (W)</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="C107" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="D107" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="E107" t="n">
-        <v>2.36</v>
+        <v>1.62</v>
       </c>
       <c r="F107" t="n">
-        <v>1.51</v>
+        <v>2.11</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3316,23 +3318,23 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KFUM 2 vs Lokomotiv Oslo</t>
+          <t>SC Rust vs SV Leithaprodersdorf</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1.64</v>
+        <v>4.2</v>
       </c>
       <c r="C108" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="D108" t="n">
-        <v>3.5</v>
+        <v>1.55</v>
       </c>
       <c r="E108" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="F108" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3343,23 +3345,23 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Molde (A) vs Aalesund FK II</t>
+          <t>Academia de Balompie Boliviano vs San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="C109" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="D109" t="n">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="E109" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="F109" t="n">
-        <v>4.25</v>
+        <v>2.77</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3370,23 +3372,23 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Kvik Trondheim vs Ranheim 2</t>
+          <t>Flamengo RJ U20 vs Forte U20</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>2.63</v>
+        <v>17</v>
       </c>
       <c r="C110" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D110" t="n">
-        <v>2.02</v>
+        <v>1.07</v>
       </c>
       <c r="E110" t="n">
-        <v>1.16</v>
+        <v>1.07</v>
       </c>
       <c r="F110" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3397,23 +3399,23 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Droebak/Frogn vs Lyn Oslo 2</t>
+          <t>EC Bahia U20 vs Atletico Alagoinhas U20</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1.87</v>
+        <v>1.16</v>
       </c>
       <c r="C111" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="D111" t="n">
-        <v>2.8</v>
+        <v>11</v>
       </c>
       <c r="E111" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="F111" t="n">
-        <v>4.25</v>
+        <v>2.73</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3424,23 +3426,23 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Orn Horten vs Sarpsborg 08 2</t>
+          <t>Gremio RS U20 vs Real SC RS U20</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1.64</v>
+        <v>1.1</v>
       </c>
       <c r="C112" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="D112" t="n">
-        <v>3.5</v>
+        <v>13.25</v>
       </c>
       <c r="E112" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="F112" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3451,23 +3453,23 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Gneist vs Aasane Fotball II</t>
+          <t>Atletico Mineiro U20 vs Sobradinho U20</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2.26</v>
+        <v>1.22</v>
       </c>
       <c r="C113" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="D113" t="n">
-        <v>2.37</v>
+        <v>8.5</v>
       </c>
       <c r="E113" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="F113" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3478,23 +3480,23 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Fardu Ferghana vs PFK Aral</t>
+          <t>Athletic Club MG U20 vs Real Brasilia FC U20</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2.7</v>
+        <v>1.51</v>
       </c>
       <c r="C114" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="D114" t="n">
-        <v>2.27</v>
+        <v>4.75</v>
       </c>
       <c r="E114" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="F114" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -3505,23 +3507,23 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Guarani Asuncion vs Deportivo Recoleta</t>
+          <t>Alianca Nacional GO (W) vs Anapolina Saf GO (W)</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1.96</v>
+        <v>3.1</v>
       </c>
       <c r="C115" t="n">
         <v>3.4</v>
       </c>
       <c r="D115" t="n">
-        <v>3.4</v>
+        <v>1.96</v>
       </c>
       <c r="E115" t="n">
-        <v>1.85</v>
+        <v>1.68</v>
       </c>
       <c r="F115" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -3532,23 +3534,23 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense Reserves vs Olimpia Asuncion Reserves</t>
+          <t>Sao Caetano U20 vs Osasco Sporting SP U20</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>4.25</v>
+        <v>2.63</v>
       </c>
       <c r="C116" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="D116" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="E116" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="F116" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3559,23 +3561,23 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Club Libertad Asuncion Reserves vs Rubio Nu Reserve</t>
+          <t>Montana vs Vihren Sandanski</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="C117" t="n">
-        <v>12</v>
+        <v>3.2</v>
       </c>
       <c r="D117" t="n">
-        <v>21</v>
+        <v>2.59</v>
       </c>
       <c r="E117" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="F117" t="n">
-        <v>2.34</v>
+        <v>1.74</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -3586,23 +3588,23 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sportivo Luqueno Reserves vs Sportivo Ameliano Reserves</t>
+          <t>Kolding IF (K) vs Brondby (K)</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="C118" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="D118" t="n">
-        <v>2.26</v>
+        <v>1.35</v>
       </c>
       <c r="E118" t="n">
-        <v>2.02</v>
+        <v>1.37</v>
       </c>
       <c r="F118" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -3613,23 +3615,23 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta (K) vs Club Guarani (K)</t>
+          <t>Brezilya U20 (K) vs Kanada U20 (K)</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>13.25</v>
+        <v>1.94</v>
       </c>
       <c r="C119" t="n">
-        <v>7</v>
+        <v>3.3</v>
       </c>
       <c r="D119" t="n">
-        <v>1.12</v>
+        <v>3.3</v>
       </c>
       <c r="E119" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="F119" t="n">
-        <v>2.9</v>
+        <v>1.8</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -3640,23 +3642,23 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Club Sport Colonial vs General Caballero Campo Grande</t>
+          <t>Benin U20 (K) vs Arjantin U20 (K)</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="C120" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="D120" t="n">
-        <v>11</v>
+        <v>1.51</v>
       </c>
       <c r="E120" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="F120" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -3667,23 +3669,23 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Molinos El Pirata vs Carlos A. Mannucci</t>
+          <t>Polonya U20 (K) vs Meksika U20 (K)</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="C121" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="D121" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="E121" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="F121" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -3694,23 +3696,23 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Wieczysta Krakow vs Zaglebie Lubin</t>
+          <t>İngiltere U20 (K) vs Tanzanya U20 (K)</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="C122" t="n">
-        <v>3.6</v>
+        <v>9</v>
       </c>
       <c r="D122" t="n">
-        <v>3.2</v>
+        <v>21</v>
       </c>
       <c r="E122" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="F122" t="n">
-        <v>2.05</v>
+        <v>2.9</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -3721,23 +3723,23 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Pogon Szczecin vs Wisla Plock</t>
+          <t>FC Bentonit vs Lernayin Artsakh FC</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="C123" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="D123" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="E123" t="n">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="F123" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -3748,23 +3750,23 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>KS Ruch Chorzow vs Unia Skierniewice</t>
+          <t>JK Trans Narva vs Flora Tallinn</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1.68</v>
+        <v>4.5</v>
       </c>
       <c r="C124" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D124" t="n">
-        <v>4.15</v>
+        <v>1.55</v>
       </c>
       <c r="E124" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F124" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -3775,21 +3777,23 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Voluntari vs FC Arges</t>
+          <t>Nomme Kalju vs JK Nomme United</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2.8</v>
+        <v>1.41</v>
       </c>
       <c r="C125" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="D125" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E125" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="E125" t="n">
+        <v>1.41</v>
+      </c>
       <c r="F125" t="n">
-        <v>1.45</v>
+        <v>2.63</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -3800,23 +3804,23 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Universitatea Craiova vs U Cluj</t>
+          <t>Lahti vs Mariehamn</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="C126" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D126" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="E126" t="n">
         <v>1.66</v>
       </c>
       <c r="F126" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -3827,23 +3831,23 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Gazovik Orenburg 2 vs FK Izhevsk</t>
+          <t>Ilves vs Jaro</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>2.27</v>
+        <v>1.62</v>
       </c>
       <c r="C127" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="D127" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="E127" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="F127" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -3854,23 +3858,23 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Rubin Kazan vs Akhmat Grozny</t>
+          <t>VPS vs Oulu</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2.73</v>
+        <v>2.08</v>
       </c>
       <c r="C128" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="D128" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="E128" t="n">
-        <v>2.31</v>
+        <v>1.96</v>
       </c>
       <c r="F128" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -3881,23 +3885,23 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Police Fc (Rwanda) vs Gicumbi FC</t>
+          <t>TPS Turku vs SJK</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1.62</v>
+        <v>2.55</v>
       </c>
       <c r="C129" t="n">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="D129" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="E129" t="n">
-        <v>2.36</v>
+        <v>1.71</v>
       </c>
       <c r="F129" t="n">
-        <v>1.47</v>
+        <v>2.03</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -3908,23 +3912,23 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OFK Belgrade vs IMT Belgrade</t>
+          <t>Gnistan vs KuPS</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2.31</v>
+        <v>3.3</v>
       </c>
       <c r="C130" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="D130" t="n">
-        <v>2.8</v>
+        <v>1.93</v>
       </c>
       <c r="E130" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="F130" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -3935,23 +3939,23 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Vozdovac vs Backa Topola</t>
+          <t>Pepo Lappeenranta vs HIFK</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>2.77</v>
+        <v>1.7</v>
       </c>
       <c r="C131" t="n">
+        <v>4</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E131" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="F131" t="n">
         <v>3.05</v>
-      </c>
-      <c r="D131" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E131" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="F131" t="n">
-        <v>1.6</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -3962,23 +3966,23 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ZFK Spartak Subotica (K) vs ZFK Masinac Nis (K)</t>
+          <t>HPS vs PPJ Helsinki</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1.13</v>
+        <v>2.63</v>
       </c>
       <c r="C132" t="n">
-        <v>7.5</v>
+        <v>3.8</v>
       </c>
       <c r="D132" t="n">
-        <v>12</v>
+        <v>2.08</v>
       </c>
       <c r="E132" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="F132" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -3989,23 +3993,23 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Balestier Khalsa FC II vs Tanjong Pagar II</t>
+          <t>FC Kiffen vs Atlantis FC</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>9.5</v>
+        <v>1.76</v>
       </c>
       <c r="C133" t="n">
-        <v>5.5</v>
+        <v>4.25</v>
       </c>
       <c r="D133" t="n">
-        <v>1.11</v>
+        <v>3.15</v>
       </c>
       <c r="E133" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="F133" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4016,23 +4020,23 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Geylang International II vs FC Jurong II</t>
+          <t>Orbit College vs Lerumo Lions</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="C134" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="D134" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="E134" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="F134" t="n">
-        <v>2.9</v>
+        <v>1.47</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4043,23 +4047,23 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MSK Zilina B vs SK Slovan Bratislava B</t>
+          <t>NK Vardarac vs Hajduk Split</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1.87</v>
+        <v>23</v>
       </c>
       <c r="C135" t="n">
-        <v>3.5</v>
+        <v>13.25</v>
       </c>
       <c r="D135" t="n">
-        <v>3.28</v>
+        <v>1.02</v>
       </c>
       <c r="E135" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="F135" t="n">
-        <v>2.16</v>
+        <v>1.75</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4070,23 +4074,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Raslavice vs Vranov nad Topl'ou</t>
+          <t>NK Zagorec Krapina vs Istra 1961</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1.64</v>
+        <v>21</v>
       </c>
       <c r="C136" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D136" t="n">
-        <v>3.8</v>
+        <v>1.06</v>
       </c>
       <c r="E136" t="n">
-        <v>1.41</v>
+        <v>1.98</v>
       </c>
       <c r="F136" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4097,23 +4101,23 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Radomlje U19 vs NK Aluminij U19</t>
+          <t>Madan vs Mawryngkneng</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2.33</v>
+        <v>1.83</v>
       </c>
       <c r="C137" t="n">
         <v>3.6</v>
       </c>
       <c r="D137" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E137" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F137" t="n">
         <v>2.35</v>
-      </c>
-      <c r="E137" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="F137" t="n">
-        <v>2.77</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4124,23 +4128,23 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>FC Koper U19 vs Olimpija Ljubljana U19</t>
+          <t>Erbil SC vs Diyala FC</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3.8</v>
+        <v>1.81</v>
       </c>
       <c r="C138" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="D138" t="n">
-        <v>1.62</v>
+        <v>3.7</v>
       </c>
       <c r="E138" t="n">
-        <v>1.38</v>
+        <v>1.96</v>
       </c>
       <c r="F138" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4151,23 +4155,23 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NK Celje U19 vs Beltinci U19</t>
+          <t>Duhok vs Ghaz Al Shamal</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="C139" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="D139" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="E139" t="n">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="F139" t="n">
-        <v>2.77</v>
+        <v>1.57</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4178,23 +4182,23 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Jadran Dekani U19 vs Ns Mura U19</t>
+          <t>Mayfield United vs Midleton FC</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2.63</v>
+        <v>3.6</v>
       </c>
       <c r="C140" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D140" t="n">
-        <v>2.12</v>
+        <v>1.79</v>
       </c>
       <c r="E140" t="n">
-        <v>1.47</v>
+        <v>1.78</v>
       </c>
       <c r="F140" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4205,23 +4209,23 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Al-Khaleej vs Al Riyadh</t>
+          <t>Ross County vs Aberdeen FC II</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2.2</v>
+        <v>1.14</v>
       </c>
       <c r="C141" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D141" t="n">
+        <v>11</v>
+      </c>
+      <c r="E141" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F141" t="n">
         <v>3.4</v>
-      </c>
-      <c r="D141" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E141" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F141" t="n">
-        <v>1.95</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4232,23 +4236,23 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Al Hilal Riyadh vs Neom SC</t>
+          <t>Montrose vs Dundee FC II</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="D142" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E142" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="F142" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -4259,23 +4263,23 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Al-Faisaly Harmah U21 vs Al Najma SC U21</t>
+          <t>Annan Athletic vs Motherwell II</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="C143" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="D143" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="E143" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F143" t="n">
         <v>1.62</v>
-      </c>
-      <c r="F143" t="n">
-        <v>2.15</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -4286,23 +4290,23 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Damac U21 vs AL Riyadh SC U21</t>
+          <t>Airdrieonians FC vs St Mirren II</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3.6</v>
+        <v>1.47</v>
       </c>
       <c r="C144" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="D144" t="n">
-        <v>1.81</v>
+        <v>4.75</v>
       </c>
       <c r="E144" t="n">
-        <v>1.78</v>
+        <v>1.38</v>
       </c>
       <c r="F144" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4313,23 +4317,23 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>AL Kholood U21 vs Al Orobah U21</t>
+          <t>Cove Rangers vs Dumbarton</t>
         </is>
       </c>
       <c r="B145" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C145" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D145" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E145" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F145" t="n">
         <v>2.45</v>
-      </c>
-      <c r="C145" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D145" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E145" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F145" t="n">
-        <v>1.95</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4340,23 +4344,23 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>AL Taawoun U21 vs Al Hilal U21</t>
+          <t>Berwick Rangers vs Hibernian B</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="C146" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D146" t="n">
-        <v>1.87</v>
+        <v>2.68</v>
       </c>
       <c r="E146" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="F146" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -4367,23 +4371,23 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Al Adalah vs Al-Saqer FC</t>
+          <t>Formartine United FC vs Dundee Utd II</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="C147" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="D147" t="n">
-        <v>2.31</v>
+        <v>7</v>
       </c>
       <c r="E147" t="n">
-        <v>1.93</v>
+        <v>1.35</v>
       </c>
       <c r="F147" t="n">
-        <v>1.76</v>
+        <v>2.8</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4394,23 +4398,23 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Al Jabalain vs Al Wahda Mecca</t>
+          <t>Peterhead vs Clachnacuddin</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>2.27</v>
+        <v>1.38</v>
       </c>
       <c r="C148" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="D148" t="n">
-        <v>2.73</v>
+        <v>5.5</v>
       </c>
       <c r="E148" t="n">
-        <v>1.81</v>
+        <v>1.33</v>
       </c>
       <c r="F148" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -4421,23 +4425,23 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Al Akhdoud vs Al Najma (SAUD)</t>
+          <t>Elgin City vs Fraserburgh</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2.54</v>
+        <v>1.5</v>
       </c>
       <c r="C149" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="D149" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="E149" t="n">
-        <v>2.14</v>
+        <v>1.43</v>
       </c>
       <c r="F149" t="n">
-        <v>1.6</v>
+        <v>2.58</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -4448,23 +4452,23 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Azam vs Namungo</t>
+          <t>FC Edinburgh vs Queen of the South</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1.22</v>
+        <v>2.63</v>
       </c>
       <c r="C150" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D150" t="n">
-        <v>10</v>
+        <v>2.18</v>
       </c>
       <c r="E150" t="n">
-        <v>1.87</v>
+        <v>1.55</v>
       </c>
       <c r="F150" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -4475,23 +4479,23 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Albion FC vs CA Progreso Montevideo</t>
+          <t>East Kilbride vs Bonnyrigg Rose</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="C151" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="D151" t="n">
-        <v>3.3</v>
+        <v>5.5</v>
       </c>
       <c r="E151" t="n">
-        <v>2.14</v>
+        <v>1.35</v>
       </c>
       <c r="F151" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -4502,23 +4506,23 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ca Penarol Reserves vs Boston River Reserves</t>
+          <t>Cowdenbeath vs Kilmarnock II</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="C152" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D152" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="E152" t="n">
-        <v>1.76</v>
+        <v>1.37</v>
       </c>
       <c r="F152" t="n">
-        <v>1.92</v>
+        <v>2.73</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -4529,23 +4533,23 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Montevideo City Torque Reserve vs Liverpool Montevideo Reserves</t>
+          <t>Banks O'Dee F.C. vs Forfar Athletic</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2.16</v>
+        <v>2.6</v>
       </c>
       <c r="C153" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D153" t="n">
-        <v>2.73</v>
+        <v>2.2</v>
       </c>
       <c r="E153" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="F153" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -4556,23 +4560,23 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Club Oriental Reserves vs Racing Club de Montevideo Reserves</t>
+          <t>Clydebank vs Alloa Athletic</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3.5</v>
+        <v>3.28</v>
       </c>
       <c r="C154" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D154" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="E154" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="F154" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -4583,23 +4587,23 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Colon Montevideo Reserves vs Montevideo Wanderers Reserves</t>
+          <t>Clyde FC vs East Fife</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="C155" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D155" t="n">
-        <v>1.72</v>
+        <v>2.37</v>
       </c>
       <c r="E155" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="F155" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -4610,23 +4614,23 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Cerro Largo FC Reserves vs Defensor Sporting Reserves</t>
+          <t>Stirling Albion vs Glasgow Rangers II</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="C156" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D156" t="n">
-        <v>1.81</v>
+        <v>2.55</v>
       </c>
       <c r="E156" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="F156" t="n">
-        <v>2.27</v>
+        <v>2.8</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -4637,23 +4641,23 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>CA River Plate Montevideo Reserves vs Nacional de Montevideo Reserves</t>
+          <t>Spartans FC vs Hamilton Academical FC</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="C157" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D157" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="E157" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="F157" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -4664,23 +4668,23 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Deportivo Maldonado Reserves vs Juventud De Las Piedras Reserves</t>
+          <t>Gala Fairydean Rovers vs Hearts II</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="C158" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D158" t="n">
-        <v>2.39</v>
+        <v>2.73</v>
       </c>
       <c r="E158" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="F158" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -4691,20 +4695,24 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Nashama Al-Mustaqbal (W) vs Al Orthodoxi (W)</t>
+          <t>Maccabi Herzliya U19 vs Hapoel Kfar Saba U19</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="C159" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="D159" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
+        <v>2.77</v>
+      </c>
+      <c r="E159" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="F159" t="n">
+        <v>1.96</v>
+      </c>
       <c r="G159" t="inlineStr">
         <is>
           <t>-</t>
@@ -4714,23 +4722,23 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Al Hashemeya vs Hayy Al-Amir Hassan</t>
+          <t>Hapoel Tel Aviv U19 vs Ashdod U19</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="C160" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D160" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="E160" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="F160" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -4741,23 +4749,23 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Asteras Tripolis vs Iraklis</t>
+          <t>Maccabi Petach Tikva U19 vs Hapoel Nir Ramat Hasharon U19</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1.93</v>
+        <v>1.12</v>
       </c>
       <c r="C161" t="n">
-        <v>3.3</v>
+        <v>7</v>
       </c>
       <c r="D161" t="n">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="E161" t="n">
-        <v>2.12</v>
+        <v>1.25</v>
       </c>
       <c r="F161" t="n">
-        <v>1.66</v>
+        <v>3.5</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -4768,23 +4776,23 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FC Marko vs Panserraikos</t>
+          <t>Hapoel Kiryat Shmona U19 vs Hapoel Raanana U19</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>3.2</v>
+        <v>1.94</v>
       </c>
       <c r="C162" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D162" t="n">
         <v>3.05</v>
       </c>
-      <c r="D162" t="n">
-        <v>2.12</v>
-      </c>
       <c r="E162" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="F162" t="n">
-        <v>1.53</v>
+        <v>2.27</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -4795,23 +4803,23 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Kallithea vs Niki Volou</t>
+          <t>Bnei Yehuda Tel Aviv U19 vs Hapoel Beer Sheva U19</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="C163" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="D163" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="E163" t="n">
-        <v>2.73</v>
+        <v>1.6</v>
       </c>
       <c r="F163" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -4822,25 +4830,1240 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ellas Syrou vs Apollon Kalamarias</t>
+          <t>Sutjeska Niksic vs Mornar Bar</t>
         </is>
       </c>
       <c r="B164" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C164" t="n">
+        <v>3</v>
+      </c>
+      <c r="D164" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E164" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F164" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Al Mesaimeer SC vs Al Kharitiyath</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C165" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D165" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="E165" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F165" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>AL Shamal U23 vs Al Bidda SC</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C166" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D166" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E166" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="F166" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Astana (K) vs Tobol Kostanay (K)</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D167" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E167" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F167" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Incheon United vs Bucheon 1995</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
         <v>1.97</v>
       </c>
-      <c r="C164" t="n">
+      <c r="C168" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D168" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E168" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="F168" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Ulsan Hyundai Horang-i vs FC Seoul</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
         <v>3.2</v>
       </c>
-      <c r="D164" t="n">
+      <c r="C169" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D169" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E169" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F169" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Larne vs Bangor</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C170" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="D170" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E170" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F170" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Star City FC vs Kedah</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C171" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D171" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E171" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F171" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>El Zamalek vs Abu Qir Semad FC</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C172" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="D172" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E172" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Smouha vs Ceramica Cleopatra FC</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C173" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D173" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F173" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Djerv 1919 vs Haugesund</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>10</v>
+      </c>
+      <c r="C174" t="n">
+        <v>7</v>
+      </c>
+      <c r="D174" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E174" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F174" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Asker Fotball vs Stromsgodset</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>6</v>
+      </c>
+      <c r="C175" t="n">
+        <v>5</v>
+      </c>
+      <c r="D175" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="E175" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F175" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>3 De Noviembre vs Sol de America</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C176" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D176" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E176" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Paraguari AC vs Guairena FC</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D177" t="n">
         <v>3.5</v>
       </c>
-      <c r="E164" t="n">
+      <c r="E177" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F177" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Cerro Porteno Reserve vs Nacional Asunción Reserve</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C178" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E178" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F178" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>KF Drenica Skenderaj vs FC Prishtina</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C179" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D179" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E179" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>KF Vushtrria vs KF Llapi Podujeve</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C180" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D180" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>FC Ryazan vs Spartak Kostroma</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>5</v>
+      </c>
+      <c r="C181" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="E181" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>FK Tekstilshchik Ivanovo vs Arsenal Tula</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C182" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D182" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E182" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Domagnano vs SC Faetano</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="C183" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D183" t="n">
+        <v>8</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="F183" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>SP Tre Penne vs AC Juvenes/Dogana</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C184" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D184" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F184" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Lion City Sailors FC II vs Hougang II</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="C185" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E185" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F185" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Sk Novohrad Lucenec vs Komarno</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>29</v>
+      </c>
+      <c r="C186" t="n">
+        <v>11</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E186" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="F186" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Raca Bratislava vs Samorin</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>7</v>
+      </c>
+      <c r="C187" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E187" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F187" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>MSK Namestovo vs Kinex Bytca</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
         <v>2.15</v>
       </c>
-      <c r="F164" t="n">
+      <c r="C188" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D188" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="E188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F188" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Spartak Medzev vs Zemplin Michalovce</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C189" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D189" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E189" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F189" t="n">
+        <v>3</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Fk Kosicka Nova Ves vs Podbrezova</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="C190" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D190" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E190" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F190" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Mnk Izola vs Tabor Sezana</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C191" t="n">
+        <v>4</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E191" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="F191" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>NK Brezice vs Dravinja</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C192" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E192" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Primorje Ajdovscina vs NK Bilje</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C193" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D193" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E193" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F193" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq Dammam vs Al Faisaly Harmah</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="C194" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D194" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E194" t="n">
         <v>1.6</v>
       </c>
-      <c r="G164" t="inlineStr">
+      <c r="F194" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Al Hazm vs Al Taawon Buraidah</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C195" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D195" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E195" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="F195" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Al-Qadsiah Al Khubar vs Al Ahli Jeddah</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D196" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F196" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Al-Ittihad vs Al Feiha</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="C197" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D197" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Al Zulfi FC vs Hajer</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C198" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D198" t="n">
+        <v>4</v>
+      </c>
+      <c r="E198" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F198" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Damac FC vs Al-Ula</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C199" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D199" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E199" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="F199" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Al-Anwar vs Al Taee Hail</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="C200" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D200" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E200" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F200" t="n">
+        <v>2</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Mashujaa vs Singida BS</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C201" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D201" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E201" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="F201" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Young Africans vs Geita Gold</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C202" t="n">
+        <v>9</v>
+      </c>
+      <c r="D202" t="n">
+        <v>23</v>
+      </c>
+      <c r="E202" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F202" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Bul FC vs Ntugasaze FC</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C203" t="n">
+        <v>4</v>
+      </c>
+      <c r="D203" t="n">
+        <v>8</v>
+      </c>
+      <c r="E203" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="F203" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Maroons Fc vs Blacks Power</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C204" t="n">
+        <v>3</v>
+      </c>
+      <c r="D204" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Kigezi Homeboys vs Kampala City Capital Authority Fc</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="C205" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E205" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="F205" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Fc Olympia Savyntsi vs Kryvbas Kriviy</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>23</v>
+      </c>
+      <c r="C206" t="n">
+        <v>10</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E206" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F206" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Central Espanol Reserves vs Albion Reserves</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="C207" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D207" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E207" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F207" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CA Progreso Reserves vs La Luz Reserves</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C208" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D208" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E208" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Olympiakos vs Volos NFC</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C209" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D209" t="n">
+        <v>17</v>
+      </c>
+      <c r="E209" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F209" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G209" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G209"/>
+  <dimension ref="A1:G218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Club Brugge vs Aston Villa</t>
+          <t>VfB Stuttgart vs Viking</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6</v>
+        <v>6.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="F2" t="n">
-        <v>2.14</v>
+        <v>3.8</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -483,23 +483,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AEK Athens vs LASK Linz</t>
+          <t>Barcelona vs Feyenoord</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.76</v>
+        <v>1.08</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E3" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -510,23 +510,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Porto vs Manchester City</t>
+          <t>Sporting CP vs Galatasaray</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5</v>
+        <v>1.72</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.71</v>
+        <v>4.25</v>
       </c>
       <c r="E4" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -537,23 +537,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lille vs Real Betis</t>
+          <t>Liverpool vs Atletico Madrid</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.22</v>
+        <v>1.74</v>
       </c>
       <c r="C5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>3.05</v>
+        <v>4.15</v>
       </c>
       <c r="E5" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="F5" t="n">
-        <v>1.95</v>
+        <v>2.39</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Borussia Dortmund vs Villarreal</t>
+          <t>Napoli vs Arsenal</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.81</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="D6" t="n">
-        <v>3.8</v>
+        <v>1.62</v>
       </c>
       <c r="E6" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>1.85</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -591,23 +591,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Real Madrid vs Inter</t>
+          <t>PSG vs Slovan Bratislava</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="C7" t="n">
-        <v>4.5</v>
+        <v>13.25</v>
       </c>
       <c r="D7" t="n">
-        <v>4.75</v>
+        <v>34</v>
       </c>
       <c r="E7" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="F7" t="n">
-        <v>2.73</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -618,23 +618,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Fc Porto vs Manchester City U19</t>
+          <t>Sporting Lisbon U19 vs Galatasaray U19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.68</v>
+        <v>1.22</v>
       </c>
       <c r="C8" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.06</v>
+        <v>8.5</v>
       </c>
       <c r="E8" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -645,23 +645,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Club Brugge U19 vs Aston Villa U19</t>
+          <t>Liverpool U19 vs Atletico Madrid U19</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="C9" t="n">
         <v>3.7</v>
       </c>
       <c r="D9" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="E9" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="F9" t="n">
-        <v>2.45</v>
+        <v>2.77</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -672,23 +672,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lille OSC U19 vs Real Betis Balompie Under 19</t>
+          <t>Norwich vs Birmingham</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.3</v>
+        <v>1.92</v>
       </c>
       <c r="C10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D10" t="n">
-        <v>1.81</v>
+        <v>3.7</v>
       </c>
       <c r="E10" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="F10" t="n">
-        <v>2.63</v>
+        <v>1.95</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -699,23 +699,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Real Madrid U19 vs Inter Milan U19</t>
+          <t>Derby County vs West Bromwich</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.37</v>
+        <v>3.1</v>
       </c>
       <c r="C11" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="D11" t="n">
-        <v>5.5</v>
+        <v>2.23</v>
       </c>
       <c r="E11" t="n">
-        <v>1.38</v>
+        <v>1.94</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -726,23 +726,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Borussia Dortmund U19 vs Villarreal CF U19</t>
+          <t>Charlton vs QPR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.12</v>
+        <v>2.9</v>
       </c>
       <c r="C12" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D12" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="E12" t="n">
-        <v>1.43</v>
+        <v>1.95</v>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -753,23 +753,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Watford vs Preston</t>
+          <t>Exmouth Town vs Banbury United</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="C13" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3</v>
+        <v>2.11</v>
       </c>
       <c r="E13" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="F13" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -780,23 +780,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Wrexham vs Burnley</t>
+          <t>AFC Whyteleafe vs Crowborough Athletic</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="C14" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="E14" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="F14" t="n">
-        <v>1.87</v>
+        <v>3.6</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -807,23 +807,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Blackburn vs Sheffield United</t>
+          <t>Bishop Auckland FC vs Emley</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="C15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D15" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="F15" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -834,23 +834,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cardiff vs Stoke</t>
+          <t>Chelsea vs Leeds United</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.04</v>
+        <v>1.5</v>
       </c>
       <c r="C16" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="F16" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -861,23 +861,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Southampton vs Swansea</t>
+          <t>Tamworth vs Middlesbrough U21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="C17" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8</v>
+        <v>2.34</v>
       </c>
       <c r="E17" t="n">
-        <v>1.76</v>
+        <v>1.33</v>
       </c>
       <c r="F17" t="n">
-        <v>1.99</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -888,23 +888,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bolton vs West Ham</t>
+          <t>Coventry United vs Boston Town</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4.75</v>
+        <v>2.07</v>
       </c>
       <c r="C18" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="E18" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="F18" t="n">
-        <v>2.33</v>
+        <v>2.05</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Worcester City vs Knowle FC</t>
+          <t>Corby Town vs Bedworth United</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="C19" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D19" t="n">
-        <v>4.5</v>
+        <v>1.91</v>
       </c>
       <c r="E19" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="F19" t="n">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -942,23 +942,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brentwood Town vs Concord Rangers FC</t>
+          <t>Rugby Borough vs Long Eaton United</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="E20" t="n">
         <v>1.53</v>
       </c>
-      <c r="C20" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.45</v>
-      </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>2.31</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -969,23 +969,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fakenham Town FC vs Ware FC</t>
+          <t>Lichfield City vs Hanley Town FC</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.55</v>
+        <v>7.5</v>
       </c>
       <c r="C21" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>2.23</v>
+        <v>1.25</v>
       </c>
       <c r="E21" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="F21" t="n">
-        <v>2.68</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -996,23 +996,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Havant &amp; Waterloville vs Chippenham Town</t>
+          <t>Blackburn U21 vs Queens Park Rangers U21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.73</v>
+        <v>2.14</v>
       </c>
       <c r="C22" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D22" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="E22" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="F22" t="n">
-        <v>2.04</v>
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1023,23 +1023,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Kettering Town vs Wellingborough Town</t>
+          <t>Getafe (W) vs Pozuelo de Alarcon (W)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1.79</v>
+        <v>2.59</v>
       </c>
       <c r="C23" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D23" t="n">
-        <v>3.7</v>
+        <v>2.27</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="F23" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1050,23 +1050,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Needham Market vs Stanway Rovers</t>
+          <t>Real Oviedo (W) vs Sporting Gijon (W)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="C24" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="D24" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="F24" t="n">
-        <v>2.02</v>
+        <v>2.27</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1077,23 +1077,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Boldmere St Michaels vs Bourne Town FC</t>
+          <t>Elche CF (K) vs Levante (K)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.09</v>
+        <v>7.5</v>
       </c>
       <c r="C25" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>2.9</v>
+        <v>1.28</v>
       </c>
       <c r="E25" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="F25" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1104,23 +1104,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hitchin Town vs Biggleswade Town</t>
+          <t>Balears FC (W) vs Villarreal (K)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.72</v>
+        <v>13</v>
       </c>
       <c r="C26" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="D26" t="n">
-        <v>3.8</v>
+        <v>1.14</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="F26" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1131,23 +1131,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Doncaster vs Huddersfield</t>
+          <t>Sporting de Huelva (W) vs Malaga CF (W)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="C27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D27" t="n">
-        <v>2.2</v>
+        <v>2.73</v>
       </c>
       <c r="E27" t="n">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="F27" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1158,23 +1158,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Exeter vs Tottenham U21</t>
+          <t>Burgos (W) vs Bizkerre (W)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="C28" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="E28" t="n">
-        <v>1.38</v>
+        <v>1.93</v>
       </c>
       <c r="F28" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1185,23 +1185,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Crystal Palace vs Middlesbrough</t>
+          <t>Celta Vigo (W) vs Real Aviles CF (W)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.74</v>
+        <v>1.47</v>
       </c>
       <c r="C29" t="n">
         <v>3.8</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="E29" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="F29" t="n">
-        <v>2.22</v>
+        <v>1.87</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1212,23 +1212,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Leyton Orient vs Bradford</t>
+          <t>Sport Extremadura (W) vs Cacereno (K)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="C30" t="n">
         <v>3.3</v>
       </c>
       <c r="D30" t="n">
-        <v>2.23</v>
+        <v>2.31</v>
       </c>
       <c r="E30" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="F30" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1239,23 +1239,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bournemouth vs Lincoln City</t>
+          <t>CD Samper (W) vs CFF Olympia Las Rozas (W)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="C31" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>2.02</v>
       </c>
       <c r="E31" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="F31" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1266,23 +1266,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sunderland vs Hull City</t>
+          <t>UD Santa Marta vs Vimenor CF</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="C32" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="D32" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="E32" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="F32" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1293,23 +1293,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Millwall vs Newcastle</t>
+          <t>Compostela vs CD Derio</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5.5</v>
+        <v>1.53</v>
       </c>
       <c r="C33" t="n">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="D33" t="n">
-        <v>1.5</v>
+        <v>4.75</v>
       </c>
       <c r="E33" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="F33" t="n">
-        <v>2.23</v>
+        <v>1.9</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1320,23 +1320,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AFC Hornchurch vs Ipswich U21</t>
+          <t>Salamanca CF UDS vs Caudal Deportivo de Mieres</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="C34" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>2.59</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="F34" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1347,23 +1347,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Boreham Wood vs Newcastle U21</t>
+          <t>Comillas CF vs CE L'Hospitalet</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.2</v>
+        <v>3.7</v>
       </c>
       <c r="C35" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="D35" t="n">
-        <v>8.5</v>
+        <v>1.87</v>
       </c>
       <c r="E35" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="F35" t="n">
-        <v>3.3</v>
+        <v>1.62</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1374,23 +1374,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Wealdstone vs Stoke U21</t>
+          <t>Torrent CF vs Saguntino</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.45</v>
+        <v>1.97</v>
       </c>
       <c r="C36" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="D36" t="n">
-        <v>4.75</v>
+        <v>3.15</v>
       </c>
       <c r="E36" t="n">
-        <v>1.32</v>
+        <v>1.79</v>
       </c>
       <c r="F36" t="n">
-        <v>2.9</v>
+        <v>1.91</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1401,23 +1401,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sutton Utd vs Birmingham U21</t>
+          <t>CF Badalona vs Sestao River Club</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="C37" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="D37" t="n">
-        <v>4.75</v>
+        <v>2.03</v>
       </c>
       <c r="E37" t="n">
-        <v>1.35</v>
+        <v>2.02</v>
       </c>
       <c r="F37" t="n">
-        <v>2.77</v>
+        <v>1.68</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1428,23 +1428,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Halifax vs Wolverhampton U21</t>
+          <t>AD San Juan Pamplona vs Terrassa CF</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.76</v>
+        <v>3.7</v>
       </c>
       <c r="C38" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="D38" t="n">
-        <v>3.3</v>
+        <v>1.87</v>
       </c>
       <c r="E38" t="n">
-        <v>1.3</v>
+        <v>2.12</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1455,23 +1455,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Scunthorpe vs Nottingham Forest U21</t>
+          <t>Motril CF vs Recreativo Huelva</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="C39" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="D39" t="n">
-        <v>3.4</v>
+        <v>2.31</v>
       </c>
       <c r="E39" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="F39" t="n">
-        <v>2.45</v>
+        <v>1.84</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1482,23 +1482,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Boston United vs West Brom U21</t>
+          <t>Cacereno vs UD San Pedro</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="C40" t="n">
         <v>3.8</v>
       </c>
       <c r="D40" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="E40" t="n">
-        <v>1.38</v>
+        <v>2.01</v>
       </c>
       <c r="F40" t="n">
-        <v>2.63</v>
+        <v>1.71</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1509,23 +1509,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Solihull Moors vs Leeds U21</t>
+          <t>U.D. Talavera vs Navalcarnero</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="C41" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="D41" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="E41" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="F41" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1536,23 +1536,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gateshead vs Derby U21</t>
+          <t>Grosseto vs Latina</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.92</v>
+        <v>2.18</v>
       </c>
       <c r="C42" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="D42" t="n">
         <v>2.9</v>
       </c>
       <c r="E42" t="n">
-        <v>1.28</v>
+        <v>2.04</v>
       </c>
       <c r="F42" t="n">
-        <v>3.1</v>
+        <v>1.66</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1563,23 +1563,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Braintree vs Fulham U21</t>
+          <t>Bayern Alzenau vs Hanauer SC 1960</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="C43" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D43" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="E43" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="F43" t="n">
-        <v>2.77</v>
+        <v>2.18</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1590,23 +1590,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Worthing vs Norwich City U21</t>
+          <t>FC Turabdin-Babylon Pohlheim vs FSV Fernwald</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="C44" t="n">
         <v>3.6</v>
       </c>
       <c r="D44" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="E44" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="F44" t="n">
-        <v>2.54</v>
+        <v>1.43</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1617,23 +1617,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Aldershot vs West Ham U21</t>
+          <t>FC Teningen vs Turkischer SV Singen</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="C45" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D45" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="E45" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="F45" t="n">
-        <v>2.68</v>
+        <v>2.22</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1644,23 +1644,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Woking vs Southampton U21</t>
+          <t>FC Normannia Gmund vs TSG Backnang</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.83</v>
+        <v>9.5</v>
       </c>
       <c r="C46" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="D46" t="n">
-        <v>3.2</v>
+        <v>1.18</v>
       </c>
       <c r="E46" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="F46" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1671,23 +1671,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Macclesfield Town vs Scarborough Athletic</t>
+          <t>Moreirense vs Benfica</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.75</v>
+        <v>15</v>
       </c>
       <c r="C47" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>3.8</v>
+        <v>1.13</v>
       </c>
       <c r="E47" t="n">
-        <v>1.72</v>
+        <v>1.41</v>
       </c>
       <c r="F47" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1698,23 +1698,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Radcliffe Borough vs Hebburn Town</t>
+          <t>Benfica U23 vs Vizela U23</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2.45</v>
+        <v>1.83</v>
       </c>
       <c r="C48" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D48" t="n">
         <v>3.4</v>
       </c>
-      <c r="D48" t="n">
-        <v>2.39</v>
-      </c>
       <c r="E48" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="F48" t="n">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1725,23 +1725,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Spennymoor Town vs Spalding Utd</t>
+          <t>Twente vs Telstar</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2.55</v>
+        <v>1.27</v>
       </c>
       <c r="C49" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="D49" t="n">
-        <v>2.37</v>
+        <v>8.5</v>
       </c>
       <c r="E49" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="F49" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1752,23 +1752,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Worksop Town vs Bedford Town</t>
+          <t>Inter Club d'Escaldes vs Atletic Club d'Escaldes</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="C50" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D50" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="E50" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="F50" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1779,23 +1779,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Chorley vs Darlington</t>
+          <t>FC Cabinda vs Primeiro de Agosto</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.16</v>
+        <v>7</v>
       </c>
       <c r="C51" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="D51" t="n">
-        <v>2.77</v>
+        <v>1.41</v>
       </c>
       <c r="E51" t="n">
-        <v>1.62</v>
+        <v>2.23</v>
       </c>
       <c r="F51" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1806,23 +1806,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Southport vs Morecambe</t>
+          <t>CA Defensores de Belgrano vs CA Los Andes</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C52" t="n">
         <v>2.8</v>
       </c>
-      <c r="C52" t="n">
-        <v>3.3</v>
-      </c>
       <c r="D52" t="n">
-        <v>2.16</v>
+        <v>3.7</v>
       </c>
       <c r="E52" t="n">
-        <v>1.79</v>
+        <v>2.9</v>
       </c>
       <c r="F52" t="n">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1833,23 +1833,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Buxton vs Brackley</t>
+          <t>Ca Platense Reserves vs Boca Juniors Reserves</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.68</v>
+        <v>5</v>
       </c>
       <c r="C53" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>1.57</v>
       </c>
       <c r="E53" t="n">
-        <v>1.64</v>
+        <v>2.2</v>
       </c>
       <c r="F53" t="n">
-        <v>2.08</v>
+        <v>1.58</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -1860,23 +1860,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>South Shields vs Marine</t>
+          <t>San Martin de San Juan Reserves vs Defensa Y Justicia Reserves</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.43</v>
+        <v>4</v>
       </c>
       <c r="C54" t="n">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>1.66</v>
       </c>
       <c r="E54" t="n">
-        <v>1.47</v>
+        <v>1.64</v>
       </c>
       <c r="F54" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -1887,23 +1887,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kings Lynn vs Hednesford Town</t>
+          <t>San Lorenzo Reserves vs Union Santa Fe Reserves</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="C55" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
         <v>2.8</v>
       </c>
       <c r="E55" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="F55" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -1914,23 +1914,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Harborough Town vs Hereford</t>
+          <t>Instituto AC Cordoba Reserves vs CA Sarmiento Reserves</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="C56" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="E56" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="F56" t="n">
         <v>1.51</v>
-      </c>
-      <c r="F56" t="n">
-        <v>2.33</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -1941,23 +1941,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Chester vs Merthyr Town</t>
+          <t>Ca Talleres De Cordoba Reserves vs Barracas Central Reserves</t>
         </is>
       </c>
       <c r="B57" t="n">
         <v>1.6</v>
       </c>
       <c r="C57" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D57" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="E57" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="F57" t="n">
-        <v>2.12</v>
+        <v>1.74</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -1968,23 +1968,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Telford vs Oxford City</t>
+          <t>Canuelas FC Reserves vs Victoriano Arenas Reserves</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="C58" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="D58" t="n">
-        <v>2.73</v>
+        <v>7</v>
       </c>
       <c r="E58" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="F58" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -1995,23 +1995,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Maidenhead United vs Torquay United</t>
+          <t>Sacachispas Reserves vs El Porvenir Reserves</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="C59" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="D59" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="E59" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="F59" t="n">
-        <v>2.03</v>
+        <v>1.93</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2022,23 +2022,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Weston-super-Mare vs AFC Totton</t>
+          <t>Club Comunicaciones Reserves vs Deportivo Armenio Reserves</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="C60" t="n">
         <v>3.6</v>
       </c>
       <c r="D60" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="E60" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="F60" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2049,23 +2049,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Dagenham &amp; Redbridge vs Dover Athletic</t>
+          <t>Deportivo Merlo Reserves vs Deportivo Laferrere Reserves</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1.45</v>
+        <v>2.02</v>
       </c>
       <c r="C61" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="E61" t="n">
-        <v>1.43</v>
+        <v>1.96</v>
       </c>
       <c r="F61" t="n">
-        <v>2.58</v>
+        <v>1.72</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2076,23 +2076,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ebbsfleet United vs Hemel Hempstead Town</t>
+          <t>CS Dock Sud Reserves vs CA Brown de Adrogue Reserves</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="C62" t="n">
         <v>3.4</v>
       </c>
       <c r="D62" t="n">
-        <v>3.7</v>
+        <v>4.33</v>
       </c>
       <c r="E62" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="F62" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2103,23 +2103,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Tonbridge Angels vs Maidstone Utd</t>
+          <t>Defensores Unidos Reserves vs Flandria Reserves</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2.73</v>
+        <v>3.7</v>
       </c>
       <c r="C63" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D63" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="E63" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="F63" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2130,23 +2130,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Chesham United vs Billericay Town</t>
+          <t>CDT Real Oruro vs Nacional Potosi</t>
         </is>
       </c>
       <c r="B64" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D64" t="n">
         <v>1.96</v>
       </c>
-      <c r="C64" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D64" t="n">
-        <v>3.2</v>
-      </c>
       <c r="E64" t="n">
-        <v>1.78</v>
+        <v>1.43</v>
       </c>
       <c r="F64" t="n">
-        <v>1.92</v>
+        <v>2.59</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2157,23 +2157,21 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dorking Wanderers vs Chelmsford City</t>
+          <t>FK Zeljeznicar Sarajevo vs Sarajevo</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2.02</v>
+        <v>3.28</v>
       </c>
       <c r="C65" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="D65" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E65" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="n">
         <v>1.45</v>
-      </c>
-      <c r="F65" t="n">
-        <v>2.45</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2184,23 +2182,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Hampton &amp; Richmond Borough vs Farnborough</t>
+          <t>Cruzeiro EC U20 vs Guanabara City GO U20</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="C66" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="D66" t="n">
-        <v>2.27</v>
+        <v>19</v>
       </c>
       <c r="E66" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="F66" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2211,23 +2209,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Salisbury vs Slough Town</t>
+          <t>Fortaleza CE U20 vs Piaui U20</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="C67" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E67" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="F67" t="n">
-        <v>2.9</v>
+        <v>2.16</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2238,23 +2236,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Folkestone Invicta vs Horsham</t>
+          <t>Botafogo RJ U20 vs EC Estrela de Marco U20</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.94</v>
+        <v>1.16</v>
       </c>
       <c r="C68" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F68" t="n">
         <v>3.2</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="F68" t="n">
-        <v>2.07</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2265,23 +2263,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>West Auckland Town vs Ossett United</t>
+          <t>Nautico U20 vs America PE U20</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="C69" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D69" t="n">
-        <v>2.73</v>
+        <v>8.5</v>
       </c>
       <c r="E69" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="F69" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2292,23 +2290,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Bradford Park Avenue vs Silsden</t>
+          <t>Criciuma U20 vs Cascavel U20</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="C70" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="D70" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="E70" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="F70" t="n">
-        <v>2.27</v>
+        <v>1.93</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2319,23 +2317,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Garforth Town vs Beverley Town FC</t>
+          <t>Internacional Rs U20 vs Barra FC SC U20</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.72</v>
+        <v>1.43</v>
       </c>
       <c r="C71" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="D71" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
       <c r="E71" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="F71" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2346,23 +2344,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mossley vs Clitheroe</t>
+          <t>Paysandu U20 vs EC Macapa U20</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2.8</v>
+        <v>1.27</v>
       </c>
       <c r="C72" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D72" t="n">
-        <v>2.11</v>
+        <v>8</v>
       </c>
       <c r="E72" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="F72" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2373,23 +2371,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Stafford Rangers vs Nantwich Town</t>
+          <t>America RN U20 vs Quinho Futebol Clube U20</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="C73" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D73" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="F73" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2400,23 +2398,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Chasetown FC vs Kidsgrove Athletic</t>
+          <t>Tuna Luso PA U20 vs Batalhao U20</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.96</v>
+        <v>1.38</v>
       </c>
       <c r="C74" t="n">
-        <v>3.6</v>
+        <v>4.25</v>
       </c>
       <c r="D74" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="E74" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="F74" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2427,23 +2425,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Witton Albion vs Wythenshawe Town</t>
+          <t>CS Alagoano U20 vs Confianca EC PB U20</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2.37</v>
+        <v>1.55</v>
       </c>
       <c r="C75" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D75" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="E75" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="F75" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2454,23 +2452,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hull City U21 vs Brentford U21</t>
+          <t>Ceara SC CE U20 vs Atletico Piauiense U20</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>3.7</v>
+        <v>1.41</v>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="D76" t="n">
-        <v>1.66</v>
+        <v>5.5</v>
       </c>
       <c r="E76" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="F76" t="n">
-        <v>2.9</v>
+        <v>2.11</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2481,23 +2479,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Fleetwood Town U21 vs Burnley U21</t>
+          <t>Santa Cruz PE U20 vs CS Esportiva U20</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2.77</v>
+        <v>1.62</v>
       </c>
       <c r="C77" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="D77" t="n">
-        <v>2.07</v>
+        <v>4.33</v>
       </c>
       <c r="E77" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="F77" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2508,23 +2506,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Racing Santander (W) vs Osasuna (K)</t>
+          <t>Goias EC U20 vs Trindade U20</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5.5</v>
+        <v>1.6</v>
       </c>
       <c r="C78" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="D78" t="n">
-        <v>1.43</v>
+        <v>4.33</v>
       </c>
       <c r="E78" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="F78" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2535,23 +2533,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Huesca (W) vs Zaragoza CFF (W)</t>
+          <t>Atletico Mineiro (K) vs Itabirito (W)</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>2.6</v>
+        <v>1.37</v>
       </c>
       <c r="C79" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="D79" t="n">
-        <v>2.4</v>
+        <v>6</v>
       </c>
       <c r="E79" t="n">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="F79" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2562,23 +2560,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alhama (K) vs Fundacion Albacete (K)</t>
+          <t>ABC RN U20 vs Assu U20</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1.6</v>
+        <v>2.25</v>
       </c>
       <c r="C80" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D80" t="n">
-        <v>4.25</v>
+        <v>2.45</v>
       </c>
       <c r="E80" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="F80" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2589,23 +2587,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>UD San Fernando vs Orihuela</t>
+          <t>Perolas Negras U20 vs Bonsucesso U20</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2.59</v>
+        <v>1.66</v>
       </c>
       <c r="C81" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="D81" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="E81" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="F81" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2616,23 +2614,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Eintracht Trier vs SC Freiburg II</t>
+          <t>Resende RJ U20 vs Olaria RJ U20</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="C82" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="D82" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="E82" t="n">
-        <v>1.51</v>
+        <v>2.23</v>
       </c>
       <c r="F82" t="n">
-        <v>2.37</v>
+        <v>1.57</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2643,23 +2641,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>FC Astoria Walldorf vs SV Stuttgarter Kickers</t>
+          <t>CEAC Araruama U20 vs Audax Rio RJ U20</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="C83" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D83" t="n">
-        <v>2.06</v>
+        <v>2.59</v>
       </c>
       <c r="E83" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="F83" t="n">
-        <v>2.31</v>
+        <v>2.12</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2670,23 +2668,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Kickers Offenbach vs TSV Steinbach</t>
+          <t>Sao Goncalo U20 vs Serrano RJ U20</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="C84" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="D84" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="E84" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="F84" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -2697,23 +2695,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Estoril U23 vs Famalicao U23</t>
+          <t>Americano RJ U20 vs America RJ U20</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="C85" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="D85" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="E85" t="n">
-        <v>1.47</v>
+        <v>1.81</v>
       </c>
       <c r="F85" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -2724,23 +2722,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Rio Ave U23 vs Torreense U23</t>
+          <t>Levski Sofia vs CSKA Sofia</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2.01</v>
+        <v>1.86</v>
       </c>
       <c r="C86" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D86" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="E86" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="F86" t="n">
-        <v>1.93</v>
+        <v>1.62</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -2751,23 +2749,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Portimonense U23 vs FC Felgueiras 1932 U23</t>
+          <t>Jablonec vs Banik Ostrava</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="C87" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D87" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="E87" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="F87" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -2778,23 +2776,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Maritimo U23 vs Gil Vicente FC U23</t>
+          <t>Hradec Kralove vs Viktoria Plzen</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="C88" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D88" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="E88" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="F88" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -2805,23 +2803,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Estrela Da Amadora U23 vs Uniao de Leiria U23</t>
+          <t>Prostejov vs Sigma Olomouc</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2.39</v>
+        <v>6</v>
       </c>
       <c r="C89" t="n">
-        <v>3.2</v>
+        <v>4.25</v>
       </c>
       <c r="D89" t="n">
-        <v>2.6</v>
+        <v>1.38</v>
       </c>
       <c r="E89" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="F89" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -2832,23 +2830,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Academico Viseu U23 vs Moreirense FC U23</t>
+          <t>Viktoria Zizkov vs Sparta Prague</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1.87</v>
+        <v>8</v>
       </c>
       <c r="C90" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D90" t="n">
-        <v>3.3</v>
+        <v>1.25</v>
       </c>
       <c r="E90" t="n">
-        <v>1.66</v>
+        <v>1.33</v>
       </c>
       <c r="F90" t="n">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -2859,23 +2857,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NEC Nijmegen vs Excelsior</t>
+          <t>VSK Arhus vs Lyngby</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1.6</v>
+        <v>7.5</v>
       </c>
       <c r="C91" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="D91" t="n">
-        <v>4.5</v>
+        <v>1.32</v>
       </c>
       <c r="E91" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="F91" t="n">
-        <v>1.47</v>
+        <v>2.22</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -2886,23 +2884,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Atlanta United II vs Connecticut United</t>
+          <t>Vanlose vs Hillerod</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2.06</v>
+        <v>4.33</v>
       </c>
       <c r="C92" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D92" t="n">
-        <v>2.73</v>
+        <v>1.6</v>
       </c>
       <c r="E92" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="F92" t="n">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -2913,23 +2911,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Toronto Fc Ii vs Columbus Crew II</t>
+          <t>BK Frem vs Roskilde</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>2.11</v>
+        <v>3.4</v>
       </c>
       <c r="C93" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="D93" t="n">
-        <v>2.7</v>
+        <v>1.86</v>
       </c>
       <c r="E93" t="n">
-        <v>1.43</v>
+        <v>1.72</v>
       </c>
       <c r="F93" t="n">
-        <v>2.6</v>
+        <v>1.98</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -2940,23 +2938,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CA Claypole vs CSD Central Ballester</t>
+          <t>Nykobing vs Middelfart</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="C94" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="D94" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="E94" t="n">
-        <v>2.63</v>
+        <v>1.47</v>
       </c>
       <c r="F94" t="n">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -2967,23 +2965,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Colon Reserves vs CA Belgrano Cordoba Reserves</t>
+          <t>Kolding BK vs Odense</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>2.68</v>
+        <v>3.3</v>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D95" t="n">
-        <v>2.37</v>
+        <v>1.87</v>
       </c>
       <c r="E95" t="n">
-        <v>2.22</v>
+        <v>1.72</v>
       </c>
       <c r="F95" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -2994,23 +2992,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Atletico Rafaela Reserves vs Ca Independiente Reserves</t>
+          <t>Aalborg U19 vs Vejle U19</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="C96" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D96" t="n">
-        <v>1.7</v>
+        <v>2.27</v>
       </c>
       <c r="E96" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="F96" t="n">
-        <v>1.79</v>
+        <v>3</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3021,23 +3019,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Velez Sarsfield Reserves vs Gimnasia La Plata Reserves</t>
+          <t>Fransa U20 (K) vs Ekvador U20 (K)</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="C97" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="D97" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="E97" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="F97" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3048,23 +3046,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Racing Club De Avellaneda Reserves vs Argentinos Juniors Reserves</t>
+          <t>Japonya U20 (K) vs ABD U20 (K)</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2.2</v>
+        <v>1.87</v>
       </c>
       <c r="C98" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="D98" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="E98" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="F98" t="n">
         <v>1.87</v>
-      </c>
-      <c r="F98" t="n">
-        <v>1.79</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3075,23 +3073,23 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Quilmes Reserves vs Ferro Carril Oeste Reserves</t>
+          <t>JK Tammeka Tartu vs Paide Linnameeskond</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1.68</v>
+        <v>2.9</v>
       </c>
       <c r="C99" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D99" t="n">
-        <v>4.25</v>
+        <v>2.02</v>
       </c>
       <c r="E99" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="F99" t="n">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3102,23 +3100,23 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Central Ballester Reserves vs General Lamadrid Reserves</t>
+          <t>Levadia Tallinn vs FC Kuressaare</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2.36</v>
+        <v>1.12</v>
       </c>
       <c r="C100" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="D100" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="E100" t="n">
-        <v>1.72</v>
+        <v>1.22</v>
       </c>
       <c r="F100" t="n">
-        <v>1.99</v>
+        <v>3.6</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3129,23 +3127,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>CA Lugano Reserves vs Yupanqui Reserves</t>
+          <t>Parnu JK Vaprus vs Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="C101" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="D101" t="n">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="E101" t="n">
-        <v>1.97</v>
+        <v>1.5</v>
       </c>
       <c r="F101" t="n">
-        <v>1.72</v>
+        <v>2.39</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3156,20 +3154,20 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Lujan Reserves vs Club Sportivo Barracas Reserves</t>
+          <t>HJK vs Inter Turku</t>
         </is>
       </c>
       <c r="B102" t="n">
         <v>2.5</v>
       </c>
       <c r="C102" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="D102" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="E102" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="F102" t="n">
         <v>1.87</v>
@@ -3183,23 +3181,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CA Atlas Reserves vs Puerto Nuevo Reserves</t>
+          <t>Lautp vs Kultsu</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>2.08</v>
+        <v>6</v>
       </c>
       <c r="C103" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="D103" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="E103" t="n">
-        <v>1.83</v>
+        <v>1.14</v>
       </c>
       <c r="F103" t="n">
-        <v>1.85</v>
+        <v>4.33</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3210,23 +3208,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Leandro N. Alem Reserves vs Deportivo Paraguayo Reserves</t>
+          <t>KPV Akatemia vs Nykarleby</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>2.35</v>
+        <v>1.76</v>
       </c>
       <c r="C104" t="n">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="D104" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="E104" t="n">
-        <v>1.71</v>
+        <v>1.18</v>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3237,23 +3235,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>San Martin Burzaco Reserves vs Arsenal De Sarandi Reserves</t>
+          <t>KuPS Akatemia II vs PK-37</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>5</v>
+        <v>2.31</v>
       </c>
       <c r="C105" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D105" t="n">
-        <v>1.47</v>
+        <v>2.31</v>
       </c>
       <c r="E105" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="F105" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3264,23 +3262,23 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Kingsway Olympic vs Perth Azzurri</t>
+          <t>Lepa vs GrIFK Reservi</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="C106" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D106" t="n">
         <v>3.8</v>
       </c>
-      <c r="D106" t="n">
-        <v>2.27</v>
-      </c>
       <c r="E106" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="F106" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3291,23 +3289,23 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Perth SC (W) vs Fremantle City Fc (W)</t>
+          <t>Mamelodi Sundowns vs Siwelele</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="C107" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D107" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E107" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="F107" t="n">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3318,23 +3316,23 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SC Rust vs SV Leithaprodersdorf</t>
+          <t>FC Spaeri vs FC Rustavi</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="C108" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="D108" t="n">
-        <v>1.55</v>
+        <v>2.16</v>
       </c>
       <c r="E108" t="n">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="F108" t="n">
-        <v>3.05</v>
+        <v>1.76</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3345,23 +3343,23 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Academia de Balompie Boliviano vs San Antonio Bulo Bulo</t>
+          <t>FC Samgurali Tskaltubo vs Dila Gori</t>
         </is>
       </c>
       <c r="B109" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C109" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D109" t="n">
         <v>2.36</v>
       </c>
-      <c r="C109" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D109" t="n">
-        <v>2.33</v>
-      </c>
       <c r="E109" t="n">
-        <v>1.37</v>
+        <v>2.11</v>
       </c>
       <c r="F109" t="n">
-        <v>2.77</v>
+        <v>1.64</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3372,23 +3370,23 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Flamengo RJ U20 vs Forte U20</t>
+          <t>FC Dinamo Batumi vs Iberia 1999</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>17</v>
+        <v>1.87</v>
       </c>
       <c r="C110" t="n">
-        <v>36</v>
+        <v>3.4</v>
       </c>
       <c r="D110" t="n">
-        <v>1.07</v>
+        <v>3.4</v>
       </c>
       <c r="E110" t="n">
-        <v>1.07</v>
+        <v>1.79</v>
       </c>
       <c r="F110" t="n">
-        <v>6.5</v>
+        <v>1.91</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3399,23 +3397,23 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>EC Bahia U20 vs Atletico Alagoinhas U20</t>
+          <t>HNK Segesta Sisak vs Osijek</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1.16</v>
+        <v>4.5</v>
       </c>
       <c r="C111" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="D111" t="n">
-        <v>11</v>
+        <v>1.57</v>
       </c>
       <c r="E111" t="n">
-        <v>1.38</v>
+        <v>1.64</v>
       </c>
       <c r="F111" t="n">
-        <v>2.73</v>
+        <v>2.11</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3426,23 +3424,23 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Gremio RS U20 vs Real SC RS U20</t>
+          <t>Zagora Unesic vs Varazdin</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1.1</v>
+        <v>10</v>
       </c>
       <c r="C112" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="D112" t="n">
-        <v>13.25</v>
+        <v>1.16</v>
       </c>
       <c r="E112" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="F112" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3453,17 +3451,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Atletico Mineiro U20 vs Sobradinho U20</t>
+          <t>NK Tomislav Cerna vs Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1.22</v>
+        <v>15</v>
       </c>
       <c r="C113" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="D113" t="n">
-        <v>8.5</v>
+        <v>1.11</v>
       </c>
       <c r="E113" t="n">
         <v>1.28</v>
@@ -3480,23 +3478,23 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Athletic Club MG U20 vs Real Brasilia FC U20</t>
+          <t>Vukovar 1991 vs HNK Cibalia Vinkovci</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1.51</v>
+        <v>2.01</v>
       </c>
       <c r="C114" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="D114" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="E114" t="n">
-        <v>1.66</v>
+        <v>1.96</v>
       </c>
       <c r="F114" t="n">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -3507,23 +3505,23 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Alianca Nacional GO (W) vs Anapolina Saf GO (W)</t>
+          <t>NK Bedem Ivankovo vs Dinamo Zagreb</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3.1</v>
+        <v>61</v>
       </c>
       <c r="C115" t="n">
-        <v>3.4</v>
+        <v>23</v>
       </c>
       <c r="D115" t="n">
-        <v>1.96</v>
+        <v>1.08</v>
       </c>
       <c r="E115" t="n">
-        <v>1.68</v>
+        <v>1.08</v>
       </c>
       <c r="F115" t="n">
-        <v>2.03</v>
+        <v>6</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -3534,23 +3532,23 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sao Caetano U20 vs Osasco Sporting SP U20</t>
+          <t>NK Uskok vs Gorica</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>2.63</v>
+        <v>6.5</v>
       </c>
       <c r="C116" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="D116" t="n">
-        <v>2.25</v>
+        <v>1.35</v>
       </c>
       <c r="E116" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="F116" t="n">
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3561,23 +3559,23 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Montana vs Vihren Sandanski</t>
+          <t>NK Hrvatski Dragovoljac vs Slaven Belupo</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>2.4</v>
+        <v>12</v>
       </c>
       <c r="C117" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="D117" t="n">
-        <v>2.59</v>
+        <v>1.16</v>
       </c>
       <c r="E117" t="n">
-        <v>1.96</v>
+        <v>1.38</v>
       </c>
       <c r="F117" t="n">
-        <v>1.74</v>
+        <v>2.77</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -3588,23 +3586,23 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Kolding IF (K) vs Brondby (K)</t>
+          <t>Orijent 1919 vs NK Mladost Zdralovi</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>6</v>
+        <v>2.3</v>
       </c>
       <c r="C118" t="n">
-        <v>4.5</v>
+        <v>3.15</v>
       </c>
       <c r="D118" t="n">
-        <v>1.35</v>
+        <v>2.77</v>
       </c>
       <c r="E118" t="n">
-        <v>1.37</v>
+        <v>2.07</v>
       </c>
       <c r="F118" t="n">
-        <v>2.8</v>
+        <v>1.66</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -3615,23 +3613,23 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Brezilya U20 (K) vs Kanada U20 (K)</t>
+          <t>NK Koprivnica vs Rudes Zagreb</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1.94</v>
+        <v>10</v>
       </c>
       <c r="C119" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D119" t="n">
-        <v>3.3</v>
+        <v>1.22</v>
       </c>
       <c r="E119" t="n">
-        <v>1.9</v>
+        <v>2.07</v>
       </c>
       <c r="F119" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -3642,23 +3640,23 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Benin U20 (K) vs Arjantin U20 (K)</t>
+          <t>Al Jolan SC vs Zakho</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="C120" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="D120" t="n">
-        <v>1.51</v>
+        <v>2.2</v>
       </c>
       <c r="E120" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F120" t="n">
         <v>1.47</v>
-      </c>
-      <c r="F120" t="n">
-        <v>2.45</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -3669,23 +3667,23 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Polonya U20 (K) vs Meksika U20 (K)</t>
+          <t>Al Talaba Fc vs Al-Karkh</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>2.27</v>
+        <v>1.95</v>
       </c>
       <c r="C121" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="D121" t="n">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="E121" t="n">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="F121" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -3696,23 +3694,23 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>İngiltere U20 (K) vs Tanzanya U20 (K)</t>
+          <t>Al Minaa vs Naft Maysan</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.07</v>
+        <v>2.18</v>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>3.1</v>
       </c>
       <c r="D122" t="n">
-        <v>21</v>
+        <v>2.9</v>
       </c>
       <c r="E122" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="F122" t="n">
-        <v>2.9</v>
+        <v>1.64</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -3723,23 +3721,23 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>FC Bentonit vs Lernayin Artsakh FC</t>
+          <t>Newroz SC vs Mosul FC</t>
         </is>
       </c>
       <c r="B123" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="C123" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E123" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F123" t="n">
         <v>1.72</v>
-      </c>
-      <c r="C123" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D123" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E123" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="F123" t="n">
-        <v>2.26</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -3750,23 +3748,23 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>JK Trans Narva vs Flora Tallinn</t>
+          <t>Al Karma vs Al Naft</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>4.5</v>
+        <v>1.76</v>
       </c>
       <c r="C124" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="D124" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F124" t="n">
         <v>1.55</v>
-      </c>
-      <c r="E124" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F124" t="n">
-        <v>2.18</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -3777,23 +3775,23 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Nomme Kalju vs JK Nomme United</t>
+          <t>Rangers vs St Mirren</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="C125" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="E125" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="F125" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -3804,23 +3802,23 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Lahti vs Mariehamn</t>
+          <t>St. Johnstone vs Celtic</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1.58</v>
+        <v>5.5</v>
       </c>
       <c r="C126" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="D126" t="n">
-        <v>5</v>
+        <v>1.47</v>
       </c>
       <c r="E126" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="F126" t="n">
-        <v>2.11</v>
+        <v>2.35</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -3831,23 +3829,23 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Ilves vs Jaro</t>
+          <t>Hapoel Rishon Lezion U19 vs Maccabi Netanya U19</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1.62</v>
+        <v>5</v>
       </c>
       <c r="C127" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="D127" t="n">
-        <v>4.5</v>
+        <v>1.47</v>
       </c>
       <c r="E127" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="F127" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -3858,23 +3856,23 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>VPS vs Oulu</t>
+          <t>Hapoel Azor vs MS Tzeirey Tira</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="C128" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D128" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="E128" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="F128" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -3885,23 +3883,23 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TPS Turku vs SJK</t>
+          <t>Hapoel Ramat Hasharon vs Hapoel Mahane Yehuda</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="C129" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D129" t="n">
-        <v>2.45</v>
+        <v>4.25</v>
       </c>
       <c r="E129" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="F129" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -3912,23 +3910,23 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Gnistan vs KuPS</t>
+          <t>Sport Club Dimona vs Maccabi Yavne</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="C130" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D130" t="n">
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="E130" t="n">
-        <v>1.58</v>
+        <v>1.97</v>
       </c>
       <c r="F130" t="n">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -3939,23 +3937,23 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Pepo Lappeenranta vs HIFK</t>
+          <t>Sderot FC vs Maccabi Kiryat Malakhi</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="C131" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="D131" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="E131" t="n">
-        <v>1.32</v>
+        <v>1.87</v>
       </c>
       <c r="F131" t="n">
-        <v>3.05</v>
+        <v>1.81</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -3966,23 +3964,23 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>HPS vs PPJ Helsinki</t>
+          <t>Hapoel Hadera vs Shimshon Tel Aviv</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="C132" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="D132" t="n">
-        <v>2.08</v>
+        <v>2.54</v>
       </c>
       <c r="E132" t="n">
-        <v>1.3</v>
+        <v>1.94</v>
       </c>
       <c r="F132" t="n">
-        <v>3.15</v>
+        <v>1.75</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -3993,23 +3991,23 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>FC Kiffen vs Atlantis FC</t>
+          <t>Hapoel Tzafririm Holon vs Hapoel Marmorek</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="C133" t="n">
-        <v>4.25</v>
+        <v>3</v>
       </c>
       <c r="D133" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="E133" t="n">
-        <v>1.18</v>
+        <v>2.26</v>
       </c>
       <c r="F133" t="n">
-        <v>4.33</v>
+        <v>1.55</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4020,23 +4018,23 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Orbit College vs Lerumo Lions</t>
+          <t>Ironi Beit Shemesh vs Kfar Saba 1928</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2.07</v>
+        <v>2.73</v>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D134" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="E134" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="F134" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4047,23 +4045,23 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NK Vardarac vs Hajduk Split</t>
+          <t>FC Jerusalem vs Maccabi Ashdod</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>23</v>
+        <v>1.53</v>
       </c>
       <c r="C135" t="n">
-        <v>13.25</v>
+        <v>3.8</v>
       </c>
       <c r="D135" t="n">
-        <v>1.02</v>
+        <v>4.75</v>
       </c>
       <c r="E135" t="n">
-        <v>1.98</v>
+        <v>1.66</v>
       </c>
       <c r="F135" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4074,23 +4072,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NK Zagorec Krapina vs Istra 1961</t>
+          <t>Hapoel Herzliya vs Agudat Sport Nordia Jerusalem</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>21</v>
+        <v>1.47</v>
       </c>
       <c r="C136" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="D136" t="n">
-        <v>1.06</v>
+        <v>5.5</v>
       </c>
       <c r="E136" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="F136" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4101,23 +4099,23 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Madan vs Mawryngkneng</t>
+          <t>Hapoel Umm Al Fahm vs Fc Tzeirei Tamra</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="C137" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="D137" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="E137" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="F137" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4128,23 +4126,23 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Erbil SC vs Diyala FC</t>
+          <t>Hapoel Ironi Baqa Al-Gharbiyye vs Ironi Nesher</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1.81</v>
+        <v>3.4</v>
       </c>
       <c r="C138" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D138" t="n">
-        <v>3.7</v>
+        <v>1.87</v>
       </c>
       <c r="E138" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="F138" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4155,23 +4153,23 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Duhok vs Ghaz Al Shamal</t>
+          <t>Sandvikens IF vs IK Oddevold</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="C139" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="D139" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="E139" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="F139" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4182,23 +4180,23 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Mayfield United vs Midleton FC</t>
+          <t>Landskrona Bois vs Helsingborgs IF</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3.6</v>
+        <v>1.78</v>
       </c>
       <c r="C140" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D140" t="n">
-        <v>1.79</v>
+        <v>3.8</v>
       </c>
       <c r="E140" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="F140" t="n">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4209,23 +4207,23 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ross County vs Aberdeen FC II</t>
+          <t>Ljungskile SK vs Norrby IF</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1.14</v>
+        <v>2.01</v>
       </c>
       <c r="C141" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="D141" t="n">
-        <v>11</v>
+        <v>3.15</v>
       </c>
       <c r="E141" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="F141" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4236,23 +4234,23 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Montrose vs Dundee FC II</t>
+          <t>United IK Nordic vs IFK Varnamo</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1.08</v>
+        <v>2.08</v>
       </c>
       <c r="C142" t="n">
-        <v>8.5</v>
+        <v>3.6</v>
       </c>
       <c r="D142" t="n">
-        <v>19</v>
+        <v>3.1</v>
       </c>
       <c r="E142" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="F142" t="n">
-        <v>3.05</v>
+        <v>2.09</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -4263,23 +4261,23 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Annan Athletic vs Motherwell II</t>
+          <t>IFK Goteborg (K) vs BK Hacken (K)</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1.41</v>
+        <v>15</v>
       </c>
       <c r="C143" t="n">
-        <v>4.33</v>
+        <v>8</v>
       </c>
       <c r="D143" t="n">
-        <v>5.5</v>
+        <v>1.07</v>
       </c>
       <c r="E143" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="F143" t="n">
-        <v>1.62</v>
+        <v>3.8</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -4290,23 +4288,23 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Airdrieonians FC vs St Mirren II</t>
+          <t>Hammarby IF (K) vs Gamla Upsala (K)</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1.47</v>
+        <v>17</v>
       </c>
       <c r="C144" t="n">
-        <v>4.33</v>
+        <v>29</v>
       </c>
       <c r="D144" t="n">
-        <v>4.75</v>
+        <v>1.02</v>
       </c>
       <c r="E144" t="n">
-        <v>1.38</v>
+        <v>1.02</v>
       </c>
       <c r="F144" t="n">
-        <v>2.7</v>
+        <v>10</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4317,23 +4315,23 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Cove Rangers vs Dumbarton</t>
+          <t>Zurich (K) vs Young Boys (K)</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="C145" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="D145" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="E145" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="F145" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4344,23 +4342,23 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Berwick Rangers vs Hibernian B</t>
+          <t>Basel (K) vs Grasshopper (K)</t>
         </is>
       </c>
       <c r="B146" t="n">
         <v>2.1</v>
       </c>
       <c r="C146" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="D146" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="E146" t="n">
-        <v>1.35</v>
+        <v>1.71</v>
       </c>
       <c r="F146" t="n">
-        <v>2.9</v>
+        <v>1.98</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -4371,23 +4369,23 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Formartine United FC vs Dundee Utd II</t>
+          <t>Luzern (K) vs Rapperswil-Jona (K)</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="C147" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D147" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="E147" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="F147" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4398,23 +4396,23 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Peterhead vs Clachnacuddin</t>
+          <t>FC Koniz vs FC Allschwil</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="C148" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D148" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="E148" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="F148" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -4425,23 +4423,23 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Elgin City vs Fraserburgh</t>
+          <t>FC Thun (W) vs FC Sion (W)</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="C149" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="D149" t="n">
-        <v>4.75</v>
+        <v>9</v>
       </c>
       <c r="E149" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="F149" t="n">
-        <v>2.58</v>
+        <v>3.6</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -4452,23 +4450,23 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FC Edinburgh vs Queen of the South</t>
+          <t>Lugano (W) vs AS Gambarogno (W)</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>2.63</v>
+        <v>1.47</v>
       </c>
       <c r="C150" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="D150" t="n">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="E150" t="n">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="F150" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -4479,23 +4477,23 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>East Kilbride vs Bonnyrigg Rose</t>
+          <t>UMF Njardvik vs Throttur Reykjavik</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1.4</v>
+        <v>2.63</v>
       </c>
       <c r="C151" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="D151" t="n">
-        <v>5.5</v>
+        <v>2.22</v>
       </c>
       <c r="E151" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="F151" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -4506,23 +4504,23 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Cowdenbeath vs Kilmarnock II</t>
+          <t>Kopavogur vs Fylkir Reykjavik</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2.22</v>
+        <v>2.45</v>
       </c>
       <c r="C152" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D152" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="E152" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="F152" t="n">
-        <v>2.73</v>
+        <v>3.28</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -4533,23 +4531,23 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Banks O'Dee F.C. vs Forfar Athletic</t>
+          <t>Afturelding (K) vs Dalvik/Reynir (K)</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>2.6</v>
+        <v>1.14</v>
       </c>
       <c r="C153" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="D153" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="E153" t="n">
-        <v>1.47</v>
+        <v>1.11</v>
       </c>
       <c r="F153" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -4560,23 +4558,23 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Clydebank vs Alloa Athletic</t>
+          <t>Decic Tuzi vs OFK Petrovac</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>3.28</v>
+        <v>2.3</v>
       </c>
       <c r="C154" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="D154" t="n">
-        <v>1.87</v>
+        <v>3.2</v>
       </c>
       <c r="E154" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="F154" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -4587,23 +4585,23 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Clyde FC vs East Fife</t>
+          <t>Kairat Almaty vs Zhenys</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2.45</v>
+        <v>1.28</v>
       </c>
       <c r="C155" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="D155" t="n">
-        <v>2.37</v>
+        <v>8.5</v>
       </c>
       <c r="E155" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="F155" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -4614,23 +4612,23 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Stirling Albion vs Glasgow Rangers II</t>
+          <t>Independiente Santa Fe (K) vs Deportivo Cali (K)</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2.18</v>
+        <v>3.4</v>
       </c>
       <c r="C156" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="D156" t="n">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="E156" t="n">
-        <v>1.37</v>
+        <v>2.4</v>
       </c>
       <c r="F156" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -4641,23 +4639,23 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Spartans FC vs Hamilton Academical FC</t>
+          <t>America de Cali (K) vs Orsomarso (K)</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="C157" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="D157" t="n">
-        <v>1.9</v>
+        <v>8</v>
       </c>
       <c r="E157" t="n">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="F157" t="n">
-        <v>2.34</v>
+        <v>1.71</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -4668,23 +4666,23 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Gala Fairydean Rovers vs Hearts II</t>
+          <t>Independiente Yumbo vs Deportes Quindio</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="C158" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="E158" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="F158" t="n">
-        <v>3</v>
+        <v>1.53</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -4695,23 +4693,23 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya U19 vs Hapoel Kfar Saba U19</t>
+          <t>Ferrovalvulas FC vs Universidad de Antioquia</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2.16</v>
+        <v>1.6</v>
       </c>
       <c r="C159" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D159" t="n">
-        <v>2.77</v>
+        <v>4.2</v>
       </c>
       <c r="E159" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="F159" t="n">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -4722,24 +4720,20 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv U19 vs Ashdod U19</t>
+          <t>Sion Swifts LFC (K) vs St. James Swifts (K)</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1.55</v>
+        <v>1.04</v>
       </c>
       <c r="C160" t="n">
-        <v>3.8</v>
+        <v>9.5</v>
       </c>
       <c r="D160" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E160" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="F160" t="n">
-        <v>2.23</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
           <t>-</t>
@@ -4749,23 +4743,23 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Maccabi Petach Tikva U19 vs Hapoel Nir Ramat Hasharon U19</t>
+          <t>Ballymena United (K) vs Ballyclare Comrades (K)</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1.12</v>
+        <v>2.37</v>
       </c>
       <c r="C161" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D161" t="n">
-        <v>12</v>
+        <v>2.25</v>
       </c>
       <c r="E161" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="F161" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -4776,23 +4770,23 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Hapoel Kiryat Shmona U19 vs Hapoel Raanana U19</t>
+          <t>Bangor (K) vs Ballymoney United (K)</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1.94</v>
+        <v>1.09</v>
       </c>
       <c r="C162" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D162" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E162" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F162" t="n">
         <v>3.6</v>
-      </c>
-      <c r="D162" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E162" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F162" t="n">
-        <v>2.27</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -4803,23 +4797,23 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Bnei Yehuda Tel Aviv U19 vs Hapoel Beer Sheva U19</t>
+          <t>Greenisland (K) vs Mid Ulster (K)</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="C163" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D163" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="E163" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="F163" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -4830,23 +4824,23 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sutjeska Niksic vs Mornar Bar</t>
+          <t>Zalgiris Kauno vs FK Suduva Marijampole</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="D164" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="E164" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="F164" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -4857,23 +4851,23 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Al Mesaimeer SC vs Al Kharitiyath</t>
+          <t>Novaci vs Ohrid</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="C165" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D165" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="E165" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="F165" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -4884,23 +4878,23 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AL Shamal U23 vs Al Bidda SC</t>
+          <t>Fk Teteks vs Bregalnica Stip</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>3.8</v>
+        <v>11</v>
       </c>
       <c r="C166" t="n">
-        <v>3.6</v>
+        <v>6</v>
       </c>
       <c r="D166" t="n">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="E166" t="n">
-        <v>1.68</v>
+        <v>1.3</v>
       </c>
       <c r="F166" t="n">
-        <v>2.02</v>
+        <v>3.2</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -4911,23 +4905,23 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Astana (K) vs Tobol Kostanay (K)</t>
+          <t>Pyramids FC vs El Gouna FC</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2.68</v>
+        <v>1.47</v>
       </c>
       <c r="C167" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D167" t="n">
-        <v>2.18</v>
+        <v>7</v>
       </c>
       <c r="E167" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F167" t="n">
         <v>1.47</v>
-      </c>
-      <c r="F167" t="n">
-        <v>2.34</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -4938,23 +4932,23 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Incheon United vs Bucheon 1995</t>
+          <t>Modern Sport FC vs Wady Degla</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1.97</v>
+        <v>4.2</v>
       </c>
       <c r="C168" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="D168" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="E168" t="n">
-        <v>2.16</v>
+        <v>2.8</v>
       </c>
       <c r="F168" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -4965,23 +4959,23 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ulsan Hyundai Horang-i vs FC Seoul</t>
+          <t>Al Moqawloon Al Arab vs Al Ahly Cairo</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="C169" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="D169" t="n">
-        <v>2.01</v>
+        <v>1.35</v>
       </c>
       <c r="E169" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="F169" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -4992,23 +4986,23 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Larne vs Bangor</t>
+          <t>ENPPI Club vs FC Masr (ZED)</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1.14</v>
+        <v>3.28</v>
       </c>
       <c r="C170" t="n">
-        <v>6.5</v>
+        <v>2.63</v>
       </c>
       <c r="D170" t="n">
-        <v>13.25</v>
+        <v>2.4</v>
       </c>
       <c r="E170" t="n">
-        <v>1.47</v>
+        <v>3.5</v>
       </c>
       <c r="F170" t="n">
-        <v>2.45</v>
+        <v>1.25</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -5019,23 +5013,23 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Star City FC vs Kedah</t>
+          <t>Olmaliq OKMK vs Pakhtakor Tashkent</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1.3</v>
+        <v>3</v>
       </c>
       <c r="C171" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="D171" t="n">
-        <v>6.5</v>
+        <v>2.02</v>
       </c>
       <c r="E171" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="F171" t="n">
-        <v>2.9</v>
+        <v>2.04</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -5046,23 +5040,23 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>El Zamalek vs Abu Qir Semad FC</t>
+          <t>Neftchi Fargona vs Surkhon Termez</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="C172" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="D172" t="n">
         <v>6.5</v>
       </c>
       <c r="E172" t="n">
-        <v>1.79</v>
+        <v>1.45</v>
       </c>
       <c r="F172" t="n">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -5073,23 +5067,23 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Smouha vs Ceramica Cleopatra FC</t>
+          <t>Nasaf Qarshi vs FC Bunyodkor</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>3.15</v>
+        <v>1.32</v>
       </c>
       <c r="C173" t="n">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="D173" t="n">
-        <v>2.31</v>
+        <v>7</v>
       </c>
       <c r="E173" t="n">
-        <v>2.9</v>
+        <v>1.53</v>
       </c>
       <c r="F173" t="n">
-        <v>1.35</v>
+        <v>2.27</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -5100,23 +5094,23 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Djerv 1919 vs Haugesund</t>
+          <t>Deportivo Santani vs Independiente FBC</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>10</v>
+        <v>1.93</v>
       </c>
       <c r="C174" t="n">
-        <v>7</v>
+        <v>3.28</v>
       </c>
       <c r="D174" t="n">
-        <v>1.14</v>
+        <v>3.4</v>
       </c>
       <c r="E174" t="n">
-        <v>1.18</v>
+        <v>2.01</v>
       </c>
       <c r="F174" t="n">
-        <v>4.2</v>
+        <v>1.7</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -5127,23 +5121,23 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Asker Fotball vs Stromsgodset</t>
+          <t>12 de Octubre de San Domingo vs Silvio Pettirossi</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>6</v>
+        <v>2.39</v>
       </c>
       <c r="C175" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="D175" t="n">
-        <v>1.32</v>
+        <v>2.4</v>
       </c>
       <c r="E175" t="n">
-        <v>1.2</v>
+        <v>1.71</v>
       </c>
       <c r="F175" t="n">
-        <v>3.8</v>
+        <v>1.99</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -5154,23 +5148,23 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3 De Noviembre vs Sol de America</t>
+          <t>24 de Setiembre vs Club Olimpia De Ita</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="C176" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="D176" t="n">
-        <v>2.16</v>
+        <v>4.33</v>
       </c>
       <c r="E176" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="F176" t="n">
-        <v>1.86</v>
+        <v>2.01</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -5181,23 +5175,23 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Paraguari AC vs Guairena FC</t>
+          <t>3 de Febrero FBC vs Presidente Hayes</t>
         </is>
       </c>
       <c r="B177" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="C177" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D177" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E177" t="n">
         <v>1.96</v>
       </c>
-      <c r="C177" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D177" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E177" t="n">
-        <v>2.23</v>
-      </c>
       <c r="F177" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -5208,23 +5202,23 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Cerro Porteno Reserve vs Nacional Asunción Reserve</t>
+          <t>12 de Octubre vs Club General Martin Ledesma</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2.45</v>
+        <v>1.43</v>
       </c>
       <c r="C178" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="D178" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="E178" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="F178" t="n">
-        <v>1.47</v>
+        <v>2.27</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -5235,23 +5229,23 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KF Drenica Skenderaj vs FC Prishtina</t>
+          <t>Dalin Myslenice vs MKS Limanovia Limanowa</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>2.9</v>
+        <v>1.55</v>
       </c>
       <c r="C179" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="D179" t="n">
-        <v>2.12</v>
+        <v>4.25</v>
       </c>
       <c r="E179" t="n">
-        <v>2.03</v>
+        <v>1.41</v>
       </c>
       <c r="F179" t="n">
-        <v>1.68</v>
+        <v>2.59</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -5262,23 +5256,23 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KF Vushtrria vs KF Llapi Podujeve</t>
+          <t>Cracovia Krakow II vs LKS Blekitni Modlnica</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>2.9</v>
+        <v>1.16</v>
       </c>
       <c r="C180" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="D180" t="n">
-        <v>2.16</v>
+        <v>10</v>
       </c>
       <c r="E180" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="F180" t="n">
-        <v>1.76</v>
+        <v>3.5</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -5289,23 +5283,23 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>FC Ryazan vs Spartak Kostroma</t>
+          <t>LKS Wolania Wola Rzedzinska vs Poprad Muszyna</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>5</v>
+        <v>1.68</v>
       </c>
       <c r="C181" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="D181" t="n">
-        <v>1.62</v>
+        <v>3.6</v>
       </c>
       <c r="E181" t="n">
-        <v>1.76</v>
+        <v>1.35</v>
       </c>
       <c r="F181" t="n">
-        <v>1.95</v>
+        <v>2.9</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -5316,23 +5310,23 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>FK Tekstilshchik Ivanovo vs Arsenal Tula</t>
+          <t>GKS Victoria Jaworzno vs Watra Bialka Tatrzanska</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="C182" t="n">
-        <v>2.9</v>
+        <v>4.75</v>
       </c>
       <c r="D182" t="n">
-        <v>2.33</v>
+        <v>7</v>
       </c>
       <c r="E182" t="n">
-        <v>1.97</v>
+        <v>1.4</v>
       </c>
       <c r="F182" t="n">
-        <v>1.74</v>
+        <v>2.7</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -5343,23 +5337,23 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Domagnano vs SC Faetano</t>
+          <t>KF Feronikeli vs Drita Gjilan</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>1.27</v>
+        <v>6</v>
       </c>
       <c r="C183" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="D183" t="n">
-        <v>8</v>
+        <v>1.41</v>
       </c>
       <c r="E183" t="n">
-        <v>1.51</v>
+        <v>1.76</v>
       </c>
       <c r="F183" t="n">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -5370,23 +5364,23 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SP Tre Penne vs AC Juvenes/Dogana</t>
+          <t>SC Gjilani vs Ballkani</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="C184" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D184" t="n">
-        <v>4.75</v>
+        <v>2.09</v>
       </c>
       <c r="E184" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="F184" t="n">
         <v>1.81</v>
-      </c>
-      <c r="F184" t="n">
-        <v>1.87</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -5397,23 +5391,23 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Lion City Sailors FC II vs Hougang II</t>
+          <t>Dinamo Kirov vs Kamaz Nab Chelny</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>2.27</v>
+        <v>3.1</v>
       </c>
       <c r="C185" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D185" t="n">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="E185" t="n">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="F185" t="n">
-        <v>2.8</v>
+        <v>1.94</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -5424,23 +5418,23 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Sk Novohrad Lucenec vs Komarno</t>
+          <t>FK Sokol Saratov vs Leningradets</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>29</v>
+        <v>3.05</v>
       </c>
       <c r="C186" t="n">
-        <v>11</v>
+        <v>3.2</v>
       </c>
       <c r="D186" t="n">
-        <v>1.03</v>
+        <v>2.15</v>
       </c>
       <c r="E186" t="n">
-        <v>1.22</v>
+        <v>1.87</v>
       </c>
       <c r="F186" t="n">
-        <v>3.7</v>
+        <v>1.83</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -5451,23 +5445,23 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Raca Bratislava vs Samorin</t>
+          <t>Murom vs Veles Moscow</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="C187" t="n">
-        <v>4.75</v>
+        <v>3.15</v>
       </c>
       <c r="D187" t="n">
-        <v>1.28</v>
+        <v>1.99</v>
       </c>
       <c r="E187" t="n">
-        <v>1.41</v>
+        <v>1.79</v>
       </c>
       <c r="F187" t="n">
-        <v>2.68</v>
+        <v>1.91</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -5478,23 +5472,23 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MSK Namestovo vs Kinex Bytca</t>
+          <t>FK Kaluga vs Ufa</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>2.15</v>
+        <v>4.33</v>
       </c>
       <c r="C188" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="D188" t="n">
-        <v>2.68</v>
+        <v>1.74</v>
       </c>
       <c r="E188" t="n">
-        <v>1.5</v>
+        <v>1.98</v>
       </c>
       <c r="F188" t="n">
-        <v>2.37</v>
+        <v>1.72</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -5505,23 +5499,23 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Spartak Medzev vs Zemplin Michalovce</t>
+          <t>FC Volgar Astrakhan vs Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>9.5</v>
+        <v>2.9</v>
       </c>
       <c r="C189" t="n">
-        <v>5.5</v>
+        <v>3.3</v>
       </c>
       <c r="D189" t="n">
-        <v>1.18</v>
+        <v>2.14</v>
       </c>
       <c r="E189" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>1.92</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -5532,23 +5526,23 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Fk Kosicka Nova Ves vs Podbrezova</t>
+          <t>Dinamo Stavropol vs Nizhny Novgorod</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>13.25</v>
+        <v>8</v>
       </c>
       <c r="C190" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="D190" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="E190" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="F190" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -5559,23 +5553,23 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Mnk Izola vs Tabor Sezana</t>
+          <t>Chertanovo Moscow vs Neftekhimik Nizhnekamsk</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="C191" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="D191" t="n">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="E191" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="F191" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -5586,23 +5580,23 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>NK Brezice vs Dravinja</t>
+          <t>Dinamo Saint-Petersburg vs Sochi</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>2.2</v>
+        <v>4.33</v>
       </c>
       <c r="C192" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="D192" t="n">
-        <v>2.7</v>
+        <v>1.66</v>
       </c>
       <c r="E192" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="F192" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -5613,23 +5607,23 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Primorje Ajdovscina vs NK Bilje</t>
+          <t>Druzhba Maikop vs Yenisey Krasnoyarsk</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>1.64</v>
+        <v>2.45</v>
       </c>
       <c r="C193" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="D193" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="E193" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="F193" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -5640,23 +5634,23 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Al-Ettifaq Dammam vs Al Faisaly Harmah</t>
+          <t>Nova Bana vs Vion Zlate Moravce</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1.93</v>
+        <v>5.5</v>
       </c>
       <c r="C194" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="D194" t="n">
-        <v>3.3</v>
+        <v>1.38</v>
       </c>
       <c r="E194" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="F194" t="n">
-        <v>2.16</v>
+        <v>2.55</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -5667,23 +5661,23 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Al Hazm vs Al Taawon Buraidah</t>
+          <t>Banik Prievidza vs Banik Lehota pod Vtacnikom</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="C195" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="D195" t="n">
-        <v>2.06</v>
+        <v>1.51</v>
       </c>
       <c r="E195" t="n">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="F195" t="n">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -5694,23 +5688,23 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Al-Qadsiah Al Khubar vs Al Ahli Jeddah</t>
+          <t>NK Roltek Dob vs ND Slovan Ljubljana</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>1.99</v>
+        <v>3.1</v>
       </c>
       <c r="C196" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="D196" t="n">
-        <v>3.15</v>
+        <v>1.87</v>
       </c>
       <c r="E196" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="F196" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -5721,23 +5715,23 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Al-Ittihad vs Al Feiha</t>
+          <t>NK Bistrica vs Odranci</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>1.35</v>
+        <v>17</v>
       </c>
       <c r="C197" t="n">
-        <v>4.75</v>
+        <v>9.5</v>
       </c>
       <c r="D197" t="n">
-        <v>6.5</v>
+        <v>1.06</v>
       </c>
       <c r="E197" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="F197" t="n">
-        <v>2.58</v>
+        <v>2.39</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -5748,23 +5742,23 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Al Zulfi FC vs Hajer</t>
+          <t>Rudar Trbovlje vs Radomlje</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>1.75</v>
+        <v>12</v>
       </c>
       <c r="C198" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="D198" t="n">
-        <v>4</v>
+        <v>1.14</v>
       </c>
       <c r="E198" t="n">
-        <v>1.98</v>
+        <v>1.33</v>
       </c>
       <c r="F198" t="n">
-        <v>1.72</v>
+        <v>3.05</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -5775,23 +5769,23 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Damac FC vs Al-Ula</t>
+          <t>Jadran Dekani vs Koper</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>3.5</v>
+        <v>17</v>
       </c>
       <c r="C199" t="n">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="D199" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="E199" t="n">
-        <v>2.07</v>
+        <v>1.41</v>
       </c>
       <c r="F199" t="n">
-        <v>1.64</v>
+        <v>2.68</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -5802,23 +5796,23 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Al-Anwar vs Al Taee Hail</t>
+          <t>NK Rudar Velenje vs Celje</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1.86</v>
+        <v>11</v>
       </c>
       <c r="C200" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D200" t="n">
-        <v>3.4</v>
+        <v>1.16</v>
       </c>
       <c r="E200" t="n">
-        <v>1.7</v>
+        <v>1.47</v>
       </c>
       <c r="F200" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -5829,23 +5823,23 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Mashujaa vs Singida BS</t>
+          <t>Al Kholood vs Al Shabab Riyadh</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>3.8</v>
+        <v>2.63</v>
       </c>
       <c r="C201" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="D201" t="n">
-        <v>1.86</v>
+        <v>2.37</v>
       </c>
       <c r="E201" t="n">
-        <v>2.37</v>
+        <v>1.76</v>
       </c>
       <c r="F201" t="n">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -5856,23 +5850,23 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Young Africans vs Geita Gold</t>
+          <t>Al Fateh vs Al Diriyah</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="C202" t="n">
-        <v>9</v>
+        <v>3.7</v>
       </c>
       <c r="D202" t="n">
-        <v>23</v>
+        <v>1.87</v>
       </c>
       <c r="E202" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="F202" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -5883,23 +5877,23 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Bul FC vs Ntugasaze FC</t>
+          <t>Al-Nassr Riyadh vs Abha</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="C203" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="D203" t="n">
-        <v>8</v>
+        <v>13.25</v>
       </c>
       <c r="E203" t="n">
-        <v>2.01</v>
+        <v>1.28</v>
       </c>
       <c r="F203" t="n">
-        <v>1.7</v>
+        <v>3.2</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -5910,23 +5904,23 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Maroons Fc vs Blacks Power</t>
+          <t>Al Raed Buraidah vs Al-Jeel</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="C204" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="D204" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="E204" t="n">
-        <v>2.4</v>
+        <v>1.86</v>
       </c>
       <c r="F204" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -5937,23 +5931,23 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Kigezi Homeboys vs Kampala City Capital Authority Fc</t>
+          <t>Al Jandal vs Al-Bukayriyah FC</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>4.15</v>
+        <v>2.45</v>
       </c>
       <c r="C205" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="D205" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="E205" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="F205" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -5964,23 +5958,23 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Fc Olympia Savyntsi vs Kryvbas Kriviy</t>
+          <t>Jeddah Club vs Al-Orubah</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>23</v>
+        <v>3.3</v>
       </c>
       <c r="C206" t="n">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="D206" t="n">
-        <v>1.05</v>
+        <v>2.05</v>
       </c>
       <c r="E206" t="n">
-        <v>1.33</v>
+        <v>2.23</v>
       </c>
       <c r="F206" t="n">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -5991,23 +5985,23 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Central Espanol Reserves vs Albion Reserves</t>
+          <t>Huachipato (W) vs Deportes Iquique (W)</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>2.55</v>
+        <v>2.39</v>
       </c>
       <c r="C207" t="n">
         <v>3.3</v>
       </c>
       <c r="D207" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="E207" t="n">
         <v>1.72</v>
       </c>
       <c r="F207" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -6018,23 +6012,23 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>CA Progreso Reserves vs La Luz Reserves</t>
+          <t>Polissya Zhytomyr vs Kudrivka</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>2.39</v>
+        <v>1.22</v>
       </c>
       <c r="C208" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="D208" t="n">
-        <v>2.45</v>
+        <v>9</v>
       </c>
       <c r="E208" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="F208" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -6045,25 +6039,268 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Olympiakos vs Volos NFC</t>
+          <t>Boston River vs Colon FC</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>1.1</v>
+        <v>1.81</v>
       </c>
       <c r="C209" t="n">
-        <v>7.5</v>
+        <v>3.4</v>
       </c>
       <c r="D209" t="n">
-        <v>17</v>
+        <v>3.7</v>
       </c>
       <c r="E209" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="F209" t="n">
-        <v>2.7</v>
+        <v>1.81</v>
       </c>
       <c r="G209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Racing Club de Montevideo vs Central Espanol FC</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C210" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D210" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E210" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="F210" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Real Frontera vs Zamora FC</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>8</v>
+      </c>
+      <c r="C211" t="n">
+        <v>5</v>
+      </c>
+      <c r="D211" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E211" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F211" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Club Atletico Barinas vs Atletico El Vigia</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D212" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E212" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="F212" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Urena Fc vs Rayo Zuliano</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="C213" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="D213" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="E213" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="F213" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Academia Anzoategui vs Dvo Italia</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C214" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D214" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="F214" t="n">
+        <v>2</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Monagas SC vs Bolivar SC</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C215" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D215" t="n">
+        <v>6</v>
+      </c>
+      <c r="E215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F215" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Yaracuyanos FC vs Aragua FC</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C216" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="D216" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F216" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>OFI Crete vs Nestos Chrisoupolis</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C217" t="n">
+        <v>6</v>
+      </c>
+      <c r="D217" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="E217" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F217" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Volos NPS U19 vs Iraklis 1908 FC U19</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C218" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D218" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="E218" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F218" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="G218" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bugun_oranlar.xlsx
+++ b/bugun_oranlar.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,23 +456,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VfB Stuttgart vs Viking</t>
+          <t>PSV vs Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="C2" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="E2" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8</v>
+        <v>2.73</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -483,23 +483,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Barcelona vs Feyenoord</t>
+          <t>Fenerbahçe vs AS Roma</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.08</v>
+        <v>3.15</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>3.7</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>2.12</v>
       </c>
       <c r="E3" t="n">
-        <v>1.14</v>
+        <v>1.66</v>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -510,23 +510,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sporting CP vs Galatasaray</t>
+          <t>FC Bayern Münih vs Bodo/Glimt</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.72</v>
+        <v>1.1</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>4.25</v>
+        <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>1.53</v>
+        <v>1.12</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -537,23 +537,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Liverpool vs Atletico Madrid</t>
+          <t>Manchester United vs Sabah</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.74</v>
+        <v>1.1</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>4.15</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="F5" t="n">
-        <v>2.39</v>
+        <v>3.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -564,23 +564,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Napoli vs Arsenal</t>
+          <t>Como vs RB Leipzig</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>1.75</v>
       </c>
       <c r="C6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="D6" t="n">
-        <v>1.62</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="F6" t="n">
-        <v>1.85</v>
+        <v>2.59</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -591,23 +591,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSG vs Slovan Bratislava</t>
+          <t>Slavia Prague vs Lens</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.05</v>
+        <v>2.54</v>
       </c>
       <c r="C7" t="n">
-        <v>13.25</v>
+        <v>3.6</v>
       </c>
       <c r="D7" t="n">
-        <v>34</v>
+        <v>2.55</v>
       </c>
       <c r="E7" t="n">
-        <v>1.14</v>
+        <v>1.71</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>2.12</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -618,23 +618,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sporting Lisbon U19 vs Galatasaray U19</t>
+          <t>Fenerbahçe U19 vs Roma U19</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.22</v>
+        <v>4.25</v>
       </c>
       <c r="C8" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="D8" t="n">
-        <v>8.5</v>
+        <v>1.51</v>
       </c>
       <c r="E8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="F8" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -645,23 +645,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Liverpool U19 vs Atletico Madrid U19</t>
+          <t>PSV U19 vs Shakhtar Donetsk U19</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.01</v>
+        <v>1.33</v>
       </c>
       <c r="C9" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="D9" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="F9" t="n">
-        <v>2.77</v>
+        <v>3.15</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -672,23 +672,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Norwich vs Birmingham</t>
+          <t>Slavia Prague U19 vs Lens U19</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="C10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="D10" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="E10" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="F10" t="n">
-        <v>1.95</v>
+        <v>3.15</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -699,23 +699,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Derby County vs West Bromwich</t>
+          <t>Manchester United U19 vs Sabah U19</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="C11" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>2.23</v>
+        <v>21</v>
       </c>
       <c r="E11" t="n">
-        <v>1.94</v>
+        <v>1.09</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -726,23 +726,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Charlton vs QPR</t>
+          <t>Como U19 vs RB Leipzig U19</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="C12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="D12" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="E12" t="n">
-        <v>1.95</v>
+        <v>1.47</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -753,23 +753,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Exmouth Town vs Banbury United</t>
+          <t>Stevenage vs Luton</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="C13" t="n">
         <v>3.3</v>
       </c>
       <c r="D13" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -780,23 +780,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AFC Whyteleafe vs Crowborough Athletic</t>
+          <t>AS Cannes vs Amiens</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="C14" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="E14" t="n">
-        <v>1.22</v>
+        <v>2.02</v>
       </c>
       <c r="F14" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -807,17 +807,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bishop Auckland FC vs Emley</t>
+          <t>Estrela vs Braga</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="C15" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="E15" t="n">
         <v>1.87</v>
@@ -834,24 +834,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chelsea vs Leeds United</t>
+          <t>G.D. Interclube vs Academica do Lobito</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="C16" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="F16" t="n">
-        <v>2.31</v>
-      </c>
+        <v>4.75</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>-</t>
@@ -861,23 +857,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Tamworth vs Middlesbrough U21</t>
+          <t>Rosario Central Reserves vs Godoy Cruz Reserves</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.33</v>
+        <v>1.47</v>
       </c>
       <c r="C17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>2.34</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -888,23 +884,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Coventry United vs Boston Town</t>
+          <t>Estudiantes La Plata Reserves vs Ca Huracan Reserves</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E18" t="n">
         <v>2.07</v>
       </c>
-      <c r="C18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1.66</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2.05</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -915,23 +911,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Corby Town vs Bedworth United</t>
+          <t>Banfield Reserves vs Gimnasia Mendoza Reserves</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="C19" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="D19" t="n">
-        <v>1.91</v>
+        <v>2.8</v>
       </c>
       <c r="E19" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="F19" t="n">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -942,23 +938,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Rugby Borough vs Long Eaton United</t>
+          <t>Independiente Rivadavia Reserves vs Newells Old Boys Reserves</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="C20" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="D20" t="n">
-        <v>3.28</v>
+        <v>2.59</v>
       </c>
       <c r="E20" t="n">
-        <v>1.53</v>
+        <v>2.45</v>
       </c>
       <c r="F20" t="n">
-        <v>2.31</v>
+        <v>1.47</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -969,23 +965,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lichfield City vs Hanley Town FC</t>
+          <t>Tigre Reserves vs Atletico Tucuman Reserves</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.5</v>
+        <v>2.37</v>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="D21" t="n">
-        <v>1.25</v>
+        <v>2.55</v>
       </c>
       <c r="E21" t="n">
-        <v>1.28</v>
+        <v>1.96</v>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>1.74</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -996,23 +992,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Blackburn U21 vs Queens Park Rangers U21</t>
+          <t>Deportivo Riestra Reserves vs Lanus Reserves</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="C22" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="D22" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="E22" t="n">
-        <v>1.32</v>
+        <v>2.03</v>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>1.68</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1023,23 +1019,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Getafe (W) vs Pozuelo de Alarcon (W)</t>
+          <t>Deportivo Espanol Reserves vs JJ Urquiza Reserves</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.59</v>
+        <v>1.95</v>
       </c>
       <c r="C23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D23" t="n">
-        <v>2.27</v>
+        <v>3.2</v>
       </c>
       <c r="E23" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="F23" t="n">
-        <v>2.16</v>
+        <v>1.94</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1050,23 +1046,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Real Oviedo (W) vs Sporting Gijon (W)</t>
+          <t>Estrella del Sur Reserves vs Leones de Rosario Reserves</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.45</v>
+        <v>2.8</v>
       </c>
       <c r="C24" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>2.15</v>
       </c>
       <c r="E24" t="n">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="F24" t="n">
-        <v>2.27</v>
+        <v>1.87</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1077,23 +1073,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Elche CF (K) vs Levante (K)</t>
+          <t>Berazategui Reserves vs Defensores de Cambaceres Reserves</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.5</v>
+        <v>1.75</v>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.28</v>
+        <v>3.8</v>
       </c>
       <c r="E25" t="n">
-        <v>1.45</v>
+        <v>1.81</v>
       </c>
       <c r="F25" t="n">
-        <v>2.45</v>
+        <v>1.86</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1104,23 +1100,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Balears FC (W) vs Villarreal (K)</t>
+          <t>Villa San Carlos Reserves vs Excursionistas Reserves</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>13</v>
+        <v>2.5</v>
       </c>
       <c r="C26" t="n">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="D26" t="n">
-        <v>1.14</v>
+        <v>2.45</v>
       </c>
       <c r="E26" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="F26" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1131,23 +1127,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sporting de Huelva (W) vs Malaga CF (W)</t>
+          <t>Real Pilar Reserves vs UAI Urquiza Reserves</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="C27" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D27" t="n">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="E27" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="F27" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1158,23 +1154,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Burgos (W) vs Bizkerre (W)</t>
+          <t>Sportivo Italiano Reserves vs Argentino Merlo Reserves</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="C28" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="D28" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="E28" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="F28" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1185,23 +1181,23 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Celta Vigo (W) vs Real Aviles CF (W)</t>
+          <t>Argentino Quilmes Reserves vs CA Ituzaingo Reserves</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1.47</v>
+        <v>2.06</v>
       </c>
       <c r="C29" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="D29" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1212,23 +1208,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sport Extremadura (W) vs Cacereno (K)</t>
+          <t>CA San Miguel Reserves vs Deportivo Moron Reserves</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="C30" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="D30" t="n">
-        <v>2.31</v>
+        <v>3.2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="F30" t="n">
-        <v>1.93</v>
+        <v>1.47</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1239,23 +1235,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CD Samper (W) vs CFF Olympia Las Rozas (W)</t>
+          <t>Club Atletico Mitre Reserves vs Acassuso Reserves</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.9</v>
+        <v>1.94</v>
       </c>
       <c r="C31" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="D31" t="n">
-        <v>2.02</v>
+        <v>3.4</v>
       </c>
       <c r="E31" t="n">
-        <v>1.51</v>
+        <v>2.23</v>
       </c>
       <c r="F31" t="n">
-        <v>2.35</v>
+        <v>1.55</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1266,23 +1262,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UD Santa Marta vs Vimenor CF</t>
+          <t>Estudiantes Caseros Reserves vs Tristan Suarez Reserves</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="C32" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="D32" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="F32" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1293,23 +1289,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Compostela vs CD Derio</t>
+          <t>Ferrocarril Midland Reserves vs CA Atlanta Reserves</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.53</v>
+        <v>2.9</v>
       </c>
       <c r="C33" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D33" t="n">
-        <v>4.75</v>
+        <v>2.12</v>
       </c>
       <c r="E33" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="F33" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1320,23 +1316,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS vs Caudal Deportivo de Mieres</t>
+          <t>Temperley Reserves vs Chacarita Juniors Reserves</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.4</v>
+        <v>1.99</v>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="E34" t="n">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="F34" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1347,23 +1343,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Comillas CF vs CE L'Hospitalet</t>
+          <t>All Boys Reserves vs Los Andes Reserves</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3.7</v>
+        <v>2.08</v>
       </c>
       <c r="C35" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="D35" t="n">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="F35" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1374,23 +1370,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Torrent CF vs Saguntino</t>
+          <t>Sabayil FK vs Energetik Mingechevir</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="C36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="F36" t="n">
         <v>1.97</v>
-      </c>
-      <c r="C36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D36" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.91</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1401,23 +1397,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CF Badalona vs Sestao River Club</t>
+          <t>Zaqatala vs Baku Sporting</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="C37" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D37" t="n">
-        <v>2.03</v>
+        <v>1.9</v>
       </c>
       <c r="E37" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="F37" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1428,23 +1424,23 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AD San Juan Pamplona vs Terrassa CF</t>
+          <t>Cabrayil vs Khankendi FK</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3.7</v>
+        <v>2.12</v>
       </c>
       <c r="C38" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="D38" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E38" t="n">
         <v>1.87</v>
       </c>
-      <c r="E38" t="n">
-        <v>2.12</v>
-      </c>
       <c r="F38" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1455,23 +1451,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Motril CF vs Recreativo Huelva</t>
+          <t>Al Jazira SC vs Al-Nasr</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.63</v>
+        <v>1.45</v>
       </c>
       <c r="C39" t="n">
-        <v>3.3</v>
+        <v>4.25</v>
       </c>
       <c r="D39" t="n">
-        <v>2.31</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="F39" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1482,23 +1478,23 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cacereno vs UD San Pedro</t>
+          <t>Dubai United FC vs Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.38</v>
+        <v>7</v>
       </c>
       <c r="C40" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>6.5</v>
+        <v>1.28</v>
       </c>
       <c r="E40" t="n">
-        <v>2.01</v>
+        <v>1.3</v>
       </c>
       <c r="F40" t="n">
-        <v>1.71</v>
+        <v>3.15</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1509,23 +1505,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>U.D. Talavera vs Navalcarnero</t>
+          <t>Al Ain vs Al Wasl</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="C41" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="D41" t="n">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="E41" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="F41" t="n">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1536,23 +1532,23 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Grosseto vs Latina</t>
+          <t>Al-Muharraq vs Manama</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2.18</v>
+        <v>1.25</v>
       </c>
       <c r="C42" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>2.9</v>
+        <v>8</v>
       </c>
       <c r="E42" t="n">
-        <v>2.04</v>
+        <v>1.47</v>
       </c>
       <c r="F42" t="n">
-        <v>1.66</v>
+        <v>2.4</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1563,23 +1559,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Bayern Alzenau vs Hanauer SC 1960</t>
+          <t>Al Riffa vs Al Khalidiyah</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="C43" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D43" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="E43" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="F43" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1590,23 +1586,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FC Turabdin-Babylon Pohlheim vs FSV Fernwald</t>
+          <t>Santos FC U20 vs Cuiaba U20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.31</v>
+        <v>1.22</v>
       </c>
       <c r="C44" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>2.45</v>
+        <v>9.5</v>
       </c>
       <c r="E44" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="F44" t="n">
-        <v>1.43</v>
+        <v>2.39</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1617,23 +1613,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FC Teningen vs Turkischer SV Singen</t>
+          <t>Operario Ferroviario EC PR U20 vs Chapecoense AF U20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="C45" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D45" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="E45" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="F45" t="n">
-        <v>2.22</v>
+        <v>2.01</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1644,23 +1640,23 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FC Normannia Gmund vs TSG Backnang</t>
+          <t>Ferroviario AC CE U20 vs Esporte de Patos U20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>9.5</v>
+        <v>1.57</v>
       </c>
       <c r="C46" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="D46" t="n">
-        <v>1.18</v>
+        <v>4.5</v>
       </c>
       <c r="E46" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>2.05</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1671,23 +1667,23 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Moreirense vs Benfica</t>
+          <t>Sao Paulo FC U20 vs Gremio RS U20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>15</v>
+        <v>1.05</v>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D47" t="n">
-        <v>1.13</v>
+        <v>17</v>
       </c>
       <c r="E47" t="n">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="F47" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1698,23 +1694,23 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Benfica U23 vs Vizela U23</t>
+          <t>Pinheirense EC vs Tesla</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.83</v>
+        <v>2.4</v>
       </c>
       <c r="C48" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="D48" t="n">
-        <v>3.4</v>
+        <v>2.54</v>
       </c>
       <c r="E48" t="n">
-        <v>1.51</v>
+        <v>1.92</v>
       </c>
       <c r="F48" t="n">
-        <v>2.31</v>
+        <v>1.76</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1725,23 +1721,23 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Twente vs Telstar</t>
+          <t>ES Ben Aknoun vs US Biskra</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="D49" t="n">
-        <v>8.5</v>
+        <v>3.8</v>
       </c>
       <c r="E49" t="n">
-        <v>1.25</v>
+        <v>2.31</v>
       </c>
       <c r="F49" t="n">
-        <v>3.5</v>
+        <v>1.53</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1752,23 +1748,23 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Inter Club d'Escaldes vs Atletic Club d'Escaldes</t>
+          <t>USM Alger vs Jeunesse Sportive d'El Biar</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.83</v>
+        <v>1.47</v>
       </c>
       <c r="C50" t="n">
         <v>3.5</v>
       </c>
       <c r="D50" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="E50" t="n">
-        <v>1.71</v>
+        <v>2.31</v>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1779,23 +1775,23 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FC Cabinda vs Primeiro de Agosto</t>
+          <t>Sundby BK vs Midtjylland</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C51" t="n">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="E51" t="n">
-        <v>2.23</v>
+        <v>1.33</v>
       </c>
       <c r="F51" t="n">
-        <v>1.55</v>
+        <v>3</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1806,23 +1802,23 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CA Defensores de Belgrano vs CA Los Andes</t>
+          <t>Kuzey Kore U20 (K) vs Kosta Rika U20 (K)</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="C52" t="n">
-        <v>2.8</v>
+        <v>12</v>
       </c>
       <c r="D52" t="n">
-        <v>3.7</v>
+        <v>46</v>
       </c>
       <c r="E52" t="n">
-        <v>2.9</v>
+        <v>1.07</v>
       </c>
       <c r="F52" t="n">
-        <v>1.35</v>
+        <v>6.5</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1833,23 +1829,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ca Platense Reserves vs Boca Juniors Reserves</t>
+          <t>Kolombiya U20 (K) vs Portekiz U20 (K)</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>5</v>
+        <v>2.68</v>
       </c>
       <c r="C53" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="D53" t="n">
-        <v>1.57</v>
+        <v>2.27</v>
       </c>
       <c r="E53" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="F53" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -1860,23 +1856,23 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>San Martin de San Juan Reserves vs Defensa Y Justicia Reserves</t>
+          <t>Çin U20 (K) vs Nijerya U20 (K)</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="C54" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="D54" t="n">
-        <v>1.66</v>
+        <v>2.18</v>
       </c>
       <c r="E54" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="F54" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -1887,23 +1883,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>San Lorenzo Reserves vs Union Santa Fe Reserves</t>
+          <t>San Antonio FC Cotacachi vs Atletico Rojiblanco</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="C55" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="D55" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="E55" t="n">
-        <v>2.18</v>
+        <v>2.27</v>
       </c>
       <c r="F55" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -1914,23 +1910,23 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Instituto AC Cordoba Reserves vs CA Sarmiento Reserves</t>
+          <t>Cumbaya FC vs Gualaceo SC</t>
         </is>
       </c>
       <c r="B56" t="n">
         <v>2.1</v>
       </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="D56" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="E56" t="n">
-        <v>2.34</v>
+        <v>2.9</v>
       </c>
       <c r="F56" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -1941,23 +1937,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ca Talleres De Cordoba Reserves vs Barracas Central Reserves</t>
+          <t>Nomme Kalju FC U21 vs FC Flora Tallinn U21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1.6</v>
+        <v>4.25</v>
       </c>
       <c r="C57" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D57" t="n">
-        <v>4.75</v>
+        <v>1.51</v>
       </c>
       <c r="E57" t="n">
-        <v>1.97</v>
+        <v>1.18</v>
       </c>
       <c r="F57" t="n">
-        <v>1.74</v>
+        <v>3.8</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -1968,23 +1964,23 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Canuelas FC Reserves vs Victoriano Arenas Reserves</t>
+          <t>Nomme Utd U21 vs JK Tallinna Kalev</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="C58" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>7</v>
+        <v>2.18</v>
       </c>
       <c r="E58" t="n">
-        <v>1.76</v>
+        <v>1.18</v>
       </c>
       <c r="F58" t="n">
-        <v>1.93</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -1995,23 +1991,23 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sacachispas Reserves vs El Porvenir Reserves</t>
+          <t>FC Tallinn vs Maardu Linnameeskond FC</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2.08</v>
+        <v>3.05</v>
       </c>
       <c r="C59" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>3.15</v>
+        <v>1.86</v>
       </c>
       <c r="E59" t="n">
-        <v>1.76</v>
+        <v>1.25</v>
       </c>
       <c r="F59" t="n">
-        <v>1.93</v>
+        <v>3.4</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2022,23 +2018,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Club Comunicaciones Reserves vs Deportivo Armenio Reserves</t>
+          <t>Viimsi Jk vs FC Elva</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="C60" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D60" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="E60" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="F60" t="n">
-        <v>1.86</v>
+        <v>2.37</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2049,23 +2045,23 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Deportivo Merlo Reserves vs Deportivo Laferrere Reserves</t>
+          <t>FC Levadia Tallinn U21 vs Tartu JK Welco</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="C61" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>3.15</v>
+        <v>1.94</v>
       </c>
       <c r="E61" t="n">
-        <v>1.96</v>
+        <v>1.25</v>
       </c>
       <c r="F61" t="n">
-        <v>1.72</v>
+        <v>3.4</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2076,23 +2072,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CS Dock Sud Reserves vs CA Brown de Adrogue Reserves</t>
+          <t>Tallinna JK Legion vs Tartu Kalev</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.66</v>
+        <v>5</v>
       </c>
       <c r="C62" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="D62" t="n">
-        <v>4.33</v>
+        <v>1.4</v>
       </c>
       <c r="E62" t="n">
-        <v>1.94</v>
+        <v>1.16</v>
       </c>
       <c r="F62" t="n">
-        <v>1.74</v>
+        <v>4.75</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2103,23 +2099,23 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Defensores Unidos Reserves vs Flandria Reserves</t>
+          <t>Parnu JK Vaprus II vs Johvi FC Phoenix</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="C63" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D63" t="n">
-        <v>1.83</v>
+        <v>2.45</v>
       </c>
       <c r="E63" t="n">
-        <v>2.08</v>
+        <v>1.14</v>
       </c>
       <c r="F63" t="n">
-        <v>1.66</v>
+        <v>4.75</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2130,23 +2126,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CDT Real Oruro vs Nacional Potosi</t>
+          <t>Tartu Tammeka U21 vs JK Tulevik Viljandi</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2.9</v>
+        <v>2.07</v>
       </c>
       <c r="C64" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>1.96</v>
+        <v>2.5</v>
       </c>
       <c r="E64" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="F64" t="n">
-        <v>2.59</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2157,21 +2153,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FK Zeljeznicar Sarajevo vs Sarajevo</t>
+          <t>Atlantis FC/PM vs Lps</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3.28</v>
+        <v>2.37</v>
       </c>
       <c r="C65" t="n">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="D65" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+        <v>2.07</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.02</v>
+      </c>
       <c r="F65" t="n">
-        <v>1.45</v>
+        <v>9.5</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2182,23 +2180,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cruzeiro EC U20 vs Guanabara City GO U20</t>
+          <t>TiPS U21 vs Lahti 69</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1.07</v>
+        <v>5.5</v>
       </c>
       <c r="C66" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="D66" t="n">
-        <v>19</v>
+        <v>1.32</v>
       </c>
       <c r="E66" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2209,23 +2207,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Fortaleza CE U20 vs Piaui U20</t>
+          <t>Tampereen Peli-Toverit vs Nokian Palloseura</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1.14</v>
+        <v>3.3</v>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="D67" t="n">
-        <v>12</v>
+        <v>1.72</v>
       </c>
       <c r="E67" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="F67" t="n">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2236,23 +2234,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Botafogo RJ U20 vs EC Estrela de Marco U20</t>
+          <t>VPV Pallo-Veikot vs FC Ylivieska</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1.16</v>
+        <v>2.27</v>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>2.37</v>
       </c>
       <c r="E68" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="F68" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2263,23 +2261,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Nautico U20 vs America PE U20</t>
+          <t>PPJ/Lauttasaari vs VJS Vantaa II</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>8.5</v>
+        <v>2.58</v>
       </c>
       <c r="E69" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="F69" t="n">
-        <v>2.26</v>
+        <v>3.4</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2290,23 +2288,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Criciuma U20 vs Cascavel U20</t>
+          <t>HooGee vs MPS</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.85</v>
+        <v>2.09</v>
       </c>
       <c r="C70" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="D70" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="E70" t="n">
-        <v>1.76</v>
+        <v>1.28</v>
       </c>
       <c r="F70" t="n">
-        <v>1.93</v>
+        <v>3.1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2317,23 +2315,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Internacional Rs U20 vs Barra FC SC U20</t>
+          <t>HPS II vs Valtti</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="C71" t="n">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="D71" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="E71" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="F71" t="n">
-        <v>2.18</v>
+        <v>4.25</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2344,23 +2342,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Paysandu U20 vs EC Macapa U20</t>
+          <t>Dinamo Tbilisi vs Meshakhte Tkibuli</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.27</v>
+        <v>1.38</v>
       </c>
       <c r="C72" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E72" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="F72" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2371,23 +2369,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>America RN U20 vs Quinho Futebol Clube U20</t>
+          <t>FC Gagra vs Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="C73" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D73" t="n">
-        <v>3.3</v>
+        <v>1.97</v>
       </c>
       <c r="E73" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="F73" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2398,23 +2396,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Tuna Luso PA U20 vs Batalhao U20</t>
+          <t>FC Merani Tbilisi vs Kolkheti Khobi</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="C74" t="n">
-        <v>4.25</v>
+        <v>3.7</v>
       </c>
       <c r="D74" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="E74" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="F74" t="n">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2425,23 +2423,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CS Alagoano U20 vs Confianca EC PB U20</t>
+          <t>Betlemi Keda vs FC Margveti 2006</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.55</v>
+        <v>2.9</v>
       </c>
       <c r="C75" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D75" t="n">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="F75" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2452,23 +2450,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ceara SC CE U20 vs Atletico Piauiense U20</t>
+          <t>Coal India SPA vs Mohun Bagan SG Reserves</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="C76" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="D76" t="n">
-        <v>5.5</v>
+        <v>2.07</v>
       </c>
       <c r="E76" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="F76" t="n">
-        <v>2.11</v>
+        <v>1.68</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2479,23 +2477,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Santa Cruz PE U20 vs CS Esportiva U20</t>
+          <t>Rangdajied United FC vs Laitkor SC</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="C77" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F77" t="n">
         <v>3.6</v>
-      </c>
-      <c r="D77" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E77" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="F77" t="n">
-        <v>1.95</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2506,23 +2504,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Goias EC U20 vs Trindade U20</t>
+          <t>Bengaluru United vs Roots FC</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="C78" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="D78" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="E78" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="F78" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2533,23 +2531,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Atletico Mineiro (K) vs Itabirito (W)</t>
+          <t>Al Quwa/Jawiya vs AL Zawraa SC</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1.37</v>
+        <v>2.6</v>
       </c>
       <c r="C79" t="n">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="D79" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="E79" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F79" t="n">
-        <v>2.34</v>
+        <v>1.58</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2560,23 +2558,21 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ABC RN U20 vs Assu U20</t>
+          <t>Esteghlal Khuzestan vs Tractor Sazi FC</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2.25</v>
+        <v>8</v>
       </c>
       <c r="C80" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D80" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E80" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="n">
         <v>1.45</v>
-      </c>
-      <c r="F80" t="n">
-        <v>2.4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2587,23 +2583,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Perolas Negras U20 vs Bonsucesso U20</t>
+          <t>Shams Azar Qazvin vs Gol Gohar</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.66</v>
+        <v>3.4</v>
       </c>
       <c r="C81" t="n">
-        <v>3.3</v>
+        <v>2.63</v>
       </c>
       <c r="D81" t="n">
-        <v>4.5</v>
+        <v>2.27</v>
       </c>
       <c r="E81" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="F81" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2614,23 +2610,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Resende RJ U20 vs Olaria RJ U20</t>
+          <t>Esteghlal Tehran vs Paykan</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2.63</v>
+        <v>1.33</v>
       </c>
       <c r="C82" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="D82" t="n">
-        <v>2.45</v>
+        <v>8</v>
       </c>
       <c r="E82" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="F82" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2641,23 +2637,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>CEAC Araruama U20 vs Audax Rio RJ U20</t>
+          <t>Tolka Rovers AFC vs Finglas United FC</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="C83" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D83" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="E83" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="F83" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2668,23 +2664,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sao Goncalo U20 vs Serrano RJ U20</t>
+          <t>Beitar Petah Tikva vs Bnei Jaffa Ortodoxim</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="C84" t="n">
         <v>3.3</v>
       </c>
       <c r="D84" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="E84" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="F84" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -2695,23 +2691,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Americano RJ U20 vs America RJ U20</t>
+          <t>Maccabi Yafo Kabilyo vs Hapoel Raanana</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D85" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="E85" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="F85" t="n">
-        <v>1.85</v>
+        <v>2.18</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -2722,23 +2718,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Levski Sofia vs CSKA Sofia</t>
+          <t>Hapoel Kfar-Saba vs Maccabi Kiryat Gat Sports Club</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="C86" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D86" t="n">
-        <v>3.8</v>
+        <v>2.73</v>
       </c>
       <c r="E86" t="n">
-        <v>2.15</v>
+        <v>1.7</v>
       </c>
       <c r="F86" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -2749,23 +2745,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Jablonec vs Banik Ostrava</t>
+          <t>Maccabi Bnei Raina vs Hapoel Afula</t>
         </is>
       </c>
       <c r="B87" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="C87" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E87" t="n">
         <v>1.81</v>
       </c>
-      <c r="C87" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D87" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E87" t="n">
-        <v>1.78</v>
-      </c>
       <c r="F87" t="n">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -2776,23 +2772,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Hradec Kralove vs Viktoria Plzen</t>
+          <t>Hapoel Ironi Rishon Lezion vs Kiryat Yam</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>2.39</v>
       </c>
       <c r="C88" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D88" t="n">
-        <v>2.16</v>
+        <v>2.45</v>
       </c>
       <c r="E88" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="F88" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -2803,23 +2799,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Prostejov vs Sigma Olomouc</t>
+          <t>Hapoel Kfar Shelem vs Maccabi Ahi Nazareth FC</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>6</v>
+        <v>1.81</v>
       </c>
       <c r="C89" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="D89" t="n">
-        <v>1.38</v>
+        <v>3.5</v>
       </c>
       <c r="E89" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="F89" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -2830,23 +2826,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Viktoria Zizkov vs Sparta Prague</t>
+          <t>Ironi Modiin vs Bnei-Yehuda Tel-Aviv</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C90" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="D90" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="E90" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>2.08</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -2857,23 +2853,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>VSK Arhus vs Lyngby</t>
+          <t>Hapoel Ironi Karmiel vs Hapoel Bnei Musmus</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>7.5</v>
+        <v>1.87</v>
       </c>
       <c r="C91" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="D91" t="n">
-        <v>1.32</v>
+        <v>3.4</v>
       </c>
       <c r="E91" t="n">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="F91" t="n">
-        <v>2.22</v>
+        <v>1.83</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -2884,23 +2880,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Vanlose vs Hillerod</t>
+          <t>Beitar Naharia vs Hapoel Ihud Bnei Jatt</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>4.33</v>
+        <v>1.57</v>
       </c>
       <c r="C92" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="D92" t="n">
-        <v>1.6</v>
+        <v>4.75</v>
       </c>
       <c r="E92" t="n">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="F92" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -2911,23 +2907,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BK Frem vs Roskilde</t>
+          <t>Tzeirei Umm al-Fahm vs Maccabi Neve Shaanan Eldad</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="C93" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="D93" t="n">
-        <v>1.86</v>
+        <v>2.5</v>
       </c>
       <c r="E93" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="F93" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -2938,23 +2934,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Nykobing vs Middelfart</t>
+          <t>Maccabi Kishronot Hadera (W) vs Bnot Netanya (W)</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="C94" t="n">
         <v>3.7</v>
       </c>
       <c r="D94" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="E94" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="F94" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -2965,23 +2961,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Kolding BK vs Odense</t>
+          <t>Hapoel Raanana (W) vs Kiryat Gat SC (W)</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="C95" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="D95" t="n">
-        <v>1.87</v>
+        <v>1.16</v>
       </c>
       <c r="E95" t="n">
-        <v>1.72</v>
+        <v>1.18</v>
       </c>
       <c r="F95" t="n">
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -2992,23 +2988,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Aalborg U19 vs Vejle U19</t>
+          <t>Enkopings SK FK vs Assyriska Ff</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="C96" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D96" t="n">
         <v>2.27</v>
       </c>
       <c r="E96" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3019,23 +3015,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Fransa U20 (K) vs Ekvador U20 (K)</t>
+          <t>IFK Haninge vs Djurgardens IF</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1.38</v>
+        <v>21</v>
       </c>
       <c r="C97" t="n">
-        <v>4.33</v>
+        <v>11</v>
       </c>
       <c r="D97" t="n">
-        <v>6</v>
+        <v>1.02</v>
       </c>
       <c r="E97" t="n">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="F97" t="n">
-        <v>2.23</v>
+        <v>5</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3046,23 +3042,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Japonya U20 (K) vs ABD U20 (K)</t>
+          <t>Falkenbergs FF vs Osters IF</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="C98" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="D98" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E98" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="F98" t="n">
-        <v>1.87</v>
+        <v>2.09</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3073,23 +3069,23 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>JK Tammeka Tartu vs Paide Linnameeskond</t>
+          <t>Varbergs BoIS FC vs IFK Norrkoping</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="C99" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="D99" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="E99" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="F99" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3100,23 +3096,23 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Levadia Tallinn vs FC Kuressaare</t>
+          <t>Ostersunds FK vs IK Brage Borlange</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.12</v>
+        <v>1.9</v>
       </c>
       <c r="C100" t="n">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="D100" t="n">
-        <v>13</v>
+        <v>3.6</v>
       </c>
       <c r="E100" t="n">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="F100" t="n">
-        <v>3.6</v>
+        <v>1.87</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3127,23 +3123,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Parnu JK Vaprus vs Harju Jalgpallikool</t>
+          <t>GIF Sundsvall vs Orebro SK</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2.33</v>
+        <v>3.4</v>
       </c>
       <c r="C101" t="n">
         <v>3.5</v>
       </c>
       <c r="D101" t="n">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="E101" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="F101" t="n">
-        <v>2.39</v>
+        <v>1.87</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3154,23 +3150,23 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>HJK vs Inter Turku</t>
+          <t>Fc Bulle vs FC Amical Saint-Prex</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="C102" t="n">
-        <v>3.4</v>
+        <v>4.25</v>
       </c>
       <c r="D102" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="E102" t="n">
-        <v>1.83</v>
+        <v>1.37</v>
       </c>
       <c r="F102" t="n">
-        <v>1.87</v>
+        <v>2.73</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3181,23 +3177,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Lautp vs Kultsu</t>
+          <t>Vaengir Jupiters vs IH Hafnarfjordur</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>6</v>
+        <v>1.53</v>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="D103" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="E103" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="F103" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3208,23 +3204,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KPV Akatemia vs Nykarleby</t>
+          <t>Alftanes vs Ellidi</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1.76</v>
+        <v>1.04</v>
       </c>
       <c r="C104" t="n">
-        <v>4.25</v>
+        <v>11</v>
       </c>
       <c r="D104" t="n">
-        <v>3.2</v>
+        <v>17</v>
       </c>
       <c r="E104" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="F104" t="n">
-        <v>4.25</v>
+        <v>8</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3235,23 +3231,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>KuPS Akatemia II vs PK-37</t>
+          <t>Alafoss vs Hafnir</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2.31</v>
+        <v>1.64</v>
       </c>
       <c r="C105" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="D105" t="n">
-        <v>2.31</v>
+        <v>3.4</v>
       </c>
       <c r="E105" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="F105" t="n">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3262,23 +3258,23 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Lepa vs GrIFK Reservi</t>
+          <t>KFR (K) vs Alftanes (K)</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="C106" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="D106" t="n">
         <v>3.8</v>
       </c>
       <c r="E106" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="F106" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3289,23 +3285,23 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns vs Siwelele</t>
+          <t>KT Reykjavik (K) vs Augnablik Kopavogur (K)</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1.22</v>
+        <v>2.08</v>
       </c>
       <c r="C107" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="D107" t="n">
-        <v>11</v>
+        <v>2.5</v>
       </c>
       <c r="E107" t="n">
-        <v>1.76</v>
+        <v>1.14</v>
       </c>
       <c r="F107" t="n">
-        <v>1.94</v>
+        <v>4.75</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3316,23 +3312,23 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>FC Spaeri vs FC Rustavi</t>
+          <t>FK Buducnost Podgorica vs FK Jezero Plav</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2.9</v>
+        <v>1.93</v>
       </c>
       <c r="C108" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="D108" t="n">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="E108" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="F108" t="n">
-        <v>1.76</v>
+        <v>1.55</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3343,23 +3339,23 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FC Samgurali Tskaltubo vs Dila Gori</t>
+          <t>FK Bokelj Kotor vs FK Otrant-Olympic</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="C109" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="D109" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="E109" t="n">
-        <v>2.11</v>
+        <v>2.45</v>
       </c>
       <c r="F109" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3370,23 +3366,23 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FC Dinamo Batumi vs Iberia 1999</t>
+          <t>FK Arsenal Tivat vs Mladost DG</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="C110" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="D110" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="E110" t="n">
-        <v>1.79</v>
+        <v>2.26</v>
       </c>
       <c r="F110" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3397,23 +3393,23 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HNK Segesta Sisak vs Osijek</t>
+          <t>Al-Wakra vs Al-Shamal</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="C111" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="D111" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="E111" t="n">
-        <v>1.64</v>
+        <v>1.47</v>
       </c>
       <c r="F111" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3424,23 +3420,23 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Zagora Unesic vs Varazdin</t>
+          <t>Al Sailiya vs Al Sadd</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C112" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="D112" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="E112" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="F112" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3451,23 +3447,23 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NK Tomislav Cerna vs Lokomotiva Zagreb</t>
+          <t>Cariari Pococi vs Municipal Santa Ana</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>15</v>
+        <v>2.27</v>
       </c>
       <c r="C113" t="n">
-        <v>8</v>
+        <v>3.3</v>
       </c>
       <c r="D113" t="n">
-        <v>1.11</v>
+        <v>2.7</v>
       </c>
       <c r="E113" t="n">
-        <v>1.28</v>
+        <v>1.76</v>
       </c>
       <c r="F113" t="n">
-        <v>3.2</v>
+        <v>1.87</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3478,23 +3474,23 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Vukovar 1991 vs HNK Cibalia Vinkovci</t>
+          <t>SK Super Nova vs Tukums 2000</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="C114" t="n">
         <v>3.3</v>
       </c>
       <c r="D114" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="E114" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="F114" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -3505,23 +3501,23 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NK Bedem Ivankovo vs Dinamo Zagreb</t>
+          <t>FK Utenis Utena vs FK Sirijus Klaipeda</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>61</v>
+        <v>3.5</v>
       </c>
       <c r="C115" t="n">
-        <v>23</v>
+        <v>3.8</v>
       </c>
       <c r="D115" t="n">
-        <v>1.08</v>
+        <v>1.72</v>
       </c>
       <c r="E115" t="n">
-        <v>1.08</v>
+        <v>1.38</v>
       </c>
       <c r="F115" t="n">
-        <v>6</v>
+        <v>2.73</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -3532,23 +3528,23 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NK Uskok vs Gorica</t>
+          <t>ZFK Ljuboten (K) vs ZFK Tiverija Strumica (W)</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>6.5</v>
+        <v>1.35</v>
       </c>
       <c r="C116" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="D116" t="n">
-        <v>1.35</v>
+        <v>5</v>
       </c>
       <c r="E116" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="F116" t="n">
-        <v>2.37</v>
+        <v>4.75</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3559,23 +3555,23 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NK Hrvatski Dragovoljac vs Slaven Belupo</t>
+          <t>Al Nasr Cairo vs Dayrout</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>12</v>
+        <v>1.66</v>
       </c>
       <c r="C117" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="D117" t="n">
-        <v>1.16</v>
+        <v>4.75</v>
       </c>
       <c r="E117" t="n">
-        <v>1.38</v>
+        <v>2.23</v>
       </c>
       <c r="F117" t="n">
-        <v>2.77</v>
+        <v>1.55</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -3586,23 +3582,23 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Orijent 1919 vs NK Mladost Zdralovi</t>
+          <t>FC Masar vs El Sekka El Hadid SC</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="C118" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="D118" t="n">
-        <v>2.77</v>
+        <v>4.33</v>
       </c>
       <c r="E118" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="F118" t="n">
-        <v>1.66</v>
+        <v>1.45</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -3613,23 +3609,23 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NK Koprivnica vs Rudes Zagreb</t>
+          <t>Kahraba Ismailia vs El Dakhleya</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>10</v>
+        <v>1.71</v>
       </c>
       <c r="C119" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="D119" t="n">
-        <v>1.22</v>
+        <v>4.5</v>
       </c>
       <c r="E119" t="n">
-        <v>2.07</v>
+        <v>2.4</v>
       </c>
       <c r="F119" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -3640,23 +3636,23 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Al Jolan SC vs Zakho</t>
+          <t>Mega Sport Club vs Haras El Hodood</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="C120" t="n">
         <v>2.9</v>
       </c>
       <c r="D120" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="E120" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="F120" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -3667,23 +3663,23 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Al Talaba Fc vs Al-Karkh</t>
+          <t>Pharco vs Baladiyet El Mahallah</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="C121" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="D121" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="E121" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="F121" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -3694,23 +3690,23 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Al Minaa vs Naft Maysan</t>
+          <t>Mostaqbal Watan Club vs Gomhoryet Shebin</t>
         </is>
       </c>
       <c r="B122" t="n">
+        <v>3</v>
+      </c>
+      <c r="C122" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="E122" t="n">
         <v>2.18</v>
       </c>
-      <c r="C122" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D122" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E122" t="n">
-        <v>2.07</v>
-      </c>
       <c r="F122" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -3721,23 +3717,23 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Newroz SC vs Mosul FC</t>
+          <t>Brann U19 vs Viking U19</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>2.04</v>
+        <v>1.18</v>
       </c>
       <c r="C123" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="D123" t="n">
-        <v>3.15</v>
+        <v>7.5</v>
       </c>
       <c r="E123" t="n">
-        <v>1.98</v>
+        <v>1.06</v>
       </c>
       <c r="F123" t="n">
-        <v>1.72</v>
+        <v>7</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -3748,23 +3744,23 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Al Karma vs Al Naft</t>
+          <t>Fredrikstad FK U19 vs Asane U19</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="C124" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="D124" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="E124" t="n">
-        <v>2.23</v>
+        <v>1.22</v>
       </c>
       <c r="F124" t="n">
-        <v>1.55</v>
+        <v>3.4</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -3775,23 +3771,23 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Rangers vs St Mirren</t>
+          <t>Skeid U19 vs Ullern U19</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1.35</v>
+        <v>1.53</v>
       </c>
       <c r="C125" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="D125" t="n">
-        <v>7.5</v>
+        <v>3.6</v>
       </c>
       <c r="E125" t="n">
-        <v>1.47</v>
+        <v>1.07</v>
       </c>
       <c r="F125" t="n">
-        <v>2.45</v>
+        <v>6.5</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -3802,23 +3798,23 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>St. Johnstone vs Celtic</t>
+          <t>Klofta U19 vs Gjelleraasen U19</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="C126" t="n">
-        <v>4.33</v>
+        <v>7.5</v>
       </c>
       <c r="D126" t="n">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="E126" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="F126" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -3829,23 +3825,23 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Hapoel Rishon Lezion U19 vs Maccabi Netanya U19</t>
+          <t>Haslum IL U19 vs Nordstrand U19</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>5</v>
+        <v>1.76</v>
       </c>
       <c r="C127" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="D127" t="n">
-        <v>1.47</v>
+        <v>3</v>
       </c>
       <c r="E127" t="n">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="F127" t="n">
-        <v>2.63</v>
+        <v>6</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -3856,23 +3852,23 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Hapoel Azor vs MS Tzeirey Tira</t>
+          <t>IF Ready U19 vs Asker U19</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1.96</v>
+        <v>1.53</v>
       </c>
       <c r="C128" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D128" t="n">
         <v>3.3</v>
       </c>
-      <c r="D128" t="n">
-        <v>3.28</v>
-      </c>
       <c r="E128" t="n">
-        <v>1.91</v>
+        <v>1.07</v>
       </c>
       <c r="F128" t="n">
-        <v>1.78</v>
+        <v>7</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -3883,23 +3879,23 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Hasharon vs Hapoel Mahane Yehuda</t>
+          <t>Christiania BK U19 vs Sarpsborg 08 U19</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1.6</v>
+        <v>1.05</v>
       </c>
       <c r="C129" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="D129" t="n">
-        <v>4.25</v>
+        <v>15</v>
       </c>
       <c r="E129" t="n">
-        <v>1.58</v>
+        <v>1.07</v>
       </c>
       <c r="F129" t="n">
-        <v>2.18</v>
+        <v>7</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -3910,23 +3906,23 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sport Club Dimona vs Maccabi Yavne</t>
+          <t>Grorud U19 vs Sprint/Jeloy U19</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2.6</v>
+        <v>1.32</v>
       </c>
       <c r="C130" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="D130" t="n">
-        <v>2.37</v>
+        <v>4.75</v>
       </c>
       <c r="E130" t="n">
-        <v>1.97</v>
+        <v>1.07</v>
       </c>
       <c r="F130" t="n">
-        <v>1.74</v>
+        <v>6.5</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -3937,23 +3933,23 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sderot FC vs Maccabi Kiryat Malakhi</t>
+          <t>KFUM U19 vs Lillehammer U19</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="C131" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="D131" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="E131" t="n">
-        <v>1.87</v>
+        <v>1.1</v>
       </c>
       <c r="F131" t="n">
-        <v>1.81</v>
+        <v>5.5</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -3964,23 +3960,23 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Hapoel Hadera vs Shimshon Tel Aviv</t>
+          <t>Skedsmo U19 vs Ullensaker/Kisa U19</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>2.45</v>
+        <v>1.02</v>
       </c>
       <c r="C132" t="n">
-        <v>3.2</v>
+        <v>12</v>
       </c>
       <c r="D132" t="n">
-        <v>2.54</v>
+        <v>17</v>
       </c>
       <c r="E132" t="n">
-        <v>1.94</v>
+        <v>1.1</v>
       </c>
       <c r="F132" t="n">
-        <v>1.75</v>
+        <v>5.5</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -3991,23 +3987,23 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Hapoel Tzafririm Holon vs Hapoel Marmorek</t>
+          <t>Ibri Club vs Saham</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="D133" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="E133" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="F133" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4018,23 +4014,23 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ironi Beit Shemesh vs Kfar Saba 1928</t>
+          <t>Al Nahda vs Al Seeb</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2.73</v>
+        <v>3.15</v>
       </c>
       <c r="C134" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="D134" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="E134" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="F134" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4045,23 +4041,23 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>FC Jerusalem vs Maccabi Ashdod</t>
+          <t>Al-Samail vs Fanja</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1.53</v>
+        <v>2.55</v>
       </c>
       <c r="C135" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="D135" t="n">
-        <v>4.75</v>
+        <v>2.58</v>
       </c>
       <c r="E135" t="n">
-        <v>1.66</v>
+        <v>2.39</v>
       </c>
       <c r="F135" t="n">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4072,23 +4068,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Hapoel Herzliya vs Agudat Sport Nordia Jerusalem</t>
+          <t>PFK Dinamo Samarkand vs PFK Qizilqum Zarafshon</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="C136" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="D136" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="E136" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="F136" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4099,23 +4095,23 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Hapoel Umm Al Fahm vs Fc Tzeirei Tamra</t>
+          <t>Andijan vs FK Kokand 1912</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="C137" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="D137" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="E137" t="n">
-        <v>1.62</v>
+        <v>2.27</v>
       </c>
       <c r="F137" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4126,17 +4122,17 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Hapoel Ironi Baqa Al-Gharbiyye vs Ironi Nesher</t>
+          <t>Xorazm Urganch vs PFK Sogdiyona Jizzax</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="C138" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="D138" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="E138" t="n">
         <v>1.83</v>
@@ -4153,23 +4149,23 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sandvikens IF vs IK Oddevold</t>
+          <t>CD Plaza Amador (W) vs Tevi Cocle FC (W)</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2.05</v>
+        <v>1.28</v>
       </c>
       <c r="C139" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D139" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="E139" t="n">
-        <v>1.72</v>
+        <v>1.16</v>
       </c>
       <c r="F139" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4180,23 +4176,23 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Landskrona Bois vs Helsingborgs IF</t>
+          <t>UMECIT Reserves vs Plaza Amador Reserves</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1.78</v>
+        <v>2.73</v>
       </c>
       <c r="C140" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D140" t="n">
-        <v>3.8</v>
+        <v>2.02</v>
       </c>
       <c r="E140" t="n">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="F140" t="n">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4207,23 +4203,23 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ljungskile SK vs Norrby IF</t>
+          <t>Club Sportivo Carapegua vs Benjamin Aceval</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="C141" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="D141" t="n">
-        <v>3.15</v>
+        <v>2.1</v>
       </c>
       <c r="E141" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="F141" t="n">
-        <v>2.25</v>
+        <v>1.96</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4234,23 +4230,23 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>United IK Nordic vs IFK Varnamo</t>
+          <t>Dukagjini vs Malisheva</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2.08</v>
+        <v>2.39</v>
       </c>
       <c r="C142" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="D142" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="E142" t="n">
-        <v>1.66</v>
+        <v>1.87</v>
       </c>
       <c r="F142" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -4261,23 +4257,23 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>IFK Goteborg (K) vs BK Hacken (K)</t>
+          <t>Dinamo Barnaul vs FC Chelyabinsk</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>15</v>
+        <v>5.5</v>
       </c>
       <c r="C143" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="D143" t="n">
-        <v>1.07</v>
+        <v>1.47</v>
       </c>
       <c r="E143" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="F143" t="n">
-        <v>3.8</v>
+        <v>2.22</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -4288,23 +4284,23 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Hammarby IF (K) vs Gamla Upsala (K)</t>
+          <t>Luki-Energiya vs Ural Yekaterinburg</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>17</v>
+        <v>3.8</v>
       </c>
       <c r="C144" t="n">
-        <v>29</v>
+        <v>3.3</v>
       </c>
       <c r="D144" t="n">
-        <v>1.02</v>
+        <v>1.84</v>
       </c>
       <c r="E144" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="F144" t="n">
-        <v>10</v>
+        <v>2.35</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4315,23 +4311,23 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Zurich (K) vs Young Boys (K)</t>
+          <t>Shinnik Yaroslav vs Torpedo Moskva</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1.83</v>
+        <v>3.15</v>
       </c>
       <c r="C145" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>3.3</v>
+        <v>2.14</v>
       </c>
       <c r="E145" t="n">
-        <v>1.51</v>
+        <v>2.2</v>
       </c>
       <c r="F145" t="n">
-        <v>2.34</v>
+        <v>1.6</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4342,23 +4338,23 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Basel (K) vs Grasshopper (K)</t>
+          <t>Radnik Surdulica vs Kızılyıldız</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>2.1</v>
+        <v>8.5</v>
       </c>
       <c r="C146" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="D146" t="n">
-        <v>2.9</v>
+        <v>1.25</v>
       </c>
       <c r="E146" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="F146" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -4369,23 +4365,23 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Luzern (K) vs Rapperswil-Jona (K)</t>
+          <t>Teleoptik Zemun vs Proleter 023 Zrenjanin</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="C147" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D147" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="E147" t="n">
-        <v>1.51</v>
+        <v>1.83</v>
       </c>
       <c r="F147" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4396,23 +4392,23 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>FC Koniz vs FC Allschwil</t>
+          <t>Police FC vs Updf Fc</t>
         </is>
       </c>
       <c r="B148" t="n">
         <v>1.74</v>
       </c>
       <c r="C148" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="D148" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="E148" t="n">
-        <v>1.47</v>
+        <v>1.95</v>
       </c>
       <c r="F148" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -4423,23 +4419,23 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>FC Thun (W) vs FC Sion (W)</t>
+          <t>FC Nyva Vinnytsia vs Dynamo Kiev</t>
         </is>
       </c>
       <c r="B149" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="C149" t="n">
+        <v>7</v>
+      </c>
+      <c r="D149" t="n">
         <v>1.13</v>
       </c>
-      <c r="C149" t="n">
-        <v>6</v>
-      </c>
-      <c r="D149" t="n">
-        <v>9</v>
-      </c>
       <c r="E149" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="F149" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -4450,23 +4446,23 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Lugano (W) vs AS Gambarogno (W)</t>
+          <t>Club Atletico Cerro vs Cerrito CS</t>
         </is>
       </c>
       <c r="B150" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="C150" t="n">
+        <v>3</v>
+      </c>
+      <c r="D150" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E150" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F150" t="n">
         <v>1.47</v>
-      </c>
-      <c r="C150" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D150" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E150" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F150" t="n">
-        <v>2.27</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -4477,23 +4473,23 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>UMF Njardvik vs Throttur Reykjavik</t>
+          <t>Amman FC vs Hayy Al-Amir Hassan</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>2.63</v>
+        <v>1.66</v>
       </c>
       <c r="C151" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="D151" t="n">
-        <v>2.22</v>
+        <v>4.25</v>
       </c>
       <c r="E151" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="F151" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -4504,23 +4500,23 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Kopavogur vs Fylkir Reykjavik</t>
+          <t>Ittihad AL Ramtha vs AL Sareeh</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="C152" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="D152" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="E152" t="n">
-        <v>1.28</v>
+        <v>2.18</v>
       </c>
       <c r="F152" t="n">
-        <v>3.28</v>
+        <v>1.6</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -4531,23 +4527,23 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Afturelding (K) vs Dalvik/Reynir (K)</t>
+          <t>Al Jazeera vs Shabab Al Ordon</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1.14</v>
+        <v>2.31</v>
       </c>
       <c r="C153" t="n">
-        <v>7.5</v>
+        <v>3.1</v>
       </c>
       <c r="D153" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="E153" t="n">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="F153" t="n">
-        <v>5.5</v>
+        <v>1.62</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -4558,23 +4554,23 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Decic Tuzi vs OFK Petrovac</t>
+          <t>The Cong Viettel FC vs Cong Anh Ha Noi</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="C154" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="D154" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="E154" t="n">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="F154" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -4585,23 +4581,23 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Kairat Almaty vs Zhenys</t>
+          <t>Panathinaikos vs AE Kifisia</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="C155" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D155" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="E155" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="F155" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -4612,23 +4608,23 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Independiente Santa Fe (K) vs Deportivo Cali (K)</t>
+          <t>Asteras Tripolis vs Aris Thessaloniki</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="C156" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="D156" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="E156" t="n">
-        <v>2.4</v>
+        <v>1.87</v>
       </c>
       <c r="F156" t="n">
-        <v>1.5</v>
+        <v>1.81</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -4639,1668 +4635,25 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>America de Cali (K) vs Orsomarso (K)</t>
+          <t>Mafunzo FC vs Polisi Zanzibar</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1.33</v>
+        <v>2.27</v>
       </c>
       <c r="C157" t="n">
-        <v>4.15</v>
+        <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="E157" t="n">
-        <v>1.99</v>
+        <v>2.36</v>
       </c>
       <c r="F157" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="G157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Independiente Yumbo vs Deportes Quindio</t>
-        </is>
-      </c>
-      <c r="B158" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="C158" t="n">
-        <v>3</v>
-      </c>
-      <c r="D158" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E158" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="F158" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Ferrovalvulas FC vs Universidad de Antioquia</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C159" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D159" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E159" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="F159" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Sion Swifts LFC (K) vs St. James Swifts (K)</t>
-        </is>
-      </c>
-      <c r="B160" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="C160" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D160" t="n">
-        <v>15</v>
-      </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Ballymena United (K) vs Ballyclare Comrades (K)</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="C161" t="n">
-        <v>4</v>
-      </c>
-      <c r="D161" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="E161" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F161" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Bangor (K) vs Ballymoney United (K)</t>
-        </is>
-      </c>
-      <c r="B162" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="C162" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="D162" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="E162" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F162" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Greenisland (K) vs Mid Ulster (K)</t>
-        </is>
-      </c>
-      <c r="B163" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="C163" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D163" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="E163" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="F163" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Zalgiris Kauno vs FK Suduva Marijampole</t>
-        </is>
-      </c>
-      <c r="B164" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="C164" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D164" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E164" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="F164" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Novaci vs Ohrid</t>
-        </is>
-      </c>
-      <c r="B165" t="n">
-        <v>5</v>
-      </c>
-      <c r="C165" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D165" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E165" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="F165" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Fk Teteks vs Bregalnica Stip</t>
-        </is>
-      </c>
-      <c r="B166" t="n">
-        <v>11</v>
-      </c>
-      <c r="C166" t="n">
-        <v>6</v>
-      </c>
-      <c r="D166" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E166" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F166" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Pyramids FC vs El Gouna FC</t>
-        </is>
-      </c>
-      <c r="B167" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="C167" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D167" t="n">
-        <v>7</v>
-      </c>
-      <c r="E167" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="F167" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Modern Sport FC vs Wady Degla</t>
-        </is>
-      </c>
-      <c r="B168" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="C168" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="D168" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E168" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F168" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Al Moqawloon Al Arab vs Al Ahly Cairo</t>
-        </is>
-      </c>
-      <c r="B169" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="C169" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="D169" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E169" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="F169" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>ENPPI Club vs FC Masr (ZED)</t>
-        </is>
-      </c>
-      <c r="B170" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="C170" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="D170" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E170" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F170" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Olmaliq OKMK vs Pakhtakor Tashkent</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>3</v>
-      </c>
-      <c r="C171" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D171" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E171" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="F171" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Neftchi Fargona vs Surkhon Termez</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C172" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D172" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="E172" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="F172" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Nasaf Qarshi vs FC Bunyodkor</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="C173" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D173" t="n">
-        <v>7</v>
-      </c>
-      <c r="E173" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="F173" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Deportivo Santani vs Independiente FBC</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="C174" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="D174" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E174" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="F174" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>12 de Octubre de San Domingo vs Silvio Pettirossi</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="C175" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D175" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E175" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="F175" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>24 de Setiembre vs Club Olimpia De Ita</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C176" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D176" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E176" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F176" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>3 de Febrero FBC vs Presidente Hayes</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="C177" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D177" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E177" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="F177" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>12 de Octubre vs Club General Martin Ledesma</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="C178" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D178" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="E178" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="F178" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Dalin Myslenice vs MKS Limanovia Limanowa</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="C179" t="n">
-        <v>4</v>
-      </c>
-      <c r="D179" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="E179" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="F179" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Cracovia Krakow II vs LKS Blekitni Modlnica</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D180" t="n">
-        <v>10</v>
-      </c>
-      <c r="E180" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="F180" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>LKS Wolania Wola Rzedzinska vs Poprad Muszyna</t>
-        </is>
-      </c>
-      <c r="B181" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="C181" t="n">
-        <v>4</v>
-      </c>
-      <c r="D181" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="E181" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="F181" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>GKS Victoria Jaworzno vs Watra Bialka Tatrzanska</t>
-        </is>
-      </c>
-      <c r="B182" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="C182" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D182" t="n">
-        <v>7</v>
-      </c>
-      <c r="E182" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F182" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>KF Feronikeli vs Drita Gjilan</t>
-        </is>
-      </c>
-      <c r="B183" t="n">
-        <v>6</v>
-      </c>
-      <c r="C183" t="n">
-        <v>4</v>
-      </c>
-      <c r="D183" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E183" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F183" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>SC Gjilani vs Ballkani</t>
-        </is>
-      </c>
-      <c r="B184" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C184" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D184" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E184" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="F184" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Dinamo Kirov vs Kamaz Nab Chelny</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C185" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D185" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E185" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F185" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>FK Sokol Saratov vs Leningradets</t>
-        </is>
-      </c>
-      <c r="B186" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="C186" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D186" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="E186" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="F186" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Murom vs Veles Moscow</t>
-        </is>
-      </c>
-      <c r="B187" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="C187" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="D187" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E187" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="F187" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>FK Kaluga vs Ufa</t>
-        </is>
-      </c>
-      <c r="B188" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="C188" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="D188" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="E188" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="F188" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>FC Volgar Astrakhan vs Volga Ulyanovsk</t>
-        </is>
-      </c>
-      <c r="B189" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="C189" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D189" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E189" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="F189" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Dinamo Stavropol vs Nizhny Novgorod</t>
-        </is>
-      </c>
-      <c r="B190" t="n">
-        <v>8</v>
-      </c>
-      <c r="C190" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="D190" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E190" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F190" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Chertanovo Moscow vs Neftekhimik Nizhnekamsk</t>
-        </is>
-      </c>
-      <c r="B191" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="C191" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D191" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E191" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F191" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Dinamo Saint-Petersburg vs Sochi</t>
-        </is>
-      </c>
-      <c r="B192" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="C192" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D192" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="E192" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="F192" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Druzhba Maikop vs Yenisey Krasnoyarsk</t>
-        </is>
-      </c>
-      <c r="B193" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="C193" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D193" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E193" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="F193" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Nova Bana vs Vion Zlate Moravce</t>
-        </is>
-      </c>
-      <c r="B194" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="C194" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D194" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E194" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="F194" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>Banik Prievidza vs Banik Lehota pod Vtacnikom</t>
-        </is>
-      </c>
-      <c r="B195" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C195" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D195" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="E195" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="F195" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>NK Roltek Dob vs ND Slovan Ljubljana</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="C196" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D196" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E196" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F196" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>NK Bistrica vs Odranci</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>17</v>
-      </c>
-      <c r="C197" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D197" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E197" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F197" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Rudar Trbovlje vs Radomlje</t>
-        </is>
-      </c>
-      <c r="B198" t="n">
-        <v>12</v>
-      </c>
-      <c r="C198" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="D198" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E198" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="F198" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>Jadran Dekani vs Koper</t>
-        </is>
-      </c>
-      <c r="B199" t="n">
-        <v>17</v>
-      </c>
-      <c r="C199" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D199" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E199" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="F199" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>NK Rudar Velenje vs Celje</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>11</v>
-      </c>
-      <c r="C200" t="n">
-        <v>6</v>
-      </c>
-      <c r="D200" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E200" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="F200" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Al Kholood vs Al Shabab Riyadh</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C201" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D201" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="E201" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F201" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Al Fateh vs Al Diriyah</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C202" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D202" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="E202" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="F202" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Al-Nassr Riyadh vs Abha</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="C203" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D203" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="E203" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="F203" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Al Raed Buraidah vs Al-Jeel</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="C204" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D204" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E204" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="F204" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>Al Jandal vs Al-Bukayriyah FC</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="C205" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="D205" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E205" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="F205" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>Jeddah Club vs Al-Orubah</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C206" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D206" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E206" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="F206" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>Huachipato (W) vs Deportes Iquique (W)</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="C207" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D207" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E207" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="F207" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>Polissya Zhytomyr vs Kudrivka</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="C208" t="n">
-        <v>5</v>
-      </c>
-      <c r="D208" t="n">
-        <v>9</v>
-      </c>
-      <c r="E208" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="F208" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Boston River vs Colon FC</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="C209" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D209" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E209" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="F209" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Racing Club de Montevideo vs Central Espanol FC</t>
-        </is>
-      </c>
-      <c r="B210" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="C210" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="D210" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E210" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="F210" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Real Frontera vs Zamora FC</t>
-        </is>
-      </c>
-      <c r="B211" t="n">
-        <v>8</v>
-      </c>
-      <c r="C211" t="n">
-        <v>5</v>
-      </c>
-      <c r="D211" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E211" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="F211" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Club Atletico Barinas vs Atletico El Vigia</t>
-        </is>
-      </c>
-      <c r="B212" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C212" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D212" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E212" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="F212" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Urena Fc vs Rayo Zuliano</t>
-        </is>
-      </c>
-      <c r="B213" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="C213" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D213" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="E213" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="F213" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Academia Anzoategui vs Dvo Italia</t>
-        </is>
-      </c>
-      <c r="B214" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C214" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D214" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="E214" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="F214" t="n">
-        <v>2</v>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Monagas SC vs Bolivar SC</t>
-        </is>
-      </c>
-      <c r="B215" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C215" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D215" t="n">
-        <v>6</v>
-      </c>
-      <c r="E215" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="F215" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Yaracuyanos FC vs Aragua FC</t>
-        </is>
-      </c>
-      <c r="B216" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="C216" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="D216" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E216" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="F216" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>OFI Crete vs Nestos Chrisoupolis</t>
-        </is>
-      </c>
-      <c r="B217" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="C217" t="n">
-        <v>6</v>
-      </c>
-      <c r="D217" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="E217" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="F217" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Volos NPS U19 vs Iraklis 1908 FC U19</t>
-        </is>
-      </c>
-      <c r="B218" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="C218" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D218" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="E218" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="F218" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="G218" t="inlineStr">
         <is>
           <t>-</t>
         </is>
